--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Avance Montecarlo'!$A$3:$G$51</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Camino a la final'!$A$3:$I$51</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Partidos A-L'!$A$3:$M$75</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Partidos A-L'!$A$3:$O$75</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="270">
   <si>
     <t xml:space="preserve">Proyección Mundial 2026 — Archivo maestro</t>
   </si>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Es una estimación probabilística reproducible, NO un pronóstico fiable. Solo usa el ranking: ignora lesiones, forma y bajas. Los cruces de octavos en adelante usan el orden estándar del cuadro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Proyección por modelo — 72 partidos de grupos</t>
+    <t xml:space="preserve">Proyección por modelo — 72 partidos de grupos (hora de Ciudad de México)</t>
   </si>
   <si>
     <t xml:space="preserve">Grupo</t>
@@ -120,6 +120,12 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
+    <t xml:space="preserve">Hora (CDMX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadio</t>
+  </si>
+  <si>
     <t xml:space="preserve">Local</t>
   </si>
   <si>
@@ -159,6 +165,12 @@
     <t xml:space="preserve">11 jun</t>
   </si>
   <si>
+    <t xml:space="preserve">13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadio Azteca, Mexico City</t>
+  </si>
+  <si>
     <t xml:space="preserve">México</t>
   </si>
   <si>
@@ -171,291 +183,372 @@
     <t xml:space="preserve">Favorito: México</t>
   </si>
   <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadio Akron, Guadalajara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corea del Sur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">República Checa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Corea del Sur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercedes-Benz Stadium, Atlanta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: República Checa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 – 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadio BBVA, Monterrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
     <t xml:space="preserve">12 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">Corea del Sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">República Checa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 – 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Corea del Sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: República Checa</t>
+    <t xml:space="preserve">BMO Field, Toronto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canadá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosnia y Herzegovina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Canadá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levi's Stadium, San Francisco Bay Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suiza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Suiza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SoFi Stadium, Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC Place, Vancouver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumen Field, Seattle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estados Unidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paraguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Estados Unidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turquía</t>
   </si>
   <si>
     <t xml:space="preserve">19 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">1 – 0</t>
+    <t xml:space="preserve">21:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Turquía</t>
   </si>
   <si>
     <t xml:space="preserve">25 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">0 – 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canadá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosnia y Herzegovina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Canadá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suiza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Suiza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estados Unidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paraguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Estados Unidos</t>
+    <t xml:space="preserve">Favorito: Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MetLife Stadium, New York New Jersey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brasil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marruecos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gillette Stadium, Boston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haití</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escocia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Escocia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Marruecos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lincoln Financial Field, Philadelphia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Brasil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard Rock Stadium, Miami</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
   </si>
   <si>
     <t xml:space="preserve">14 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turquía</t>
+    <t xml:space="preserve">11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRG Stadium, Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alemania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curazao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Alemania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costa de Marfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Ecuador</t>
   </si>
   <si>
     <t xml:space="preserve">20 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">Favorito: Turquía</t>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrowhead Stadium, Kansas City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Costa de Marfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT&amp;T Stadium, Dallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Países Bajos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Países Bajos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suecia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Túnez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Japón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arabia Saudita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uruguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Uruguay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">España</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: España</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 jun</t>
   </si>
   <si>
     <t xml:space="preserve">26 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">Favorito: Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brasil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marruecos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haití</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escocia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Escocia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Marruecos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Brasil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alemania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curazao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Alemania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costa de Marfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Costa de Marfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Países Bajos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Países Bajos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suecia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Túnez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Japón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arabia Saudita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uruguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Uruguay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">España</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabo Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: España</t>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bélgica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egipto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Bélgica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Zelanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Irán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Egipto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 – 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Francia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noruega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Noruega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Senegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inglaterra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Inglaterra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panamá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Panamá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Croacia</t>
   </si>
   <si>
     <t xml:space="preserve">27 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bélgica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egipto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Bélgica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva Zelanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Irán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Egipto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 – 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senegal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Francia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noruega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Noruega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Senegal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inglaterra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Inglaterra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panamá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Panamá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Croacia</t>
-  </si>
-  <si>
     <t xml:space="preserve">K</t>
   </si>
   <si>
@@ -477,6 +570,9 @@
     <t xml:space="preserve">Favorito: Colombia</t>
   </si>
   <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">L</t>
   </si>
   <si>
@@ -501,48 +597,48 @@
     <t xml:space="preserve">Favorito: Argelia</t>
   </si>
   <si>
+    <t xml:space="preserve">Probabilidad de avanzar — Montecarlo (20.000 torneos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selección</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prob. ganar grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prob. 1º o 2º</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prob. avanzar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probabilidad de avanzar por grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieciseisavos (Round of 32) — clasificados más probables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipo 1 (proyectado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipo 2 (proyectado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sede</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M73</t>
+  </si>
+  <si>
     <t xml:space="preserve">28 jun</t>
   </si>
   <si>
-    <t xml:space="preserve">Probabilidad de avanzar — Montecarlo (20.000 torneos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selección</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prob. ganar grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prob. 1º o 2º</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prob. avanzar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probabilidad de avanzar por grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dieciseisavos (Round of 32) — clasificados más probables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipo 1 (proyectado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipo 2 (proyectado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sede</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M73</t>
-  </si>
-  <si>
     <t xml:space="preserve">Corea del Sur (2A)</t>
   </si>
   <si>
@@ -576,9 +672,6 @@
     <t xml:space="preserve">Turquía (2C)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estadio BBVA, Monterrey</t>
-  </si>
-  <si>
     <t xml:space="preserve">M76</t>
   </si>
   <si>
@@ -672,9 +765,6 @@
     <t xml:space="preserve">Austria (2L)</t>
   </si>
   <si>
-    <t xml:space="preserve">BMO Field, Toronto</t>
-  </si>
-  <si>
     <t xml:space="preserve">M84</t>
   </si>
   <si>
@@ -691,9 +781,6 @@
   </si>
   <si>
     <t xml:space="preserve">Suecia (3º F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC Place, Vancouver</t>
   </si>
   <si>
     <t xml:space="preserve">M86</t>
@@ -1013,11 +1100,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1352,11 +1439,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="16736874"/>
-        <c:axId val="75860595"/>
+        <c:axId val="84046302"/>
+        <c:axId val="42160312"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16736874"/>
+        <c:axId val="84046302"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1388,7 +1475,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75860595"/>
+        <c:crossAx val="42160312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1396,7 +1483,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75860595"/>
+        <c:axId val="42160312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1440,7 +1527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16736874"/>
+        <c:crossAx val="84046302"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1594,11 +1681,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83611446"/>
-        <c:axId val="33091571"/>
+        <c:axId val="88992198"/>
+        <c:axId val="12933486"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83611446"/>
+        <c:axId val="88992198"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1630,7 +1717,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33091571"/>
+        <c:crossAx val="12933486"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1638,7 +1725,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33091571"/>
+        <c:axId val="12933486"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1682,7 +1769,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83611446"/>
+        <c:crossAx val="88992198"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1836,11 +1923,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="20628751"/>
-        <c:axId val="3063018"/>
+        <c:axId val="17566019"/>
+        <c:axId val="47420021"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="20628751"/>
+        <c:axId val="17566019"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1872,7 +1959,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3063018"/>
+        <c:crossAx val="47420021"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1880,7 +1967,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3063018"/>
+        <c:axId val="47420021"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1924,7 +2011,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20628751"/>
+        <c:crossAx val="17566019"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2078,11 +2165,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="37445929"/>
-        <c:axId val="9750230"/>
+        <c:axId val="93282579"/>
+        <c:axId val="33113769"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="37445929"/>
+        <c:axId val="93282579"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2114,7 +2201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9750230"/>
+        <c:crossAx val="33113769"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2122,7 +2209,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="9750230"/>
+        <c:axId val="33113769"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2166,7 +2253,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37445929"/>
+        <c:crossAx val="93282579"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2368,11 +2455,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="51134108"/>
-        <c:axId val="24234431"/>
+        <c:axId val="59775977"/>
+        <c:axId val="76891431"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="51134108"/>
+        <c:axId val="59775977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2404,7 +2491,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24234431"/>
+        <c:crossAx val="76891431"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2412,7 +2499,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24234431"/>
+        <c:axId val="76891431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2454,7 +2541,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51134108"/>
+        <c:crossAx val="59775977"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2608,11 +2695,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="81854812"/>
-        <c:axId val="37683877"/>
+        <c:axId val="46728005"/>
+        <c:axId val="15642665"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81854812"/>
+        <c:axId val="46728005"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2644,7 +2731,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37683877"/>
+        <c:crossAx val="15642665"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2652,7 +2739,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37683877"/>
+        <c:axId val="15642665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2696,7 +2783,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81854812"/>
+        <c:crossAx val="46728005"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2850,11 +2937,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="12670426"/>
-        <c:axId val="58578949"/>
+        <c:axId val="93069456"/>
+        <c:axId val="65405806"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="12670426"/>
+        <c:axId val="93069456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2886,7 +2973,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58578949"/>
+        <c:crossAx val="65405806"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2894,7 +2981,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58578949"/>
+        <c:axId val="65405806"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2938,7 +3025,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12670426"/>
+        <c:crossAx val="93069456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3092,11 +3179,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="95190869"/>
-        <c:axId val="82034265"/>
+        <c:axId val="42877766"/>
+        <c:axId val="76985555"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="95190869"/>
+        <c:axId val="42877766"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3128,7 +3215,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82034265"/>
+        <c:crossAx val="76985555"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3136,7 +3223,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82034265"/>
+        <c:axId val="76985555"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3180,7 +3267,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95190869"/>
+        <c:crossAx val="42877766"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3334,11 +3421,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="99245635"/>
-        <c:axId val="16613848"/>
+        <c:axId val="22094353"/>
+        <c:axId val="81880375"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="99245635"/>
+        <c:axId val="22094353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3370,7 +3457,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16613848"/>
+        <c:crossAx val="81880375"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3378,7 +3465,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16613848"/>
+        <c:axId val="81880375"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3422,7 +3509,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99245635"/>
+        <c:crossAx val="22094353"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3576,11 +3663,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="66817292"/>
-        <c:axId val="16967270"/>
+        <c:axId val="16358479"/>
+        <c:axId val="71180070"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66817292"/>
+        <c:axId val="16358479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3612,7 +3699,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16967270"/>
+        <c:crossAx val="71180070"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3620,7 +3707,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16967270"/>
+        <c:axId val="71180070"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3664,7 +3751,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66817292"/>
+        <c:crossAx val="16358479"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3818,11 +3905,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="34328153"/>
-        <c:axId val="89728294"/>
+        <c:axId val="1829650"/>
+        <c:axId val="69437396"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34328153"/>
+        <c:axId val="1829650"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3854,7 +3941,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89728294"/>
+        <c:crossAx val="69437396"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3862,7 +3949,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89728294"/>
+        <c:axId val="69437396"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3906,7 +3993,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34328153"/>
+        <c:crossAx val="1829650"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4060,11 +4147,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="91631297"/>
-        <c:axId val="1709468"/>
+        <c:axId val="94951035"/>
+        <c:axId val="40675791"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91631297"/>
+        <c:axId val="94951035"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4096,7 +4183,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1709468"/>
+        <c:crossAx val="40675791"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4104,7 +4191,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1709468"/>
+        <c:axId val="40675791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4148,7 +4235,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91631297"/>
+        <c:crossAx val="94951035"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4302,11 +4389,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="55035820"/>
-        <c:axId val="76048759"/>
+        <c:axId val="64611270"/>
+        <c:axId val="15533168"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55035820"/>
+        <c:axId val="64611270"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4338,7 +4425,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76048759"/>
+        <c:crossAx val="15533168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4346,7 +4433,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76048759"/>
+        <c:axId val="15533168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4390,7 +4477,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55035820"/>
+        <c:crossAx val="64611270"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5155,21 +5242,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5188,6 +5277,8 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -5229,3035 +5320,3473 @@
       <c r="M3" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="N3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="8" t="n">
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <f aca="false">ABS(D4-F4)</f>
+      <c r="I4" s="8" t="n">
+        <f aca="false">ABS(F4-H4)</f>
         <v>46</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="J4" s="11" t="n">
         <v>0.711</v>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="K4" s="11" t="n">
         <v>0.192</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="L4" s="11" t="n">
         <v>0.097</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>42</v>
+      <c r="M4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <f aca="false">ABS(D5-F5)</f>
+      <c r="I5" s="8" t="n">
+        <f aca="false">ABS(F5-H5)</f>
         <v>15</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="J5" s="11" t="n">
         <v>0.46</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="K5" s="11" t="n">
         <v>0.258</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="L5" s="11" t="n">
         <v>0.282</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>47</v>
+      <c r="M5" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="8" t="n">
+      <c r="G6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <f aca="false">ABS(D6-F6)</f>
+      <c r="I6" s="8" t="n">
+        <f aca="false">ABS(F6-H6)</f>
         <v>20</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="J6" s="11" t="n">
         <v>0.441</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="K6" s="11" t="n">
         <v>0.26</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="L6" s="11" t="n">
         <v>0.299</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>48</v>
+      <c r="M6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="8" t="n">
+      <c r="G7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <f aca="false">ABS(D7-F7)</f>
+      <c r="I7" s="8" t="n">
+        <f aca="false">ABS(F7-H7)</f>
         <v>11</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="J7" s="11" t="n">
         <v>0.548</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="K7" s="11" t="n">
         <v>0.243</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="L7" s="11" t="n">
         <v>0.209</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>42</v>
+      <c r="M7" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="8" t="n">
+      <c r="G8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <f aca="false">ABS(D8-F8)</f>
+      <c r="I8" s="8" t="n">
+        <f aca="false">ABS(F8-H8)</f>
         <v>26</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="J8" s="11" t="n">
         <v>0.142</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="K8" s="11" t="n">
         <v>0.217</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="L8" s="11" t="n">
         <v>0.641</v>
       </c>
-      <c r="K8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>42</v>
+      <c r="M8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>60</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G9" s="8" t="n">
-        <f aca="false">ABS(D9-F9)</f>
+      <c r="I9" s="8" t="n">
+        <f aca="false">ABS(F9-H9)</f>
         <v>35</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="J9" s="11" t="n">
         <v>0.219</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="K9" s="11" t="n">
         <v>0.246</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="L9" s="11" t="n">
         <v>0.535</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>47</v>
+      <c r="M9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="8" t="n">
+      <c r="G10" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <f aca="false">ABS(D10-F10)</f>
+      <c r="I10" s="8" t="n">
+        <f aca="false">ABS(F10-H10)</f>
         <v>34</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="J10" s="11" t="n">
         <v>0.58</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="K10" s="11" t="n">
         <v>0.235</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="L10" s="11" t="n">
         <v>0.185</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>58</v>
+      <c r="M10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="G11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <f aca="false">ABS(F11-H11)</f>
+        <v>37</v>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <f aca="false">ABS(D11-F11)</f>
-        <v>37</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>63</v>
+      <c r="N11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="8" t="n">
+      <c r="G12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <f aca="false">ABS(D12-F12)</f>
+      <c r="I12" s="8" t="n">
+        <f aca="false">ABS(F12-H12)</f>
         <v>45</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="J12" s="11" t="n">
         <v>0.618</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="K12" s="11" t="n">
         <v>0.225</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="L12" s="11" t="n">
         <v>0.158</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>63</v>
+      <c r="M12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="8" t="n">
+      <c r="G13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="G13" s="8" t="n">
-        <f aca="false">ABS(D13-F13)</f>
+      <c r="I13" s="8" t="n">
+        <f aca="false">ABS(F13-H13)</f>
         <v>26</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="J13" s="11" t="n">
         <v>0.553</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="K13" s="11" t="n">
         <v>0.242</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="L13" s="11" t="n">
         <v>0.206</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>58</v>
+      <c r="M13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="8" t="n">
+      <c r="G14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="8" t="n">
-        <f aca="false">ABS(D14-F14)</f>
+      <c r="I14" s="8" t="n">
+        <f aca="false">ABS(F14-H14)</f>
         <v>11</v>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="J14" s="11" t="n">
         <v>0.405</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="K14" s="11" t="n">
         <v>0.263</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="L14" s="11" t="n">
         <v>0.332</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>67</v>
+      <c r="M14" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="8" t="n">
+      <c r="G15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H15" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="G15" s="8" t="n">
-        <f aca="false">ABS(D15-F15)</f>
+      <c r="I15" s="8" t="n">
+        <f aca="false">ABS(F15-H15)</f>
         <v>8</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="J15" s="11" t="n">
         <v>0.342</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="K15" s="11" t="n">
         <v>0.263</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="L15" s="11" t="n">
         <v>0.395</v>
       </c>
-      <c r="K15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>67</v>
+      <c r="M15" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <f aca="false">ABS(F16-H16)</f>
+        <v>24</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="M16" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <f aca="false">ABS(D16-F16)</f>
-        <v>24</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>69</v>
+      <c r="N16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O16" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D17" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" s="8" t="n">
+      <c r="G17" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <f aca="false">ABS(D17-F17)</f>
+      <c r="I17" s="8" t="n">
+        <f aca="false">ABS(F17-H17)</f>
         <v>5</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="J17" s="11" t="n">
         <v>0.345</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="K17" s="11" t="n">
         <v>0.264</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="L17" s="11" t="n">
         <v>0.392</v>
       </c>
-      <c r="K17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>67</v>
+      <c r="M17" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="8" t="n">
+      <c r="G18" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <f aca="false">ABS(D18-F18)</f>
+      <c r="I18" s="8" t="n">
+        <f aca="false">ABS(F18-H18)</f>
         <v>10</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="J18" s="11" t="n">
         <v>0.536</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="K18" s="11" t="n">
         <v>0.246</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="L18" s="11" t="n">
         <v>0.219</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>69</v>
+      <c r="M18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O18" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="8" t="n">
+      <c r="G19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <f aca="false">ABS(D19-F19)</f>
+      <c r="I19" s="8" t="n">
+        <f aca="false">ABS(F19-H19)</f>
         <v>19</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="J19" s="11" t="n">
         <v>0.48</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="K19" s="11" t="n">
         <v>0.256</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="L19" s="11" t="n">
         <v>0.265</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>74</v>
+      <c r="M19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="8" t="n">
+      <c r="G20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="G20" s="8" t="n">
-        <f aca="false">ABS(D20-F20)</f>
+      <c r="I20" s="8" t="n">
+        <f aca="false">ABS(F20-H20)</f>
         <v>5</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="J20" s="11" t="n">
         <v>0.238</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="K20" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="L20" s="11" t="n">
         <v>0.511</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>69</v>
+      <c r="M20" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O20" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="8" t="n">
+      <c r="G21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <f aca="false">ABS(D21-F21)</f>
+      <c r="I21" s="8" t="n">
+        <f aca="false">ABS(F21-H21)</f>
         <v>14</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="J21" s="11" t="n">
         <v>0.286</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="K21" s="11" t="n">
         <v>0.259</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="L21" s="11" t="n">
         <v>0.455</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>73</v>
+      <c r="M21" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <f aca="false">ABS(F22-H22)</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="M22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="O22" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <f aca="false">ABS(D22-F22)</f>
-        <v>1</v>
-      </c>
-      <c r="H22" s="11" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="I22" s="11" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="8" t="n">
+      <c r="G23" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H23" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="G23" s="8" t="n">
-        <f aca="false">ABS(D23-F23)</f>
+      <c r="I23" s="8" t="n">
+        <f aca="false">ABS(F23-H23)</f>
         <v>41</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="J23" s="11" t="n">
         <v>0.238</v>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="K23" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="L23" s="11" t="n">
         <v>0.511</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>83</v>
+      <c r="M23" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="O23" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="8" t="n">
+      <c r="G24" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <f aca="false">ABS(D24-F24)</f>
+      <c r="I24" s="8" t="n">
+        <f aca="false">ABS(F24-H24)</f>
         <v>35</v>
       </c>
-      <c r="H24" s="11" t="n">
+      <c r="J24" s="11" t="n">
         <v>0.131</v>
       </c>
-      <c r="I24" s="11" t="n">
+      <c r="K24" s="11" t="n">
         <v>0.212</v>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="L24" s="11" t="n">
         <v>0.658</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>81</v>
+      <c r="M24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="O24" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" s="8" t="n">
+      <c r="G25" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="G25" s="8" t="n">
-        <f aca="false">ABS(D25-F25)</f>
+      <c r="I25" s="8" t="n">
+        <f aca="false">ABS(F25-H25)</f>
         <v>77</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="J25" s="11" t="n">
         <v>0.791</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="K25" s="11" t="n">
         <v>0.156</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="L25" s="11" t="n">
         <v>0.054</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>80</v>
+      <c r="M25" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="8" t="n">
+      <c r="G26" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <f aca="false">ABS(D26-F26)</f>
+      <c r="I26" s="8" t="n">
+        <f aca="false">ABS(F26-H26)</f>
         <v>76</v>
       </c>
-      <c r="H26" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>0.788</v>
       </c>
-      <c r="I26" s="11" t="n">
+      <c r="K26" s="11" t="n">
         <v>0.157</v>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="L26" s="11" t="n">
         <v>0.055</v>
       </c>
-      <c r="K26" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>81</v>
+      <c r="M26" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="O26" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" s="8" t="n">
+      <c r="G27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <f aca="false">ABS(D27-F27)</f>
+      <c r="I27" s="8" t="n">
+        <f aca="false">ABS(F27-H27)</f>
         <v>36</v>
       </c>
-      <c r="H27" s="11" t="n">
+      <c r="J27" s="11" t="n">
         <v>0.128</v>
       </c>
-      <c r="I27" s="11" t="n">
+      <c r="K27" s="11" t="n">
         <v>0.21</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="L27" s="11" t="n">
         <v>0.661</v>
       </c>
-      <c r="K27" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>80</v>
+      <c r="M27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <f aca="false">ABS(F28-H28)</f>
         <v>72</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="G28" s="8" t="n">
-        <f aca="false">ABS(D28-F28)</f>
-        <v>72</v>
-      </c>
-      <c r="H28" s="11" t="n">
+      <c r="J28" s="11" t="n">
         <v>0.759</v>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="K28" s="11" t="n">
         <v>0.171</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="L28" s="11" t="n">
         <v>0.07</v>
       </c>
-      <c r="K28" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>88</v>
+      <c r="M28" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="O28" s="10" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F29" s="8" t="n">
+      <c r="G29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H29" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <f aca="false">ABS(D29-F29)</f>
+      <c r="I29" s="8" t="n">
+        <f aca="false">ABS(F29-H29)</f>
         <v>10</v>
       </c>
-      <c r="H29" s="11" t="n">
+      <c r="J29" s="11" t="n">
         <v>0.307</v>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="K29" s="11" t="n">
         <v>0.261</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="L29" s="11" t="n">
         <v>0.432</v>
       </c>
-      <c r="K29" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>92</v>
+      <c r="M29" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D30" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F30" s="8" t="n">
+      <c r="G30" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H30" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="G30" s="8" t="n">
-        <f aca="false">ABS(D30-F30)</f>
+      <c r="I30" s="8" t="n">
+        <f aca="false">ABS(F30-H30)</f>
         <v>23</v>
       </c>
-      <c r="H30" s="11" t="n">
+      <c r="J30" s="11" t="n">
         <v>0.584</v>
       </c>
-      <c r="I30" s="11" t="n">
+      <c r="K30" s="11" t="n">
         <v>0.234</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="L30" s="11" t="n">
         <v>0.182</v>
       </c>
-      <c r="K30" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>88</v>
+      <c r="M30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N30" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="O30" s="10" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F31" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="8" t="n">
+      <c r="G31" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="G31" s="8" t="n">
-        <f aca="false">ABS(D31-F31)</f>
+      <c r="I31" s="8" t="n">
+        <f aca="false">ABS(F31-H31)</f>
         <v>59</v>
       </c>
-      <c r="H31" s="11" t="n">
+      <c r="J31" s="11" t="n">
         <v>0.618</v>
       </c>
-      <c r="I31" s="11" t="n">
+      <c r="K31" s="11" t="n">
         <v>0.225</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="L31" s="11" t="n">
         <v>0.158</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>92</v>
+      <c r="M31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="O31" s="10" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="C32" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F32" s="8" t="n">
+      <c r="G32" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G32" s="8" t="n">
-        <f aca="false">ABS(D32-F32)</f>
+      <c r="I32" s="8" t="n">
+        <f aca="false">ABS(F32-H32)</f>
         <v>13</v>
       </c>
-      <c r="H32" s="11" t="n">
+      <c r="J32" s="11" t="n">
         <v>0.233</v>
       </c>
-      <c r="I32" s="11" t="n">
+      <c r="K32" s="11" t="n">
         <v>0.249</v>
       </c>
-      <c r="J32" s="11" t="n">
+      <c r="L32" s="11" t="n">
         <v>0.518</v>
       </c>
-      <c r="K32" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>88</v>
+      <c r="M32" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="O32" s="10" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>82</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="8" t="n">
+      <c r="G33" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="G33" s="8" t="n">
-        <f aca="false">ABS(D33-F33)</f>
+      <c r="I33" s="8" t="n">
+        <f aca="false">ABS(F33-H33)</f>
         <v>49</v>
       </c>
-      <c r="H33" s="11" t="n">
+      <c r="J33" s="11" t="n">
         <v>0.206</v>
       </c>
-      <c r="I33" s="11" t="n">
+      <c r="K33" s="11" t="n">
         <v>0.242</v>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="L33" s="11" t="n">
         <v>0.553</v>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>91</v>
+      <c r="M33" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F34" s="8" t="n">
+      <c r="G34" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H34" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G34" s="8" t="n">
-        <f aca="false">ABS(D34-F34)</f>
+      <c r="I34" s="8" t="n">
+        <f aca="false">ABS(F34-H34)</f>
         <v>10</v>
       </c>
-      <c r="H34" s="11" t="n">
+      <c r="J34" s="11" t="n">
         <v>0.473</v>
       </c>
-      <c r="I34" s="11" t="n">
+      <c r="K34" s="11" t="n">
         <v>0.256</v>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="L34" s="11" t="n">
         <v>0.27</v>
       </c>
-      <c r="K34" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L34" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>97</v>
+      <c r="M34" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="O34" s="10" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" s="8" t="n">
+        <v>108</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="E35" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="F35" s="8" t="n">
+      <c r="G35" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="G35" s="8" t="n">
-        <f aca="false">ABS(D35-F35)</f>
+      <c r="I35" s="8" t="n">
+        <f aca="false">ABS(F35-H35)</f>
         <v>7</v>
       </c>
-      <c r="H35" s="11" t="n">
+      <c r="J35" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="K35" s="11" t="n">
         <v>0.263</v>
       </c>
-      <c r="J35" s="11" t="n">
+      <c r="L35" s="11" t="n">
         <v>0.336</v>
       </c>
-      <c r="K35" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L35" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M35" s="13" t="s">
-        <v>67</v>
+      <c r="M35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N35" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O35" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="D36" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="8" t="n">
+      <c r="G36" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="G36" s="8" t="n">
-        <f aca="false">ABS(D36-F36)</f>
+      <c r="I36" s="8" t="n">
+        <f aca="false">ABS(F36-H36)</f>
         <v>30</v>
       </c>
-      <c r="H36" s="11" t="n">
+      <c r="J36" s="11" t="n">
         <v>0.635</v>
       </c>
-      <c r="I36" s="11" t="n">
+      <c r="K36" s="11" t="n">
         <v>0.219</v>
       </c>
-      <c r="J36" s="11" t="n">
+      <c r="L36" s="11" t="n">
         <v>0.146</v>
       </c>
-      <c r="K36" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L36" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="M36" s="9" t="s">
-        <v>97</v>
+      <c r="M36" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="O36" s="10" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F37" s="8" t="n">
+      <c r="G37" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H37" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="G37" s="8" t="n">
-        <f aca="false">ABS(D37-F37)</f>
+      <c r="I37" s="8" t="n">
+        <f aca="false">ABS(F37-H37)</f>
         <v>27</v>
       </c>
-      <c r="H37" s="11" t="n">
+      <c r="J37" s="11" t="n">
         <v>0.198</v>
       </c>
-      <c r="I37" s="11" t="n">
+      <c r="K37" s="11" t="n">
         <v>0.24</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="L37" s="11" t="n">
         <v>0.563</v>
       </c>
-      <c r="K37" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>98</v>
+      <c r="M37" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F38" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" s="8" t="n">
+      <c r="G38" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H38" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="G38" s="8" t="n">
-        <f aca="false">ABS(D38-F38)</f>
+      <c r="I38" s="8" t="n">
+        <f aca="false">ABS(F38-H38)</f>
         <v>20</v>
       </c>
-      <c r="H38" s="11" t="n">
+      <c r="J38" s="11" t="n">
         <v>0.529</v>
       </c>
-      <c r="I38" s="11" t="n">
+      <c r="K38" s="11" t="n">
         <v>0.247</v>
       </c>
-      <c r="J38" s="11" t="n">
+      <c r="L38" s="11" t="n">
         <v>0.224</v>
       </c>
-      <c r="K38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L38" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="M38" s="9" t="s">
-        <v>98</v>
+      <c r="M38" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N38" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="O38" s="10" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F39" s="8" t="n">
+      <c r="G39" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <f aca="false">ABS(D39-F39)</f>
+      <c r="I39" s="8" t="n">
+        <f aca="false">ABS(F39-H39)</f>
         <v>37</v>
       </c>
-      <c r="H39" s="11" t="n">
+      <c r="J39" s="11" t="n">
         <v>0.124</v>
       </c>
-      <c r="I39" s="11" t="n">
+      <c r="K39" s="11" t="n">
         <v>0.208</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="L39" s="11" t="n">
         <v>0.667</v>
       </c>
-      <c r="K39" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>97</v>
+      <c r="M39" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="O39" s="10" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="E40" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F40" s="8" t="n">
+      <c r="G40" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="G40" s="8" t="n">
-        <f aca="false">ABS(D40-F40)</f>
+      <c r="I40" s="8" t="n">
+        <f aca="false">ABS(F40-H40)</f>
         <v>45</v>
       </c>
-      <c r="H40" s="11" t="n">
+      <c r="J40" s="11" t="n">
         <v>0.145</v>
       </c>
-      <c r="I40" s="11" t="n">
+      <c r="K40" s="11" t="n">
         <v>0.219</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="L40" s="11" t="n">
         <v>0.636</v>
       </c>
-      <c r="K40" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L40" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="M40" s="9" t="s">
-        <v>106</v>
+      <c r="M40" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N40" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="O40" s="10" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F41" s="8" t="n">
+      <c r="G41" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <f aca="false">ABS(D41-F41)</f>
+      <c r="I41" s="8" t="n">
+        <f aca="false">ABS(F41-H41)</f>
         <v>65</v>
       </c>
-      <c r="H41" s="11" t="n">
+      <c r="J41" s="11" t="n">
         <v>0.848</v>
       </c>
-      <c r="I41" s="11" t="n">
+      <c r="K41" s="11" t="n">
         <v>0.125</v>
       </c>
-      <c r="J41" s="11" t="n">
+      <c r="L41" s="11" t="n">
         <v>0.028</v>
       </c>
-      <c r="K41" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>108</v>
+      <c r="M41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="O41" s="10" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F42" s="8" t="n">
+      <c r="G42" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H42" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="G42" s="8" t="n">
-        <f aca="false">ABS(D42-F42)</f>
+      <c r="I42" s="8" t="n">
+        <f aca="false">ABS(F42-H42)</f>
         <v>59</v>
       </c>
-      <c r="H42" s="11" t="n">
+      <c r="J42" s="11" t="n">
         <v>0.833</v>
       </c>
-      <c r="I42" s="11" t="n">
+      <c r="K42" s="11" t="n">
         <v>0.133</v>
       </c>
-      <c r="J42" s="11" t="n">
+      <c r="L42" s="11" t="n">
         <v>0.034</v>
       </c>
-      <c r="K42" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L42" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="M42" s="9" t="s">
-        <v>108</v>
+      <c r="M42" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="O42" s="10" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D43" s="8" t="n">
+      <c r="E43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F43" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F43" s="8" t="n">
+      <c r="G43" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="H43" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="G43" s="8" t="n">
-        <f aca="false">ABS(D43-F43)</f>
+      <c r="I43" s="8" t="n">
+        <f aca="false">ABS(F43-H43)</f>
         <v>51</v>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="J43" s="11" t="n">
         <v>0.656</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="K43" s="11" t="n">
         <v>0.212</v>
       </c>
-      <c r="J43" s="11" t="n">
+      <c r="L43" s="11" t="n">
         <v>0.132</v>
       </c>
-      <c r="K43" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>106</v>
+      <c r="M43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="O43" s="10" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D44" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F44" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F44" s="8" t="n">
+      <c r="G44" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="G44" s="8" t="n">
-        <f aca="false">ABS(D44-F44)</f>
+      <c r="I44" s="8" t="n">
+        <f aca="false">ABS(F44-H44)</f>
         <v>6</v>
       </c>
-      <c r="H44" s="11" t="n">
+      <c r="J44" s="11" t="n">
         <v>0.349</v>
       </c>
-      <c r="I44" s="11" t="n">
+      <c r="K44" s="11" t="n">
         <v>0.264</v>
       </c>
-      <c r="J44" s="11" t="n">
+      <c r="L44" s="11" t="n">
         <v>0.387</v>
       </c>
-      <c r="K44" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L44" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M44" s="13" t="s">
-        <v>67</v>
+      <c r="M44" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O44" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D45" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F45" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F45" s="8" t="n">
+      <c r="G45" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H45" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="8" t="n">
-        <f aca="false">ABS(D45-F45)</f>
+      <c r="I45" s="8" t="n">
+        <f aca="false">ABS(F45-H45)</f>
         <v>14</v>
       </c>
-      <c r="H45" s="11" t="n">
+      <c r="J45" s="11" t="n">
         <v>0.177</v>
       </c>
-      <c r="I45" s="11" t="n">
+      <c r="K45" s="11" t="n">
         <v>0.232</v>
       </c>
-      <c r="J45" s="11" t="n">
+      <c r="L45" s="11" t="n">
         <v>0.59</v>
       </c>
-      <c r="K45" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>108</v>
+      <c r="M45" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F46" s="8" t="n">
+      <c r="G46" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="H46" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <f aca="false">ABS(D46-F46)</f>
+      <c r="I46" s="8" t="n">
+        <f aca="false">ABS(F46-H46)</f>
         <v>20</v>
       </c>
-      <c r="H46" s="11" t="n">
+      <c r="J46" s="11" t="n">
         <v>0.562</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="K46" s="11" t="n">
         <v>0.24</v>
       </c>
-      <c r="J46" s="11" t="n">
+      <c r="L46" s="11" t="n">
         <v>0.199</v>
       </c>
-      <c r="K46" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L46" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="M46" s="9" t="s">
-        <v>113</v>
+      <c r="M46" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="O46" s="10" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D47" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="F47" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E47" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="F47" s="8" t="n">
+      <c r="G47" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H47" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="G47" s="8" t="n">
-        <f aca="false">ABS(D47-F47)</f>
+      <c r="I47" s="8" t="n">
+        <f aca="false">ABS(F47-H47)</f>
         <v>65</v>
       </c>
-      <c r="H47" s="11" t="n">
+      <c r="J47" s="11" t="n">
         <v>0.662</v>
       </c>
-      <c r="I47" s="11" t="n">
+      <c r="K47" s="11" t="n">
         <v>0.21</v>
       </c>
-      <c r="J47" s="11" t="n">
+      <c r="L47" s="11" t="n">
         <v>0.128</v>
       </c>
-      <c r="K47" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="M47" s="9" t="s">
-        <v>117</v>
+      <c r="M47" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="O47" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D48" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F48" s="8" t="n">
+      <c r="G48" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H48" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G48" s="8" t="n">
-        <f aca="false">ABS(D48-F48)</f>
+      <c r="I48" s="8" t="n">
+        <f aca="false">ABS(F48-H48)</f>
         <v>11</v>
       </c>
-      <c r="H48" s="11" t="n">
+      <c r="J48" s="11" t="n">
         <v>0.489</v>
       </c>
-      <c r="I48" s="11" t="n">
+      <c r="K48" s="11" t="n">
         <v>0.254</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="L48" s="11" t="n">
         <v>0.257</v>
       </c>
-      <c r="K48" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L48" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="M48" s="9" t="s">
-        <v>113</v>
+      <c r="M48" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="E49" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F49" s="8" t="n">
+      <c r="G49" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H49" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="G49" s="8" t="n">
-        <f aca="false">ABS(D49-F49)</f>
+      <c r="I49" s="8" t="n">
+        <f aca="false">ABS(F49-H49)</f>
         <v>56</v>
       </c>
-      <c r="H49" s="11" t="n">
+      <c r="J49" s="11" t="n">
         <v>0.176</v>
       </c>
-      <c r="I49" s="11" t="n">
+      <c r="K49" s="11" t="n">
         <v>0.232</v>
       </c>
-      <c r="J49" s="11" t="n">
+      <c r="L49" s="11" t="n">
         <v>0.591</v>
       </c>
-      <c r="K49" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L49" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="M49" s="9" t="s">
-        <v>114</v>
+      <c r="M49" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="O49" s="10" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F50" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F50" s="8" t="n">
+      <c r="G50" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H50" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G50" s="8" t="n">
-        <f aca="false">ABS(D50-F50)</f>
+      <c r="I50" s="8" t="n">
+        <f aca="false">ABS(F50-H50)</f>
         <v>9</v>
       </c>
-      <c r="H50" s="11" t="n">
+      <c r="J50" s="11" t="n">
         <v>0.301</v>
       </c>
-      <c r="I50" s="11" t="n">
+      <c r="K50" s="11" t="n">
         <v>0.26</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="L50" s="11" t="n">
         <v>0.439</v>
       </c>
-      <c r="K50" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L50" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="M50" s="9" t="s">
-        <v>117</v>
+      <c r="M50" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N50" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="O50" s="10" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F51" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F51" s="8" t="n">
+      <c r="G51" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H51" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G51" s="8" t="n">
-        <f aca="false">ABS(D51-F51)</f>
+      <c r="I51" s="8" t="n">
+        <f aca="false">ABS(F51-H51)</f>
         <v>76</v>
       </c>
-      <c r="H51" s="11" t="n">
+      <c r="J51" s="11" t="n">
         <v>0.063</v>
       </c>
-      <c r="I51" s="11" t="n">
+      <c r="K51" s="11" t="n">
         <v>0.164</v>
       </c>
-      <c r="J51" s="11" t="n">
+      <c r="L51" s="11" t="n">
         <v>0.773</v>
       </c>
-      <c r="K51" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>113</v>
+      <c r="M51" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N51" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D52" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E52" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="F52" s="8" t="n">
+      <c r="G52" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H52" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G52" s="8" t="n">
-        <f aca="false">ABS(D52-F52)</f>
+      <c r="I52" s="8" t="n">
+        <f aca="false">ABS(F52-H52)</f>
         <v>12</v>
       </c>
-      <c r="H52" s="11" t="n">
+      <c r="J52" s="11" t="n">
         <v>0.583</v>
       </c>
-      <c r="I52" s="11" t="n">
+      <c r="K52" s="11" t="n">
         <v>0.234</v>
       </c>
-      <c r="J52" s="11" t="n">
+      <c r="L52" s="11" t="n">
         <v>0.183</v>
       </c>
-      <c r="K52" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L52" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="M52" s="9" t="s">
-        <v>124</v>
+      <c r="M52" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="O52" s="10" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D53" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F53" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F53" s="8" t="n">
+      <c r="G53" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H53" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="G53" s="8" t="n">
-        <f aca="false">ABS(D53-F53)</f>
+      <c r="I53" s="8" t="n">
+        <f aca="false">ABS(F53-H53)</f>
         <v>26</v>
       </c>
-      <c r="H53" s="11" t="n">
+      <c r="J53" s="11" t="n">
         <v>0.264</v>
       </c>
-      <c r="I53" s="11" t="n">
+      <c r="K53" s="11" t="n">
         <v>0.255</v>
       </c>
-      <c r="J53" s="11" t="n">
+      <c r="L53" s="11" t="n">
         <v>0.481</v>
       </c>
-      <c r="K53" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L53" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="M53" s="9" t="s">
-        <v>128</v>
+      <c r="M53" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D54" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="F54" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E54" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F54" s="8" t="n">
+      <c r="G54" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H54" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G54" s="8" t="n">
-        <f aca="false">ABS(D54-F54)</f>
+      <c r="I54" s="8" t="n">
+        <f aca="false">ABS(F54-H54)</f>
         <v>54</v>
       </c>
-      <c r="H54" s="11" t="n">
+      <c r="J54" s="11" t="n">
         <v>0.821</v>
       </c>
-      <c r="I54" s="11" t="n">
+      <c r="K54" s="11" t="n">
         <v>0.14</v>
       </c>
-      <c r="J54" s="11" t="n">
+      <c r="L54" s="11" t="n">
         <v>0.039</v>
       </c>
-      <c r="K54" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L54" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="M54" s="9" t="s">
-        <v>124</v>
+      <c r="M54" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N54" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="O54" s="10" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F55" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="F55" s="8" t="n">
+      <c r="G55" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H55" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="G55" s="8" t="n">
-        <f aca="false">ABS(D55-F55)</f>
+      <c r="I55" s="8" t="n">
+        <f aca="false">ABS(F55-H55)</f>
         <v>16</v>
       </c>
-      <c r="H55" s="11" t="n">
+      <c r="J55" s="11" t="n">
         <v>0.236</v>
       </c>
-      <c r="I55" s="11" t="n">
+      <c r="K55" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="J55" s="11" t="n">
+      <c r="L55" s="11" t="n">
         <v>0.515</v>
       </c>
-      <c r="K55" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>125</v>
+      <c r="M55" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F56" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F56" s="8" t="n">
+      <c r="G56" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G56" s="8" t="n">
-        <f aca="false">ABS(D56-F56)</f>
+      <c r="I56" s="8" t="n">
+        <f aca="false">ABS(F56-H56)</f>
         <v>28</v>
       </c>
-      <c r="H56" s="11" t="n">
+      <c r="J56" s="11" t="n">
         <v>0.09</v>
       </c>
-      <c r="I56" s="11" t="n">
+      <c r="K56" s="11" t="n">
         <v>0.186</v>
       </c>
-      <c r="J56" s="11" t="n">
+      <c r="L56" s="11" t="n">
         <v>0.724</v>
       </c>
-      <c r="K56" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L56" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="M56" s="9" t="s">
-        <v>124</v>
+      <c r="M56" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N56" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="O56" s="10" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="D57" s="8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="F57" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F57" s="8" t="n">
+      <c r="G57" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H57" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G57" s="8" t="n">
-        <f aca="false">ABS(D57-F57)</f>
+      <c r="I57" s="8" t="n">
+        <f aca="false">ABS(F57-H57)</f>
         <v>42</v>
       </c>
-      <c r="H57" s="11" t="n">
+      <c r="J57" s="11" t="n">
         <v>0.629</v>
       </c>
-      <c r="I57" s="11" t="n">
+      <c r="K57" s="11" t="n">
         <v>0.221</v>
       </c>
-      <c r="J57" s="11" t="n">
+      <c r="L57" s="11" t="n">
         <v>0.15</v>
       </c>
-      <c r="K57" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>125</v>
+      <c r="M57" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="O57" s="10" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D58" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F58" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E58" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="F58" s="8" t="n">
+      <c r="G58" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H58" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G58" s="8" t="n">
-        <f aca="false">ABS(D58-F58)</f>
+      <c r="I58" s="8" t="n">
+        <f aca="false">ABS(F58-H58)</f>
         <v>7</v>
       </c>
-      <c r="H58" s="11" t="n">
+      <c r="J58" s="11" t="n">
         <v>0.488</v>
       </c>
-      <c r="I58" s="11" t="n">
+      <c r="K58" s="11" t="n">
         <v>0.254</v>
       </c>
-      <c r="J58" s="11" t="n">
+      <c r="L58" s="11" t="n">
         <v>0.258</v>
       </c>
-      <c r="K58" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L58" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="M58" s="9" t="s">
-        <v>134</v>
+      <c r="M58" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N58" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="O58" s="10" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F59" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="E59" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F59" s="8" t="n">
+      <c r="G59" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H59" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="G59" s="8" t="n">
-        <f aca="false">ABS(D59-F59)</f>
+      <c r="I59" s="8" t="n">
+        <f aca="false">ABS(F59-H59)</f>
         <v>39</v>
       </c>
-      <c r="H59" s="11" t="n">
+      <c r="J59" s="11" t="n">
         <v>0.235</v>
       </c>
-      <c r="I59" s="11" t="n">
+      <c r="K59" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="J59" s="11" t="n">
+      <c r="L59" s="11" t="n">
         <v>0.516</v>
       </c>
-      <c r="K59" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="M59" s="9" t="s">
-        <v>138</v>
+      <c r="M59" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="O59" s="10" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D60" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F60" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F60" s="8" t="n">
+      <c r="G60" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H60" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="G60" s="8" t="n">
-        <f aca="false">ABS(D60-F60)</f>
+      <c r="I60" s="8" t="n">
+        <f aca="false">ABS(F60-H60)</f>
         <v>69</v>
       </c>
-      <c r="H60" s="11" t="n">
+      <c r="J60" s="11" t="n">
         <v>0.821</v>
       </c>
-      <c r="I60" s="11" t="n">
+      <c r="K60" s="11" t="n">
         <v>0.14</v>
       </c>
-      <c r="J60" s="11" t="n">
+      <c r="L60" s="11" t="n">
         <v>0.039</v>
       </c>
-      <c r="K60" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L60" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="M60" s="9" t="s">
-        <v>134</v>
+      <c r="M60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N60" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="O60" s="10" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F61" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="E61" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" s="8" t="n">
+      <c r="G61" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="H61" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G61" s="8" t="n">
-        <f aca="false">ABS(D61-F61)</f>
+      <c r="I61" s="8" t="n">
+        <f aca="false">ABS(F61-H61)</f>
         <v>23</v>
       </c>
-      <c r="H61" s="11" t="n">
+      <c r="J61" s="11" t="n">
         <v>0.189</v>
       </c>
-      <c r="I61" s="11" t="n">
+      <c r="K61" s="11" t="n">
         <v>0.237</v>
       </c>
-      <c r="J61" s="11" t="n">
+      <c r="L61" s="11" t="n">
         <v>0.575</v>
       </c>
-      <c r="K61" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>135</v>
+      <c r="M61" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="O61" s="10" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D62" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F62" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E62" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F62" s="8" t="n">
+      <c r="G62" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="H62" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="G62" s="8" t="n">
-        <f aca="false">ABS(D62-F62)</f>
+      <c r="I62" s="8" t="n">
+        <f aca="false">ABS(F62-H62)</f>
         <v>62</v>
       </c>
-      <c r="H62" s="11" t="n">
+      <c r="J62" s="11" t="n">
         <v>0.718</v>
       </c>
-      <c r="I62" s="11" t="n">
+      <c r="K62" s="11" t="n">
         <v>0.189</v>
       </c>
-      <c r="J62" s="11" t="n">
+      <c r="L62" s="11" t="n">
         <v>0.093</v>
       </c>
-      <c r="K62" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L62" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="M62" s="9" t="s">
-        <v>135</v>
+      <c r="M62" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N62" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="O62" s="10" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D63" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F63" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="E63" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F63" s="8" t="n">
+      <c r="G63" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H63" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G63" s="8" t="n">
-        <f aca="false">ABS(D63-F63)</f>
+      <c r="I63" s="8" t="n">
+        <f aca="false">ABS(F63-H63)</f>
         <v>30</v>
       </c>
-      <c r="H63" s="11" t="n">
+      <c r="J63" s="11" t="n">
         <v>0.109</v>
       </c>
-      <c r="I63" s="11" t="n">
+      <c r="K63" s="11" t="n">
         <v>0.199</v>
       </c>
-      <c r="J63" s="11" t="n">
+      <c r="L63" s="11" t="n">
         <v>0.693</v>
       </c>
-      <c r="K63" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="M63" s="9" t="s">
-        <v>134</v>
+      <c r="M63" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="O63" s="10" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D64" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F64" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E64" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F64" s="8" t="n">
+      <c r="G64" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H64" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="G64" s="8" t="n">
-        <f aca="false">ABS(D64-F64)</f>
+      <c r="I64" s="8" t="n">
+        <f aca="false">ABS(F64-H64)</f>
         <v>41</v>
       </c>
-      <c r="H64" s="11" t="n">
+      <c r="J64" s="11" t="n">
         <v>0.682</v>
       </c>
-      <c r="I64" s="11" t="n">
+      <c r="K64" s="11" t="n">
         <v>0.203</v>
       </c>
-      <c r="J64" s="11" t="n">
+      <c r="L64" s="11" t="n">
         <v>0.115</v>
       </c>
-      <c r="K64" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L64" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="M64" s="9" t="s">
-        <v>142</v>
+      <c r="M64" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N64" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="O64" s="10" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D65" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>50</v>
       </c>
+      <c r="D65" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="E65" s="9" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="F65" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H65" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="G65" s="8" t="n">
-        <f aca="false">ABS(D65-F65)</f>
+      <c r="I65" s="8" t="n">
+        <f aca="false">ABS(F65-H65)</f>
         <v>37</v>
       </c>
-      <c r="H65" s="11" t="n">
+      <c r="J65" s="11" t="n">
         <v>0.156</v>
       </c>
-      <c r="I65" s="11" t="n">
+      <c r="K65" s="11" t="n">
         <v>0.224</v>
       </c>
-      <c r="J65" s="11" t="n">
+      <c r="L65" s="11" t="n">
         <v>0.62</v>
       </c>
-      <c r="K65" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="M65" s="9" t="s">
-        <v>146</v>
+      <c r="M65" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="O65" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D66" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F66" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F66" s="8" t="n">
+      <c r="G66" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H66" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G66" s="8" t="n">
-        <f aca="false">ABS(D66-F66)</f>
+      <c r="I66" s="8" t="n">
+        <f aca="false">ABS(F66-H66)</f>
         <v>45</v>
       </c>
-      <c r="H66" s="11" t="n">
+      <c r="J66" s="11" t="n">
         <v>0.696</v>
       </c>
-      <c r="I66" s="11" t="n">
+      <c r="K66" s="11" t="n">
         <v>0.198</v>
       </c>
-      <c r="J66" s="11" t="n">
+      <c r="L66" s="11" t="n">
         <v>0.107</v>
       </c>
-      <c r="K66" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L66" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="M66" s="9" t="s">
-        <v>142</v>
+      <c r="M66" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N66" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="O66" s="10" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="D67" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F67" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F67" s="8" t="n">
+      <c r="G67" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H67" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="G67" s="8" t="n">
-        <f aca="false">ABS(D67-F67)</f>
+      <c r="I67" s="8" t="n">
+        <f aca="false">ABS(F67-H67)</f>
         <v>33</v>
       </c>
-      <c r="H67" s="11" t="n">
+      <c r="J67" s="11" t="n">
         <v>0.606</v>
       </c>
-      <c r="I67" s="11" t="n">
+      <c r="K67" s="11" t="n">
         <v>0.228</v>
       </c>
-      <c r="J67" s="11" t="n">
+      <c r="L67" s="11" t="n">
         <v>0.166</v>
       </c>
-      <c r="K67" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>146</v>
+      <c r="M67" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D68" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F68" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="E68" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F68" s="8" t="n">
+      <c r="G68" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H68" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G68" s="8" t="n">
-        <f aca="false">ABS(D68-F68)</f>
+      <c r="I68" s="8" t="n">
+        <f aca="false">ABS(F68-H68)</f>
         <v>8</v>
       </c>
-      <c r="H68" s="11" t="n">
+      <c r="J68" s="11" t="n">
         <v>0.295</v>
       </c>
-      <c r="I68" s="11" t="n">
+      <c r="K68" s="11" t="n">
         <v>0.26</v>
       </c>
-      <c r="J68" s="11" t="n">
+      <c r="L68" s="11" t="n">
         <v>0.445</v>
       </c>
-      <c r="K68" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="L68" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="M68" s="9" t="s">
-        <v>142</v>
+      <c r="M68" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="O68" s="10" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D69" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F69" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="E69" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F69" s="8" t="n">
+      <c r="G69" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H69" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="G69" s="8" t="n">
-        <f aca="false">ABS(D69-F69)</f>
+      <c r="I69" s="8" t="n">
+        <f aca="false">ABS(F69-H69)</f>
         <v>4</v>
       </c>
-      <c r="H69" s="11" t="n">
+      <c r="J69" s="11" t="n">
         <v>0.382</v>
       </c>
-      <c r="I69" s="11" t="n">
+      <c r="K69" s="11" t="n">
         <v>0.264</v>
       </c>
-      <c r="J69" s="11" t="n">
+      <c r="L69" s="11" t="n">
         <v>0.354</v>
       </c>
-      <c r="K69" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L69" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M69" s="13" t="s">
-        <v>67</v>
+      <c r="M69" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N69" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O69" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D70" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F70" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F70" s="8" t="n">
+      <c r="G70" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H70" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="G70" s="8" t="n">
-        <f aca="false">ABS(D70-F70)</f>
+      <c r="I70" s="8" t="n">
+        <f aca="false">ABS(F70-H70)</f>
         <v>27</v>
       </c>
-      <c r="H70" s="11" t="n">
+      <c r="J70" s="11" t="n">
         <v>0.708</v>
       </c>
-      <c r="I70" s="11" t="n">
+      <c r="K70" s="11" t="n">
         <v>0.193</v>
       </c>
-      <c r="J70" s="11" t="n">
+      <c r="L70" s="11" t="n">
         <v>0.099</v>
       </c>
-      <c r="K70" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="L70" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="M70" s="9" t="s">
-        <v>149</v>
+      <c r="M70" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="N70" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="O70" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D71" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F71" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="E71" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="F71" s="8" t="n">
+      <c r="G71" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="H71" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="G71" s="8" t="n">
-        <f aca="false">ABS(D71-F71)</f>
+      <c r="I71" s="8" t="n">
+        <f aca="false">ABS(F71-H71)</f>
         <v>39</v>
       </c>
-      <c r="H71" s="11" t="n">
+      <c r="J71" s="11" t="n">
         <v>0.549</v>
       </c>
-      <c r="I71" s="11" t="n">
+      <c r="K71" s="11" t="n">
         <v>0.243</v>
       </c>
-      <c r="J71" s="11" t="n">
+      <c r="L71" s="11" t="n">
         <v>0.208</v>
       </c>
-      <c r="K71" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="M71" s="9" t="s">
-        <v>152</v>
+      <c r="M71" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="D72" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F72" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F72" s="8" t="n">
+      <c r="G72" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H72" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="G72" s="8" t="n">
-        <f aca="false">ABS(D72-F72)</f>
+      <c r="I72" s="8" t="n">
+        <f aca="false">ABS(F72-H72)</f>
         <v>23</v>
       </c>
-      <c r="H72" s="11" t="n">
+      <c r="J72" s="11" t="n">
         <v>0.683</v>
       </c>
-      <c r="I72" s="11" t="n">
+      <c r="K72" s="11" t="n">
         <v>0.202</v>
       </c>
-      <c r="J72" s="11" t="n">
+      <c r="L72" s="11" t="n">
         <v>0.114</v>
       </c>
-      <c r="K72" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L72" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="M72" s="9" t="s">
-        <v>149</v>
+      <c r="M72" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="O72" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D73" s="8" t="n">
+        <v>158</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F73" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="E73" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F73" s="8" t="n">
+      <c r="G73" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="H73" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="G73" s="8" t="n">
-        <f aca="false">ABS(D73-F73)</f>
+      <c r="I73" s="8" t="n">
+        <f aca="false">ABS(F73-H73)</f>
         <v>35</v>
       </c>
-      <c r="H73" s="11" t="n">
+      <c r="J73" s="11" t="n">
         <v>0.229</v>
       </c>
-      <c r="I73" s="11" t="n">
+      <c r="K73" s="11" t="n">
         <v>0.248</v>
       </c>
-      <c r="J73" s="11" t="n">
+      <c r="L73" s="11" t="n">
         <v>0.522</v>
       </c>
-      <c r="K73" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>150</v>
+      <c r="M73" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D74" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E74" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F74" s="8" t="n">
+      <c r="G74" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H74" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="G74" s="8" t="n">
-        <f aca="false">ABS(D74-F74)</f>
+      <c r="I74" s="8" t="n">
+        <f aca="false">ABS(F74-H74)</f>
         <v>4</v>
       </c>
-      <c r="H74" s="11" t="n">
+      <c r="J74" s="11" t="n">
         <v>0.343</v>
       </c>
-      <c r="I74" s="11" t="n">
+      <c r="K74" s="11" t="n">
         <v>0.263</v>
       </c>
-      <c r="J74" s="11" t="n">
+      <c r="L74" s="11" t="n">
         <v>0.394</v>
       </c>
-      <c r="K74" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L74" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="M74" s="13" t="s">
-        <v>67</v>
+      <c r="M74" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="N74" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="O74" s="13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="D75" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="F75" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="E75" s="9" t="s">
+      <c r="G75" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <f aca="false">ABS(F75-H75)</f>
+        <v>62</v>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L75" s="11" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="M75" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F75" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="8" t="n">
-        <f aca="false">ABS(D75-F75)</f>
-        <v>62</v>
-      </c>
-      <c r="H75" s="11" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="I75" s="11" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J75" s="11" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="K75" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>149</v>
+      <c r="N75" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M75"/>
+  <autoFilter ref="A3:O75"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8287,7 +8816,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -8301,30 +8830,30 @@
         <v>27</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="9" t="s">
         <v>42</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>14</v>
@@ -8344,10 +8873,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>25</v>
@@ -8367,10 +8896,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>53</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>40</v>
@@ -8390,10 +8919,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>60</v>
@@ -8413,10 +8942,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>19</v>
@@ -8436,10 +8965,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>58</v>
+        <v>65</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>30</v>
@@ -8459,10 +8988,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>56</v>
@@ -8482,10 +9011,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>64</v>
@@ -8505,10 +9034,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>69</v>
+        <v>82</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>17</v>
@@ -8528,10 +9057,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>22</v>
@@ -8551,10 +9080,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>73</v>
+        <v>82</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>27</v>
@@ -8574,10 +9103,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>41</v>
@@ -8597,10 +9126,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>80</v>
+        <v>94</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>96</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>6</v>
@@ -8620,10 +9149,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>81</v>
+        <v>94</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>7</v>
@@ -8643,10 +9172,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>42</v>
@@ -8666,10 +9195,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>83</v>
@@ -8689,10 +9218,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>88</v>
+        <v>107</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>10</v>
@@ -8712,10 +9241,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>92</v>
+        <v>107</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>23</v>
@@ -8735,10 +9264,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>91</v>
+        <v>107</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>33</v>
@@ -8758,10 +9287,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>82</v>
@@ -8781,10 +9310,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>97</v>
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>8</v>
@@ -8804,10 +9333,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>98</v>
+        <v>123</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>126</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>18</v>
@@ -8827,10 +9356,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>38</v>
@@ -8850,10 +9379,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>45</v>
@@ -8873,10 +9402,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>108</v>
+        <v>131</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>2</v>
@@ -8896,10 +9425,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>106</v>
+        <v>131</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>16</v>
@@ -8919,10 +9448,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>61</v>
@@ -8942,10 +9471,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>67</v>
@@ -8965,10 +9494,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>113</v>
+        <v>141</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>142</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>9</v>
@@ -8988,10 +9517,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>117</v>
+        <v>141</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>145</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>20</v>
@@ -9011,10 +9540,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>114</v>
+        <v>141</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>143</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>29</v>
@@ -9034,10 +9563,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>85</v>
@@ -9057,10 +9586,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>124</v>
+        <v>150</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>152</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>3</v>
@@ -9080,10 +9609,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>125</v>
+        <v>150</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>153</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>15</v>
@@ -9103,10 +9632,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>31</v>
@@ -9126,10 +9655,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>57</v>
@@ -9149,10 +9678,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>134</v>
+        <v>161</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>4</v>
@@ -9172,10 +9701,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>135</v>
+        <v>161</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>11</v>
@@ -9195,10 +9724,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>138</v>
+        <v>161</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>167</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>34</v>
@@ -9218,10 +9747,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>73</v>
@@ -9241,10 +9770,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>142</v>
+        <v>172</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>5</v>
@@ -9264,10 +9793,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>146</v>
+        <v>172</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>177</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>13</v>
@@ -9287,10 +9816,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>46</v>
@@ -9310,10 +9839,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>50</v>
@@ -9333,10 +9862,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>149</v>
+        <v>180</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1</v>
@@ -9356,10 +9885,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>152</v>
+        <v>180</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>184</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>24</v>
@@ -9379,10 +9908,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>150</v>
+        <v>180</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>182</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>28</v>
@@ -9402,10 +9931,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
@@ -9449,7 +9978,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -9479,7 +10008,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9488,285 +10017,285 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>172</v>
+        <v>203</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>177</v>
+        <v>208</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>181</v>
+        <v>212</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>185</v>
+        <v>215</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>190</v>
+        <v>220</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>194</v>
+        <v>224</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>198</v>
+        <v>228</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="10"/>
+        <v>233</v>
+      </c>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" s="10"/>
+        <v>236</v>
+      </c>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="E13" s="10"/>
+        <v>239</v>
+      </c>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>213</v>
+        <v>243</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>172</v>
+        <v>246</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>220</v>
+        <v>249</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>225</v>
+        <v>253</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>229</v>
+        <v>257</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>194</v>
+        <v>261</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -9802,7 +10331,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9815,39 +10344,39 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>238</v>
+        <v>267</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>3</v>
@@ -9873,10 +10402,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>1</v>
@@ -9902,10 +10431,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>2</v>
@@ -9931,10 +10460,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>4</v>
@@ -9959,11 +10488,11 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>142</v>
+      <c r="A8" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>5</v>
@@ -9988,11 +10517,11 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>97</v>
+      <c r="A9" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>8</v>
@@ -10017,11 +10546,11 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>80</v>
+      <c r="A10" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>6</v>
@@ -10046,11 +10575,11 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>81</v>
+      <c r="A11" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>7</v>
@@ -10075,11 +10604,11 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>14</v>
@@ -10104,11 +10633,11 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>88</v>
+      <c r="A13" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>10</v>
@@ -10133,11 +10662,11 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>69</v>
+      <c r="A14" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>17</v>
@@ -10162,11 +10691,11 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>113</v>
+      <c r="A15" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>9</v>
@@ -10191,11 +10720,11 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>135</v>
+      <c r="A16" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>11</v>
@@ -10220,11 +10749,11 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>146</v>
+      <c r="A17" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>13</v>
@@ -10249,11 +10778,11 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>125</v>
+      <c r="A18" s="9" t="s">
+        <v>153</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>15</v>
@@ -10278,11 +10807,11 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>106</v>
+      <c r="A19" s="9" t="s">
+        <v>134</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>16</v>
@@ -10307,11 +10836,11 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>98</v>
+      <c r="A20" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>18</v>
@@ -10336,11 +10865,11 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>63</v>
+      <c r="A21" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>19</v>
@@ -10365,11 +10894,11 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>58</v>
+      <c r="A22" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>30</v>
@@ -10394,11 +10923,11 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>74</v>
+      <c r="A23" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>22</v>
@@ -10423,11 +10952,11 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>92</v>
+      <c r="A24" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>23</v>
@@ -10452,11 +10981,11 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>117</v>
+      <c r="A25" s="9" t="s">
+        <v>145</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>20</v>
@@ -10481,11 +11010,11 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>47</v>
+      <c r="A26" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>25</v>
@@ -10510,11 +11039,11 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
-        <v>152</v>
+      <c r="A27" s="9" t="s">
+        <v>184</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>24</v>
@@ -10539,11 +11068,11 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>73</v>
+      <c r="A28" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>27</v>
@@ -10568,11 +11097,11 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
-        <v>150</v>
+      <c r="A29" s="9" t="s">
+        <v>182</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>28</v>
@@ -10597,11 +11126,11 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>114</v>
+      <c r="A30" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>29</v>
@@ -10626,11 +11155,11 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
-        <v>128</v>
+      <c r="A31" s="9" t="s">
+        <v>156</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>31</v>
@@ -10655,11 +11184,11 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
-        <v>91</v>
+      <c r="A32" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>33</v>
@@ -10684,11 +11213,11 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
-        <v>101</v>
+      <c r="A33" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>38</v>
@@ -10713,11 +11242,11 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
-        <v>83</v>
+      <c r="A34" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>42</v>
@@ -10742,11 +11271,11 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
-        <v>48</v>
+      <c r="A35" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>40</v>
@@ -10771,11 +11300,11 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
-        <v>102</v>
+      <c r="A36" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>45</v>
@@ -10800,11 +11329,11 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
-        <v>138</v>
+      <c r="A37" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>34</v>
@@ -10829,11 +11358,11 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="s">
-        <v>127</v>
+      <c r="A38" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>57</v>
@@ -10858,11 +11387,11 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
-        <v>43</v>
+      <c r="A39" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>60</v>
@@ -10887,11 +11416,11 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
-        <v>59</v>
+      <c r="A40" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>64</v>
@@ -10916,11 +11445,11 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="s">
-        <v>62</v>
+      <c r="A41" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>56</v>
@@ -10945,11 +11474,11 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="s">
-        <v>70</v>
+      <c r="A42" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>41</v>
@@ -10974,11 +11503,11 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10" t="s">
-        <v>82</v>
+      <c r="A43" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>83</v>
@@ -11003,11 +11532,11 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="s">
-        <v>89</v>
+      <c r="A44" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>82</v>
@@ -11032,11 +11561,11 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
-        <v>105</v>
+      <c r="A45" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>61</v>
@@ -11061,11 +11590,11 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="s">
-        <v>109</v>
+      <c r="A46" s="9" t="s">
+        <v>137</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>67</v>
@@ -11090,11 +11619,11 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10" t="s">
-        <v>118</v>
+      <c r="A47" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>85</v>
@@ -11119,11 +11648,11 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="s">
-        <v>137</v>
+      <c r="A48" s="9" t="s">
+        <v>166</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>73</v>
@@ -11148,11 +11677,11 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10" t="s">
-        <v>143</v>
+      <c r="A49" s="9" t="s">
+        <v>174</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>46</v>
@@ -11177,11 +11706,11 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10" t="s">
-        <v>145</v>
+      <c r="A50" s="9" t="s">
+        <v>176</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>50</v>
@@ -11206,11 +11735,11 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10" t="s">
-        <v>153</v>
+      <c r="A51" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
@@ -11264,20 +11793,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>240</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B4" s="23" t="n">
         <v>0.189</v>
@@ -11285,7 +11814,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B5" s="23" t="n">
         <v>0.184</v>
@@ -11293,7 +11822,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="B6" s="23" t="n">
         <v>0.163</v>
@@ -11301,7 +11830,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="B7" s="23" t="n">
         <v>0.096</v>
@@ -11309,7 +11838,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="B8" s="23" t="n">
         <v>0.044</v>
@@ -11317,7 +11846,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="B9" s="23" t="n">
         <v>0.04</v>
@@ -11325,7 +11854,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B10" s="23" t="n">
         <v>0.04</v>
@@ -11333,7 +11862,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B11" s="23" t="n">
         <v>0.038</v>
@@ -11341,7 +11870,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B12" s="23" t="n">
         <v>0.036</v>
@@ -11349,7 +11878,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B13" s="23" t="n">
         <v>0.027</v>
@@ -11357,7 +11886,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B14" s="23" t="n">
         <v>0.027</v>
@@ -11365,7 +11894,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="B15" s="23" t="n">
         <v>0.024</v>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Avance Montecarlo'!$A$3:$G$51</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Camino a la final'!$A$3:$I$51</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Partidos A-L'!$A$3:$O$75</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Partidos A-L'!$A$3:$P$75</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="288">
   <si>
     <t xml:space="preserve">Proyección Mundial 2026 — Archivo maestro</t>
   </si>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Es una estimación probabilística reproducible, NO un pronóstico fiable. Solo usa el ranking: ignora lesiones, forma y bajas. Los cruces de octavos en adelante usan el orden estándar del cuadro.</t>
   </si>
   <si>
-    <t xml:space="preserve">Proyección por modelo — 72 partidos de grupos (hora de Ciudad de México)</t>
+    <t xml:space="preserve">Resultados reales y proyección — 72 partidos de grupos (hora de Ciudad de México)</t>
   </si>
   <si>
     <t xml:space="preserve">Grupo</t>
@@ -150,15 +150,18 @@
     <t xml:space="preserve">Prob. Visitante</t>
   </si>
   <si>
-    <t xml:space="preserve">Marcador más prob.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pronóstico</t>
+    <t xml:space="preserve">Marcador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pronóstico / Resultado</t>
   </si>
   <si>
     <t xml:space="preserve">Ganador / Empate</t>
   </si>
   <si>
+    <t xml:space="preserve">Estado</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -180,54 +183,69 @@
     <t xml:space="preserve">2 – 0</t>
   </si>
   <si>
+    <t xml:space="preserve">Ganó México</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadio Akron, Guadalajara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corea del Sur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">República Checa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Corea del Sur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercedes-Benz Stadium, Atlanta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: República Checa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyección</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 – 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: México</t>
   </si>
   <si>
-    <t xml:space="preserve">20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estadio Akron, Guadalajara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corea del Sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">República Checa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 – 1</t>
+    <t xml:space="preserve">24 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadio BBVA, Monterrey</t>
   </si>
   <si>
     <t xml:space="preserve">Favorito: Corea del Sur</t>
   </si>
   <si>
-    <t xml:space="preserve">18 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mercedes-Benz Stadium, Atlanta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: República Checa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 – 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 – 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estadio BBVA, Monterrey</t>
-  </si>
-  <si>
     <t xml:space="preserve">B</t>
   </si>
   <si>
@@ -243,39 +261,39 @@
     <t xml:space="preserve">Bosnia y Herzegovina</t>
   </si>
   <si>
+    <t xml:space="preserve">Empate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levi's Stadium, San Francisco Bay Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suiza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SoFi Stadium, Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Suiza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC Place, Vancouver</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Canadá</t>
   </si>
   <si>
-    <t xml:space="preserve">13 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levi's Stadium, San Francisco Bay Area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suiza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Suiza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SoFi Stadium, Los Angeles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC Place, Vancouver</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parejo</t>
   </si>
   <si>
-    <t xml:space="preserve">Empate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lumen Field, Seattle</t>
   </si>
   <si>
@@ -288,21 +306,30 @@
     <t xml:space="preserve">Paraguay</t>
   </si>
   <si>
+    <t xml:space="preserve">4 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Estados Unidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turquía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 jun</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Estados Unidos</t>
   </si>
   <si>
-    <t xml:space="preserve">22:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turquía</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 jun</t>
-  </si>
-  <si>
     <t xml:space="preserve">21:00</t>
   </si>
   <si>
@@ -336,7 +363,7 @@
     <t xml:space="preserve">Escocia</t>
   </si>
   <si>
-    <t xml:space="preserve">Favorito: Escocia</t>
+    <t xml:space="preserve">Ganó Escocia</t>
   </si>
   <si>
     <t xml:space="preserve">Favorito: Marruecos</t>
@@ -372,33 +399,42 @@
     <t xml:space="preserve">Curazao</t>
   </si>
   <si>
+    <t xml:space="preserve">7 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Alemania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costa de Marfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Costa de Marfil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Alemania</t>
   </si>
   <si>
-    <t xml:space="preserve">17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costa de Marfil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ecuador</t>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrowhead Stadium, Kansas City</t>
   </si>
   <si>
     <t xml:space="preserve">Favorito: Ecuador</t>
   </si>
   <si>
-    <t xml:space="preserve">20 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrowhead Stadium, Kansas City</t>
-  </si>
-  <si>
     <t xml:space="preserve">Favorito: Costa de Marfil</t>
   </si>
   <si>
@@ -414,15 +450,24 @@
     <t xml:space="preserve">Japón</t>
   </si>
   <si>
+    <t xml:space="preserve">2 – 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suecia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Túnez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Suecia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Países Bajos</t>
   </si>
   <si>
-    <t xml:space="preserve">Suecia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Túnez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Favorito: Japón</t>
   </si>
   <si>
@@ -438,21 +483,24 @@
     <t xml:space="preserve">Uruguay</t>
   </si>
   <si>
+    <t xml:space="preserve">España</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabo Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 – 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: España</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Uruguay</t>
   </si>
   <si>
-    <t xml:space="preserve">España</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabo Verde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: España</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 jun</t>
-  </si>
-  <si>
     <t xml:space="preserve">26 jun</t>
   </si>
   <si>
@@ -465,21 +513,21 @@
     <t xml:space="preserve">Egipto</t>
   </si>
   <si>
+    <t xml:space="preserve">Irán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nueva Zelanda</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Bélgica</t>
   </si>
   <si>
-    <t xml:space="preserve">Irán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nueva Zelanda</t>
+    <t xml:space="preserve">Favorito: Egipto</t>
   </si>
   <si>
     <t xml:space="preserve">Favorito: Irán</t>
   </si>
   <si>
-    <t xml:space="preserve">Favorito: Egipto</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 – 2</t>
   </si>
   <si>
@@ -495,24 +543,30 @@
     <t xml:space="preserve">Senegal</t>
   </si>
   <si>
+    <t xml:space="preserve">3 – 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Francia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noruega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Noruega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Francia</t>
   </si>
   <si>
-    <t xml:space="preserve">Irak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noruega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Noruega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00</t>
-  </si>
-  <si>
     <t xml:space="preserve">Favorito: Senegal</t>
   </si>
   <si>
@@ -657,52 +711,52 @@
     <t xml:space="preserve">Alemania (1E)</t>
   </si>
   <si>
+    <t xml:space="preserve">Turquía (3º C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gillette, Boston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Países Bajos (1F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia (2C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estados Unidos (1C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suecia (2F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRG, Houston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francia (1I)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Escocia (3º D)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gillette, Boston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Países Bajos (1F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turquía (2C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estados Unidos (1C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japón (2F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRG, Houston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francia (1I)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egipto (3º H)</t>
-  </si>
-  <si>
     <t xml:space="preserve">MetLife, Nueva York/NJ</t>
   </si>
   <si>
     <t xml:space="preserve">M78</t>
   </si>
   <si>
-    <t xml:space="preserve">Ecuador (2E)</t>
+    <t xml:space="preserve">Costa de Marfil (2E)</t>
   </si>
   <si>
     <t xml:space="preserve">Senegal (2I)</t>
@@ -717,7 +771,7 @@
     <t xml:space="preserve">México (1A)</t>
   </si>
   <si>
-    <t xml:space="preserve">Costa de Marfil (3º E)</t>
+    <t xml:space="preserve">Ecuador (3º E)</t>
   </si>
   <si>
     <t xml:space="preserve">Estadio Azteca, CDMX</t>
@@ -732,57 +786,57 @@
     <t xml:space="preserve">Argentina (1L)</t>
   </si>
   <si>
+    <t xml:space="preserve">RD Congo (3º K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brasil (1D)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Panamá (3º J)</t>
   </si>
   <si>
-    <t xml:space="preserve">M81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brasil (1D)</t>
+    <t xml:space="preserve">M82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">España (1G)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">República Checa (3º A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 jul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia (2K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria (2L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bélgica (1H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croacia (2J)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suiza (1B)</t>
   </si>
   <si>
     <t xml:space="preserve">Noruega (3º I)</t>
   </si>
   <si>
-    <t xml:space="preserve">M82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">España (1G)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">República Checa (3º A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 jul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colombia (2K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria (2L)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bélgica (1H)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croacia (2J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suiza (1B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suecia (3º F)</t>
-  </si>
-  <si>
     <t xml:space="preserve">M86</t>
   </si>
   <si>
@@ -792,7 +846,7 @@
     <t xml:space="preserve">Inglaterra (1J)</t>
   </si>
   <si>
-    <t xml:space="preserve">Irán (2H)</t>
+    <t xml:space="preserve">Egipto (2H)</t>
   </si>
   <si>
     <t xml:space="preserve">Hard Rock, Miami</t>
@@ -851,7 +905,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -934,6 +988,14 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1063,7 +1125,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1112,11 +1174,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1124,15 +1194,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1152,7 +1222,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1422,16 +1492,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.95</c:v>
+                  <c:v>0.993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.759</c:v>
+                  <c:v>0.936</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.579</c:v>
+                  <c:v>0.425</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4</c:v>
+                  <c:v>0.305</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1439,11 +1509,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="84046302"/>
-        <c:axId val="42160312"/>
+        <c:axId val="4112897"/>
+        <c:axId val="73643774"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84046302"/>
+        <c:axId val="4112897"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1475,7 +1545,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42160312"/>
+        <c:crossAx val="73643774"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1483,7 +1553,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42160312"/>
+        <c:axId val="73643774"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1527,7 +1597,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84046302"/>
+        <c:crossAx val="4112897"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1664,16 +1734,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.969</c:v>
+                  <c:v>0.968</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.896</c:v>
+                  <c:v>0.891</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.557</c:v>
+                  <c:v>0.55</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.223</c:v>
+                  <c:v>0.22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1681,11 +1751,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="88992198"/>
-        <c:axId val="12933486"/>
+        <c:axId val="70298180"/>
+        <c:axId val="13109993"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="88992198"/>
+        <c:axId val="70298180"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1717,7 +1787,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12933486"/>
+        <c:crossAx val="13109993"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1725,7 +1795,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12933486"/>
+        <c:axId val="13109993"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1769,7 +1839,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88992198"/>
+        <c:crossAx val="70298180"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1906,16 +1976,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.941</c:v>
+                  <c:v>0.939</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.877</c:v>
+                  <c:v>0.876</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.437</c:v>
+                  <c:v>0.432</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.406</c:v>
+                  <c:v>0.401</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1923,11 +1993,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17566019"/>
-        <c:axId val="47420021"/>
+        <c:axId val="7117603"/>
+        <c:axId val="2795313"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17566019"/>
+        <c:axId val="7117603"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1959,7 +2029,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47420021"/>
+        <c:crossAx val="2795313"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1967,7 +2037,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="47420021"/>
+        <c:axId val="2795313"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2011,7 +2081,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17566019"/>
+        <c:crossAx val="7117603"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2148,16 +2218,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.987</c:v>
+                  <c:v>0.986</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.698</c:v>
+                  <c:v>0.692</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.645</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.292</c:v>
+                  <c:v>0.288</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2165,11 +2235,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="93282579"/>
-        <c:axId val="33113769"/>
+        <c:axId val="17273670"/>
+        <c:axId val="39020463"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93282579"/>
+        <c:axId val="17273670"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2201,7 +2271,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33113769"/>
+        <c:crossAx val="39020463"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2209,7 +2279,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33113769"/>
+        <c:axId val="39020463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2253,7 +2323,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93282579"/>
+        <c:crossAx val="17273670"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2384,22 +2454,22 @@
                   <c:v>Portugal</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>Brasil</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Marruecos</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>México</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Países Bajos</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Brasil</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Marruecos</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>México</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>Alemania</c:v>
+                  <c:v>Estados Unidos</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Estados Unidos</c:v>
+                  <c:v>Alemania</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>Bélgica</c:v>
@@ -2414,37 +2484,37 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.189</c:v>
+                  <c:v>0.201</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.184</c:v>
+                  <c:v>0.181</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.163</c:v>
+                  <c:v>0.153</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.096</c:v>
+                  <c:v>0.097</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.044</c:v>
+                  <c:v>0.043</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.04</c:v>
+                  <c:v>0.042</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.04</c:v>
+                  <c:v>0.039</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.038</c:v>
+                  <c:v>0.039</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.036</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.027</c:v>
+                  <c:v>0.029</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.027</c:v>
+                  <c:v>0.028</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.024</c:v>
@@ -2455,11 +2525,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="59775977"/>
-        <c:axId val="76891431"/>
+        <c:axId val="24412181"/>
+        <c:axId val="56258895"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59775977"/>
+        <c:axId val="24412181"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2491,7 +2561,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76891431"/>
+        <c:crossAx val="56258895"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2499,7 +2569,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76891431"/>
+        <c:axId val="56258895"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2541,7 +2611,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59775977"/>
+        <c:crossAx val="24412181"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2678,16 +2748,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.891</c:v>
+                  <c:v>0.823</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.853</c:v>
+                  <c:v>0.76</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.516</c:v>
+                  <c:v>0.577</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.452</c:v>
+                  <c:v>0.499</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2695,11 +2765,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="46728005"/>
-        <c:axId val="15642665"/>
+        <c:axId val="26998309"/>
+        <c:axId val="51513912"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46728005"/>
+        <c:axId val="26998309"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2731,7 +2801,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15642665"/>
+        <c:crossAx val="51513912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2739,7 +2809,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15642665"/>
+        <c:axId val="51513912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2783,7 +2853,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46728005"/>
+        <c:crossAx val="26998309"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2902,10 +2972,10 @@
                   <c:v>Estados Unidos</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Turquía</c:v>
+                  <c:v>Australia</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Australia</c:v>
+                  <c:v>Turquía</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Paraguay</c:v>
@@ -2920,16 +2990,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.899</c:v>
+                  <c:v>0.993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.706</c:v>
+                  <c:v>0.947</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.662</c:v>
+                  <c:v>0.46</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.458</c:v>
+                  <c:v>0.286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2937,11 +3007,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="93069456"/>
-        <c:axId val="65405806"/>
+        <c:axId val="44159070"/>
+        <c:axId val="4489048"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93069456"/>
+        <c:axId val="44159070"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2973,7 +3043,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65405806"/>
+        <c:crossAx val="4489048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2981,7 +3051,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65405806"/>
+        <c:axId val="4489048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3025,7 +3095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93069456"/>
+        <c:crossAx val="44159070"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3162,16 +3232,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.951</c:v>
+                  <c:v>0.96</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.949</c:v>
+                  <c:v>0.959</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.526</c:v>
+                  <c:v>0.751</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.207</c:v>
+                  <c:v>0.055</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3179,11 +3249,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42877766"/>
-        <c:axId val="76985555"/>
+        <c:axId val="56542734"/>
+        <c:axId val="11279968"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42877766"/>
+        <c:axId val="56542734"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3215,7 +3285,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76985555"/>
+        <c:crossAx val="11279968"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3223,7 +3293,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76985555"/>
+        <c:axId val="11279968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3267,7 +3337,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42877766"/>
+        <c:crossAx val="56542734"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3386,10 +3456,10 @@
                   <c:v>Alemania</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Ecuador</c:v>
+                  <c:v>Costa de Marfil</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Costa de Marfil</c:v>
+                  <c:v>Ecuador</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Curazao</c:v>
@@ -3404,16 +3474,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.946</c:v>
+                  <c:v>0.997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8</c:v>
+                  <c:v>0.944</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.686</c:v>
+                  <c:v>0.627</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.272</c:v>
+                  <c:v>0.13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3421,11 +3491,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="22094353"/>
-        <c:axId val="81880375"/>
+        <c:axId val="89811315"/>
+        <c:axId val="71449825"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22094353"/>
+        <c:axId val="89811315"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3457,7 +3527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81880375"/>
+        <c:crossAx val="71449825"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3465,7 +3535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81880375"/>
+        <c:axId val="71449825"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3509,7 +3579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22094353"/>
+        <c:crossAx val="89811315"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3625,13 +3695,13 @@
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>Suecia</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Países Bajos</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Japón</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Suecia</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Túnez</c:v>
@@ -3646,16 +3716,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.93</c:v>
+                  <c:v>0.943</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.82</c:v>
+                  <c:v>0.922</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.511</c:v>
+                  <c:v>0.854</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.431</c:v>
+                  <c:v>0.124</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3663,11 +3733,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="16358479"/>
-        <c:axId val="71180070"/>
+        <c:axId val="68495857"/>
+        <c:axId val="13826117"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16358479"/>
+        <c:axId val="68495857"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3699,7 +3769,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71180070"/>
+        <c:crossAx val="13826117"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3707,7 +3777,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71180070"/>
+        <c:axId val="13826117"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3751,7 +3821,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16358479"/>
+        <c:crossAx val="68495857"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3873,10 +3943,10 @@
                   <c:v>Uruguay</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Arabia Saudita</c:v>
+                  <c:v>Cabo Verde</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Cabo Verde</c:v>
+                  <c:v>Arabia Saudita</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3888,16 +3958,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.991</c:v>
+                  <c:v>0.961</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.876</c:v>
+                  <c:v>0.765</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.372</c:v>
+                  <c:v>0.488</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.324</c:v>
+                  <c:v>0.445</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3905,11 +3975,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="1829650"/>
-        <c:axId val="69437396"/>
+        <c:axId val="44031909"/>
+        <c:axId val="45712669"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1829650"/>
+        <c:axId val="44031909"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3941,7 +4011,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69437396"/>
+        <c:crossAx val="45712669"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3949,7 +4019,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="69437396"/>
+        <c:axId val="45712669"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3993,7 +4063,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1829650"/>
+        <c:crossAx val="44031909"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4112,10 +4182,10 @@
                   <c:v>Bélgica</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Irán</c:v>
+                  <c:v>Egipto</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Egipto</c:v>
+                  <c:v>Irán</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Nueva Zelanda</c:v>
@@ -4130,16 +4200,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.943</c:v>
+                  <c:v>0.921</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.833</c:v>
+                  <c:v>0.764</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.713</c:v>
+                  <c:v>0.658</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.229</c:v>
+                  <c:v>0.267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4147,11 +4217,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94951035"/>
-        <c:axId val="40675791"/>
+        <c:axId val="3678428"/>
+        <c:axId val="38247360"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94951035"/>
+        <c:axId val="3678428"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4183,7 +4253,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40675791"/>
+        <c:crossAx val="38247360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4191,7 +4261,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40675791"/>
+        <c:axId val="38247360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4235,7 +4305,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94951035"/>
+        <c:crossAx val="3678428"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4372,16 +4442,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.979</c:v>
+                  <c:v>0.998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.823</c:v>
+                  <c:v>0.747</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.547</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.288</c:v>
+                  <c:v>0.289</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4389,11 +4459,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="64611270"/>
-        <c:axId val="15533168"/>
+        <c:axId val="5353455"/>
+        <c:axId val="26405346"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64611270"/>
+        <c:axId val="5353455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4425,7 +4495,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15533168"/>
+        <c:crossAx val="26405346"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4433,7 +4503,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15533168"/>
+        <c:axId val="26405346"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4477,7 +4547,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64611270"/>
+        <c:crossAx val="5353455"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5242,7 +5312,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -5257,8 +5327,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5279,6 +5351,7 @@
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -5326,28 +5399,31 @@
       <c r="O3" s="7" t="s">
         <v>41</v>
       </c>
+      <c r="P3" s="7" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>14</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>60</v>
@@ -5366,36 +5442,39 @@
         <v>0.097</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H5" s="8" t="n">
         <v>40</v>
@@ -5414,36 +5493,39 @@
         <v>0.282</v>
       </c>
       <c r="M5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O5" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>52</v>
+      <c r="P5" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>40</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>60</v>
@@ -5462,36 +5544,39 @@
         <v>0.299</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>14</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>25</v>
@@ -5510,36 +5595,39 @@
         <v>0.209</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>46</v>
+        <v>66</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>40</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>14</v>
@@ -5558,36 +5646,39 @@
         <v>0.641</v>
       </c>
       <c r="M8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>60</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>25</v>
@@ -5606,36 +5697,39 @@
         <v>0.535</v>
       </c>
       <c r="M9" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N9" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="10" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>68</v>
+        <v>73</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>64</v>
@@ -5653,37 +5747,40 @@
       <c r="L10" s="11" t="n">
         <v>0.185</v>
       </c>
-      <c r="M10" s="8" t="s">
+      <c r="M10" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="N10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>68</v>
+      <c r="N10" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>74</v>
+      <c r="G11" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>19</v>
@@ -5701,37 +5798,40 @@
       <c r="L11" s="11" t="n">
         <v>0.59</v>
       </c>
-      <c r="M11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>74</v>
+      <c r="M11" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P11" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>19</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>64</v>
@@ -5750,36 +5850,39 @@
         <v>0.158</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="O12" s="10" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>56</v>
@@ -5798,36 +5901,39 @@
         <v>0.206</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="O13" s="10" t="s">
-        <v>68</v>
+        <v>85</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>19</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>30</v>
@@ -5845,37 +5951,40 @@
       <c r="L14" s="11" t="n">
         <v>0.332</v>
       </c>
-      <c r="M14" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>80</v>
+      <c r="M14" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>64</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>56</v>
@@ -5893,37 +6002,40 @@
       <c r="L15" s="11" t="n">
         <v>0.395</v>
       </c>
-      <c r="M15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>80</v>
+      <c r="M15" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>17</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>41</v>
@@ -5942,36 +6054,39 @@
         <v>0.153</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="O16" s="10" t="s">
-        <v>83</v>
+        <v>92</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>94</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>27</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>22</v>
@@ -5989,37 +6104,40 @@
       <c r="L17" s="11" t="n">
         <v>0.392</v>
       </c>
-      <c r="M17" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>80</v>
+      <c r="M17" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>83</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>17</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>27</v>
@@ -6038,36 +6156,39 @@
         <v>0.219</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="O18" s="10" t="s">
-        <v>83</v>
+        <v>98</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>22</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>41</v>
@@ -6086,36 +6207,39 @@
         <v>0.265</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>88</v>
+        <v>100</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>22</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>17</v>
@@ -6134,36 +6258,39 @@
         <v>0.511</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>83</v>
+        <v>98</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>41</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>27</v>
@@ -6182,36 +6309,39 @@
         <v>0.455</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="O21" s="10" t="s">
-        <v>87</v>
+        <v>102</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>7</v>
@@ -6229,37 +6359,40 @@
       <c r="L22" s="11" t="n">
         <v>0.365</v>
       </c>
-      <c r="M22" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>80</v>
+      <c r="M22" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>83</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>42</v>
@@ -6278,36 +6411,39 @@
         <v>0.511</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>100</v>
+        <v>110</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="P23" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>42</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>7</v>
@@ -6326,36 +6462,39 @@
         <v>0.658</v>
       </c>
       <c r="M24" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="P24" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="O24" s="10" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>6</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>83</v>
@@ -6374,36 +6513,39 @@
         <v>0.054</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N25" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="O25" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="O25" s="10" t="s">
-        <v>96</v>
+      <c r="P25" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>7</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>83</v>
@@ -6422,36 +6564,39 @@
         <v>0.055</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="O26" s="10" t="s">
-        <v>97</v>
+        <v>111</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F27" s="8" t="n">
         <v>42</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>6</v>
@@ -6470,36 +6615,39 @@
         <v>0.661</v>
       </c>
       <c r="M27" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="P27" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>10</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>82</v>
@@ -6518,36 +6666,39 @@
         <v>0.07</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="O28" s="10" t="s">
-        <v>111</v>
+        <v>123</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="F29" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>116</v>
+      <c r="G29" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>23</v>
@@ -6566,36 +6717,39 @@
         <v>0.432</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="O29" s="10" t="s">
-        <v>116</v>
+        <v>127</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P29" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>10</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H30" s="8" t="n">
         <v>33</v>
@@ -6614,36 +6768,39 @@
         <v>0.182</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="O30" s="10" t="s">
-        <v>111</v>
+        <v>130</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="P30" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>23</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>82</v>
@@ -6662,36 +6819,39 @@
         <v>0.158</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="O31" s="10" t="s">
-        <v>116</v>
+        <v>133</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>23</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>10</v>
@@ -6710,36 +6870,39 @@
         <v>0.518</v>
       </c>
       <c r="M32" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="O32" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="O32" s="10" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>82</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>33</v>
@@ -6758,36 +6921,39 @@
         <v>0.553</v>
       </c>
       <c r="M33" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="O33" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="P33" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N33" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>125</v>
+        <v>136</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>137</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>18</v>
@@ -6805,37 +6971,40 @@
       <c r="L34" s="11" t="n">
         <v>0.27</v>
       </c>
-      <c r="M34" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="O34" s="10" t="s">
-        <v>125</v>
+      <c r="M34" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="N34" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P34" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>128</v>
+        <v>69</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="F35" s="8" t="n">
         <v>38</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>45</v>
@@ -6853,37 +7022,40 @@
       <c r="L35" s="11" t="n">
         <v>0.336</v>
       </c>
-      <c r="M35" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N35" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O35" s="13" t="s">
-        <v>80</v>
+      <c r="M35" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="O35" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="P35" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B36" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="D36" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>38</v>
@@ -6902,36 +7074,39 @@
         <v>0.146</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="O36" s="10" t="s">
-        <v>125</v>
+        <v>144</v>
+      </c>
+      <c r="O36" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="P36" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>45</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>18</v>
@@ -6950,36 +7125,39 @@
         <v>0.563</v>
       </c>
       <c r="M37" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="O37" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>18</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>38</v>
@@ -6998,36 +7176,39 @@
         <v>0.224</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="O38" s="10" t="s">
-        <v>126</v>
+        <v>145</v>
+      </c>
+      <c r="O38" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="P38" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>45</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>8</v>
@@ -7046,36 +7227,39 @@
         <v>0.667</v>
       </c>
       <c r="M39" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="O39" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="P39" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N39" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="O39" s="10" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>134</v>
+      <c r="G40" s="9" t="s">
+        <v>149</v>
       </c>
       <c r="H40" s="8" t="n">
         <v>16</v>
@@ -7093,37 +7277,40 @@
       <c r="L40" s="11" t="n">
         <v>0.636</v>
       </c>
-      <c r="M40" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="N40" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="O40" s="10" t="s">
-        <v>134</v>
+      <c r="M40" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N40" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O40" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P40" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>136</v>
+        <v>60</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>150</v>
       </c>
       <c r="F41" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>67</v>
@@ -7141,37 +7328,40 @@
       <c r="L41" s="11" t="n">
         <v>0.028</v>
       </c>
-      <c r="M41" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N41" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="O41" s="10" t="s">
-        <v>136</v>
+      <c r="M41" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="N41" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O41" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P41" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>61</v>
@@ -7190,36 +7380,39 @@
         <v>0.034</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N42" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="O42" s="10" t="s">
-        <v>136</v>
+        <v>154</v>
+      </c>
+      <c r="O42" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="P42" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>16</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>67</v>
@@ -7238,36 +7431,39 @@
         <v>0.132</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="O43" s="10" t="s">
-        <v>134</v>
+        <v>155</v>
+      </c>
+      <c r="O43" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="D44" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="F44" s="8" t="n">
         <v>67</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>61</v>
@@ -7285,37 +7481,40 @@
       <c r="L44" s="11" t="n">
         <v>0.387</v>
       </c>
-      <c r="M44" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N44" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O44" s="13" t="s">
-        <v>80</v>
+      <c r="M44" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N44" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O44" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>120</v>
-      </c>
       <c r="D45" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>16</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>2</v>
@@ -7334,36 +7533,39 @@
         <v>0.59</v>
       </c>
       <c r="M45" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="O45" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="P45" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>142</v>
+        <v>87</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>158</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>9</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>29</v>
@@ -7381,37 +7583,40 @@
       <c r="L46" s="11" t="n">
         <v>0.199</v>
       </c>
-      <c r="M46" s="8" t="s">
+      <c r="M46" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="N46" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="O46" s="10" t="s">
-        <v>142</v>
+      <c r="N46" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O46" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P46" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>145</v>
+        <v>81</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>160</v>
       </c>
       <c r="F47" s="8" t="n">
         <v>20</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>85</v>
@@ -7429,37 +7634,40 @@
       <c r="L47" s="11" t="n">
         <v>0.128</v>
       </c>
-      <c r="M47" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="O47" s="10" t="s">
-        <v>145</v>
+      <c r="M47" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="N47" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="O47" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P47" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F48" s="8" t="n">
         <v>9</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>20</v>
@@ -7478,36 +7686,39 @@
         <v>0.257</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="O48" s="10" t="s">
-        <v>142</v>
+        <v>162</v>
+      </c>
+      <c r="O48" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="P48" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F49" s="8" t="n">
         <v>85</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>29</v>
@@ -7526,36 +7737,39 @@
         <v>0.591</v>
       </c>
       <c r="M49" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="O49" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="P49" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N49" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="O49" s="10" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F50" s="8" t="n">
         <v>29</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>20</v>
@@ -7574,36 +7788,39 @@
         <v>0.439</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="O50" s="10" t="s">
-        <v>145</v>
+        <v>164</v>
+      </c>
+      <c r="O50" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="P50" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F51" s="8" t="n">
         <v>85</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>9</v>
@@ -7622,36 +7839,39 @@
         <v>0.773</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="O51" s="10" t="s">
-        <v>142</v>
+        <v>162</v>
+      </c>
+      <c r="O51" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="P51" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F52" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="H52" s="8" t="n">
         <v>15</v>
@@ -7670,36 +7890,39 @@
         <v>0.183</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="N52" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>152</v>
+        <v>171</v>
+      </c>
+      <c r="O52" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="P52" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="F53" s="8" t="n">
         <v>57</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>31</v>
@@ -7718,36 +7941,39 @@
         <v>0.481</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="O53" s="10" t="s">
-        <v>156</v>
+        <v>174</v>
+      </c>
+      <c r="O53" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="P53" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>57</v>
@@ -7766,36 +7992,39 @@
         <v>0.039</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="O54" s="10" t="s">
-        <v>152</v>
+        <v>177</v>
+      </c>
+      <c r="O54" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="P54" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F55" s="8" t="n">
         <v>31</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>15</v>
@@ -7814,36 +8043,39 @@
         <v>0.515</v>
       </c>
       <c r="M55" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="O55" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="P55" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>31</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>3</v>
@@ -7862,36 +8094,39 @@
         <v>0.724</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="O56" s="10" t="s">
-        <v>152</v>
+        <v>177</v>
+      </c>
+      <c r="O56" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="F57" s="8" t="n">
         <v>15</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>57</v>
@@ -7910,36 +8145,39 @@
         <v>0.15</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>153</v>
+        <v>178</v>
+      </c>
+      <c r="O57" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="P57" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F58" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>11</v>
@@ -7958,36 +8196,39 @@
         <v>0.258</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="O58" s="10" t="s">
-        <v>163</v>
+        <v>183</v>
+      </c>
+      <c r="O58" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="P58" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="F59" s="8" t="n">
         <v>73</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>34</v>
@@ -8006,36 +8247,39 @@
         <v>0.516</v>
       </c>
       <c r="M59" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="O59" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P59" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="O59" s="10" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>73</v>
@@ -8054,36 +8298,39 @@
         <v>0.039</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="O60" s="10" t="s">
-        <v>163</v>
+        <v>183</v>
+      </c>
+      <c r="O60" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="P60" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="F61" s="8" t="n">
         <v>34</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H61" s="8" t="n">
         <v>11</v>
@@ -8102,36 +8349,39 @@
         <v>0.575</v>
       </c>
       <c r="M61" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="O61" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="P61" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N61" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="O61" s="10" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="F62" s="8" t="n">
         <v>11</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>73</v>
@@ -8150,36 +8400,39 @@
         <v>0.093</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="O62" s="10" t="s">
-        <v>164</v>
+        <v>188</v>
+      </c>
+      <c r="O62" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="P62" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="F63" s="8" t="n">
         <v>34</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>4</v>
@@ -8198,36 +8451,39 @@
         <v>0.693</v>
       </c>
       <c r="M63" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="O63" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="P63" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N63" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="O63" s="10" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F64" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>46</v>
@@ -8246,36 +8502,39 @@
         <v>0.115</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="O64" s="10" t="s">
-        <v>173</v>
+        <v>193</v>
+      </c>
+      <c r="O64" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="P64" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="F65" s="8" t="n">
         <v>50</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>13</v>
@@ -8294,36 +8553,39 @@
         <v>0.62</v>
       </c>
       <c r="M65" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N65" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="O65" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="P65" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N65" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="O65" s="10" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="F66" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>50</v>
@@ -8342,36 +8604,39 @@
         <v>0.107</v>
       </c>
       <c r="M66" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="O66" s="10" t="s">
-        <v>173</v>
+        <v>193</v>
+      </c>
+      <c r="O66" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="P66" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F67" s="8" t="n">
         <v>13</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="H67" s="8" t="n">
         <v>46</v>
@@ -8390,36 +8655,39 @@
         <v>0.166</v>
       </c>
       <c r="M67" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="O67" s="10" t="s">
-        <v>177</v>
+        <v>196</v>
+      </c>
+      <c r="O67" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="P67" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F68" s="8" t="n">
         <v>13</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>5</v>
@@ -8438,36 +8706,39 @@
         <v>0.445</v>
       </c>
       <c r="M68" s="8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="O68" s="10" t="s">
-        <v>173</v>
+        <v>193</v>
+      </c>
+      <c r="O68" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="P68" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="F69" s="8" t="n">
         <v>46</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="H69" s="8" t="n">
         <v>50</v>
@@ -8485,37 +8756,40 @@
       <c r="L69" s="11" t="n">
         <v>0.354</v>
       </c>
-      <c r="M69" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N69" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O69" s="13" t="s">
-        <v>80</v>
+      <c r="M69" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N69" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O69" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P69" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="F70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>28</v>
@@ -8534,36 +8808,39 @@
         <v>0.099</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="O70" s="10" t="s">
-        <v>181</v>
+        <v>201</v>
+      </c>
+      <c r="O70" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P70" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="F71" s="8" t="n">
         <v>24</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>63</v>
@@ -8582,36 +8859,39 @@
         <v>0.208</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="O71" s="10" t="s">
-        <v>184</v>
+        <v>204</v>
+      </c>
+      <c r="O71" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="P71" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="F72" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>24</v>
@@ -8630,36 +8910,39 @@
         <v>0.114</v>
       </c>
       <c r="M72" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="O72" s="10" t="s">
-        <v>181</v>
+        <v>201</v>
+      </c>
+      <c r="O72" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P72" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="F73" s="8" t="n">
         <v>63</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="H73" s="8" t="n">
         <v>28</v>
@@ -8678,36 +8961,39 @@
         <v>0.522</v>
       </c>
       <c r="M73" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="O73" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="P73" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="N73" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="F74" s="8" t="n">
         <v>28</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>24</v>
@@ -8725,37 +9011,40 @@
       <c r="L74" s="11" t="n">
         <v>0.394</v>
       </c>
-      <c r="M74" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="N74" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O74" s="13" t="s">
-        <v>80</v>
+      <c r="M74" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="N74" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O74" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="P74" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="F75" s="8" t="n">
         <v>63</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="H75" s="8" t="n">
         <v>1</v>
@@ -8774,19 +9063,22 @@
         <v>0.839</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="O75" s="10" t="s">
-        <v>181</v>
+        <v>201</v>
+      </c>
+      <c r="O75" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P75" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:O75"/>
+  <autoFilter ref="A3:P75"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8816,7 +9108,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -8830,858 +9122,858 @@
         <v>27</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>14</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.617</v>
+        <v>0.698</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.863</v>
+        <v>0.938</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>0.95</v>
+        <v>0.993</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.993</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>25</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.218</v>
+        <v>0.269</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.565</v>
+        <v>0.8</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0.759</v>
+        <v>0.936</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0.936</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>53</v>
+        <v>43</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>40</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.109</v>
+        <v>0.023</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.354</v>
+        <v>0.137</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>0.579</v>
+        <v>0.425</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>0.425</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>47</v>
+        <v>43</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>48</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>60</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.057</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.218</v>
+        <v>0.124</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.4</v>
+        <v>0.305</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>0.305</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>19</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.459</v>
+        <v>0.415</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.76</v>
+        <v>0.685</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>0.891</v>
+        <v>0.823</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.823</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>30</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.363</v>
+        <v>0.331</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.692</v>
+        <v>0.599</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.853</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>0.853</v>
+        <v>0.76</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>56</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.098</v>
+        <v>0.144</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.299</v>
+        <v>0.396</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.516</v>
+        <v>0.577</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.577</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>75</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>64</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0.08</v>
+        <v>0.111</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.249</v>
+        <v>0.32</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.452</v>
+        <v>0.499</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0.499</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>17</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.518</v>
+        <v>0.696</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.782</v>
+        <v>0.926</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>0.899</v>
+        <v>0.993</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.993</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.215</v>
+        <v>0.269</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.501</v>
+        <v>0.8</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>0.706</v>
+        <v>0.947</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.947</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.178</v>
+        <v>0.025</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.447</v>
+        <v>0.158</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>0.662</v>
+        <v>0.46</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>41</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.089</v>
+        <v>0.01</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.27</v>
+        <v>0.116</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>0.458</v>
+        <v>0.286</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0.286</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.47</v>
+        <v>0.447</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.853</v>
+        <v>0.838</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.951</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>0.951</v>
+        <v>0.96</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.463</v>
+        <v>0.441</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.849</v>
+        <v>0.833</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>0.949</v>
+        <v>0.959</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>42</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.055</v>
+        <v>0.108</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.226</v>
+        <v>0.317</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>0.526</v>
+        <v>0.751</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>0.751</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>108</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>83</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.072</v>
+        <v>0.011</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <v>0.207</v>
+        <v>0.055</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.577</v>
+        <v>0.746</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.843</v>
+        <v>0.933</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>0.946</v>
+        <v>0.997</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>0.997</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.243</v>
+        <v>0.227</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.594</v>
+        <v>0.785</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>0.8</v>
+        <v>0.944</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>0.944</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.151</v>
+        <v>0.023</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.435</v>
+        <v>0.23</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.686</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>0.686</v>
+        <v>0.627</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>0.627</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>112</v>
+        <v>116</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>121</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>82</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.029</v>
+        <v>0.004</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.128</v>
+        <v>0.052</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>0.272</v>
+        <v>0.13</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.54</v>
+        <v>0.254</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.824</v>
+        <v>0.515</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>0.93</v>
+        <v>0.943</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>0.943</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.297</v>
+        <v>0.442</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.652</v>
+        <v>0.789</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>0.82</v>
+        <v>0.922</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>0.922</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>128</v>
+        <v>135</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.092</v>
+        <v>0.289</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.29</v>
+        <v>0.659</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>0.511</v>
+        <v>0.854</v>
+      </c>
+      <c r="G26" s="16" t="n">
+        <v>0.854</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>129</v>
+        <v>135</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>141</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>45</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.071</v>
+        <v>0.015</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.235</v>
+        <v>0.037</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="G27" s="15" t="n">
-        <v>0.431</v>
+        <v>0.124</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0.124</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.752</v>
+        <v>0.66</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.963</v>
+        <v>0.885</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>0.991</v>
+        <v>0.961</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>0.961</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>16</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.212</v>
+        <v>0.235</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.745</v>
+        <v>0.598</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>0.876</v>
+        <v>0.765</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>0.765</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>133</v>
+        <v>146</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.021</v>
+        <v>0.059</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.16</v>
+        <v>0.287</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>0.372</v>
+        <v>0.488</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>0.488</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>137</v>
+        <v>146</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>148</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.016</v>
+        <v>0.046</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.133</v>
+        <v>0.23</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="G31" s="15" t="n">
-        <v>0.324</v>
+        <v>0.445</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>0.445</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.541</v>
+        <v>0.507</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.824</v>
+        <v>0.796</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.943</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>0.943</v>
+        <v>0.921</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>0.921</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.271</v>
+        <v>0.22</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.622</v>
+        <v>0.572</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>0.833</v>
+        <v>0.764</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>0.764</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C34" s="8" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.163</v>
+        <v>0.233</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.45</v>
+        <v>0.482</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.713</v>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>0.713</v>
+        <v>0.658</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>0.658</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>146</v>
+        <v>157</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>161</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>85</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.024</v>
+        <v>0.04</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.104</v>
+        <v>0.151</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.229</v>
+        <v>0.267</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.229</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.714</v>
+        <v>0.92</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.925</v>
+        <v>0.99</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="G36" s="14" t="n">
-        <v>0.979</v>
+        <v>0.998</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>0.998</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.202</v>
+        <v>0.023</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.645</v>
+        <v>0.538</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>0.823</v>
+        <v>0.747</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>0.747</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>156</v>
+        <v>166</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>173</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>31</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.064</v>
+        <v>0.045</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.297</v>
+        <v>0.324</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>0.547</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="17" t="n">
         <v>0.547</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>155</v>
+        <v>166</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>172</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>57</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.133</v>
+        <v>0.148</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>0.288</v>
+        <v>0.289</v>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>0.289</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>4</v>
@@ -9693,18 +9985,18 @@
         <v>0.896</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="G40" s="14" t="n">
-        <v>0.969</v>
+        <v>0.968</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>0.968</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>11</v>
@@ -9716,18 +10008,18 @@
         <v>0.747</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="G41" s="14" t="n">
-        <v>0.896</v>
+        <v>0.891</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>0.891</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>34</v>
@@ -9739,18 +10031,18 @@
         <v>0.272</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.557</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>0.557</v>
+        <v>0.55</v>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="16" t="s">
-        <v>166</v>
+        <v>179</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>184</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>73</v>
@@ -9762,18 +10054,18 @@
         <v>0.085</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>0.223</v>
+        <v>0.22</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>5</v>
@@ -9785,18 +10077,18 @@
         <v>0.844</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.941</v>
-      </c>
-      <c r="G44" s="14" t="n">
-        <v>0.941</v>
+        <v>0.939</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>0.939</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>13</v>
@@ -9808,18 +10100,18 @@
         <v>0.737</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>0.877</v>
+        <v>0.876</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>0.876</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>174</v>
+        <v>190</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>192</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>46</v>
@@ -9831,18 +10123,18 @@
         <v>0.22</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="G46" s="15" t="n">
-        <v>0.437</v>
+        <v>0.432</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>0.432</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>176</v>
+        <v>190</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>194</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>50</v>
@@ -9854,18 +10146,18 @@
         <v>0.2</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="G47" s="15" t="n">
-        <v>0.406</v>
+        <v>0.401</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>0.401</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1</v>
@@ -9877,18 +10169,18 @@
         <v>0.945</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="G48" s="14" t="n">
-        <v>0.987</v>
+        <v>0.986</v>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>0.986</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>24</v>
@@ -9900,18 +10192,18 @@
         <v>0.488</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="G49" s="14" t="n">
-        <v>0.698</v>
+        <v>0.692</v>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>0.692</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>28</v>
@@ -9923,18 +10215,18 @@
         <v>0.419</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="G50" s="14" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>185</v>
+        <v>198</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>203</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
@@ -9946,10 +10238,10 @@
         <v>0.148</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="G51" s="15" t="n">
-        <v>0.292</v>
+        <v>0.288</v>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>0.288</v>
       </c>
     </row>
   </sheetData>
@@ -9977,8 +10269,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
-        <v>194</v>
+      <c r="A1" s="20" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -10008,7 +10300,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10017,285 +10309,285 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>203</v>
+        <v>219</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>221</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>208</v>
+        <v>224</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>226</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>212</v>
+        <v>224</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>230</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>215</v>
+        <v>224</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>233</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>220</v>
+        <v>236</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>238</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>224</v>
+        <v>236</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>242</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>228</v>
+        <v>236</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>246</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>233</v>
+        <v>249</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>251</v>
       </c>
       <c r="E11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>236</v>
+        <v>249</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>254</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>239</v>
+        <v>249</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>257</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>243</v>
+        <v>259</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>261</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>246</v>
+        <v>259</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>264</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>249</v>
+        <v>259</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>267</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>253</v>
+        <v>269</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>271</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>257</v>
+        <v>269</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>275</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>261</v>
+        <v>269</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>279</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -10331,7 +10623,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10344,950 +10636,950 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
-        <v>152</v>
+      <c r="A4" s="22" t="s">
+        <v>168</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.979</v>
+        <v>0.998</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.828</v>
+        <v>0.849</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.645</v>
+        <v>0.653</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.477</v>
+        <v>0.507</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>0.189</v>
+        <v>0.321</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>0.201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>181</v>
+      <c r="A5" s="22" t="s">
+        <v>199</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.987</v>
+        <v>0.986</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.831</v>
+        <v>0.829</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.63</v>
+        <v>0.622</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.45</v>
+        <v>0.455</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>0.184</v>
+        <v>0.299</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>0.181</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
-        <v>136</v>
+      <c r="A6" s="22" t="s">
+        <v>150</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.991</v>
+        <v>0.961</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.815</v>
+        <v>0.788</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.585</v>
+        <v>0.57</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.413</v>
+        <v>0.401</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>0.163</v>
+        <v>0.25</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>0.153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>163</v>
+      <c r="A7" s="23" t="s">
+        <v>181</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.969</v>
+        <v>0.968</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.714</v>
+        <v>0.728</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.532</v>
+        <v>0.54</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.315</v>
+        <v>0.322</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>0.096</v>
+        <v>0.181</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0.097</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.941</v>
+        <v>0.939</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.667</v>
+        <v>0.663</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>0.044</v>
+        <v>0.098</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>0.043</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.624</v>
+        <v>0.659</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.41</v>
+        <v>0.355</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.193</v>
+        <v>0.197</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>0.04</v>
+        <v>0.096</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.951</v>
+        <v>0.959</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.651</v>
+        <v>0.654</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.335</v>
+        <v>0.351</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.184</v>
+        <v>0.193</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0.949</v>
+        <v>0.993</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.647</v>
+        <v>0.712</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.335</v>
+        <v>0.35</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.188</v>
+        <v>0.186</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>0.038</v>
+        <v>0.087</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.95</v>
+        <v>0.922</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.673</v>
+        <v>0.592</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.33</v>
+        <v>0.391</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.084</v>
-      </c>
-      <c r="I12" s="22" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="I12" s="24" t="n">
         <v>0.036</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.946</v>
+        <v>0.993</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.632</v>
+        <v>0.586</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.298</v>
+        <v>0.368</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.157</v>
+        <v>0.158</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="I13" s="22" t="n">
-        <v>0.027</v>
+        <v>0.07</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>0.029</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.899</v>
+        <v>0.997</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.529</v>
+        <v>0.705</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.314</v>
+        <v>0.289</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.139</v>
+        <v>0.16</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>0.027</v>
+        <v>0.067</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>0.028</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.943</v>
+        <v>0.921</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.491</v>
+        <v>0.472</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.289</v>
+        <v>0.276</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.13</v>
+        <v>0.128</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I15" s="22" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I15" s="24" t="n">
         <v>0.024</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>11</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.896</v>
+        <v>0.891</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.516</v>
+        <v>0.532</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.303</v>
+        <v>0.313</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.134</v>
+        <v>0.142</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="I16" s="22" t="n">
-        <v>0.022</v>
+        <v>0.06</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>0.021</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.877</v>
+        <v>0.876</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.53</v>
+        <v>0.527</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.254</v>
+        <v>0.253</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.105</v>
+        <v>0.106</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>0.042</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="24" t="n">
         <v>0.013</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.823</v>
+        <v>0.747</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.492</v>
+        <v>0.444</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.248</v>
+        <v>0.208</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.107</v>
+        <v>0.079</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I18" s="22" t="n">
-        <v>0.013</v>
+        <v>0.031</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>16</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.876</v>
+        <v>0.765</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.458</v>
+        <v>0.406</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.21</v>
+        <v>0.187</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.09</v>
+        <v>0.084</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="I19" s="22" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I19" s="24" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>18</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.82</v>
+        <v>0.854</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.428</v>
+        <v>0.424</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="I20" s="22" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I20" s="24" t="n">
         <v>0.008</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>19</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.891</v>
+        <v>0.823</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.527</v>
+        <v>0.464</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.211</v>
+        <v>0.19</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.078</v>
+        <v>0.065</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="I21" s="22" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="I21" s="24" t="n">
         <v>0.007</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.853</v>
+        <v>0.936</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.457</v>
+        <v>0.485</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.163</v>
+        <v>0.169</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.05</v>
+        <v>0.046</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="I22" s="22" t="n">
-        <v>0.004</v>
+        <v>0.011</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.706</v>
+        <v>0.76</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.276</v>
+        <v>0.393</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.118</v>
+        <v>0.141</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I23" s="22" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I23" s="24" t="n">
         <v>0.003</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.8</v>
+        <v>0.658</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.354</v>
+        <v>0.227</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.115</v>
+        <v>0.098</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.036</v>
+        <v>0.032</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="I24" s="22" t="n">
-        <v>0.003</v>
+      <c r="I24" s="24" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.833</v>
+        <v>0.947</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.286</v>
+        <v>0.353</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.124</v>
+        <v>0.158</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="I25" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I25" s="24" t="n">
         <v>0.002</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.759</v>
+        <v>0.46</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.363</v>
+        <v>0.148</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.115</v>
+        <v>0.058</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.036</v>
+        <v>0.019</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.009</v>
-      </c>
-      <c r="I26" s="22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I26" s="24" t="n">
         <v>0.002</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.698</v>
+        <v>0.627</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.289</v>
+        <v>0.234</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.096</v>
+        <v>0.073</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I27" s="22" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>87</v>
+        <v>202</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.662</v>
+        <v>0.692</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.23</v>
+        <v>0.285</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.094</v>
+        <v>0.096</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="I28" s="22" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I28" s="24" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>28</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.645</v>
+        <v>0.64</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.24</v>
+        <v>0.237</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.074</v>
+        <v>0.075</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>0.005</v>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="I29" s="24" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.713</v>
+        <v>0.944</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.183</v>
+        <v>0.364</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.063</v>
+        <v>0.087</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="I30" s="22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I30" s="24" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.547</v>
+        <v>0.943</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.207</v>
+        <v>0.285</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.064</v>
+        <v>0.088</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>0.003</v>
       </c>
-      <c r="I31" s="22" t="n">
+      <c r="I31" s="24" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.686</v>
+        <v>0.764</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.238</v>
+        <v>0.202</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.062</v>
+        <v>0.075</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>0</v>
+        <v>0.004</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.511</v>
+        <v>0.547</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.161</v>
+        <v>0.214</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.048</v>
+        <v>0.064</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I33" s="22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I33" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>94</v>
+        <v>179</v>
       </c>
       <c r="C34" s="8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.526</v>
+        <v>0.55</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.137</v>
+        <v>0.171</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I34" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I34" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="B35" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="C35" s="8" t="n">
-        <v>40</v>
-      </c>
       <c r="D35" s="11" t="n">
-        <v>0.579</v>
+        <v>0.751</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.198</v>
+        <v>0.194</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.043</v>
+        <v>0.038</v>
       </c>
       <c r="G35" s="11" t="n">
         <v>0.008</v>
@@ -11295,28 +11587,28 @@
       <c r="H35" s="11" t="n">
         <v>0.001</v>
       </c>
-      <c r="I35" s="22" t="n">
+      <c r="I35" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="C36" s="8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.431</v>
+        <v>0.425</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.031</v>
+        <v>0.025</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>0.005</v>
@@ -11324,144 +11616,144 @@
       <c r="H36" s="11" t="n">
         <v>0.001</v>
       </c>
-      <c r="I36" s="22" t="n">
+      <c r="I36" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.557</v>
+        <v>0.124</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.158</v>
+        <v>0.032</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.045</v>
+        <v>0.008</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>150</v>
+        <v>88</v>
       </c>
       <c r="C38" s="8" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.288</v>
+        <v>0.286</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.072</v>
+        <v>0.064</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.014</v>
+        <v>0.019</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="22" t="n">
+      <c r="I38" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.4</v>
+        <v>0.289</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.103</v>
+        <v>0.076</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.018</v>
+        <v>0.014</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="22" t="n">
+      <c r="I39" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.452</v>
+        <v>0.432</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.108</v>
+        <v>0.1</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.015</v>
+        <v>0.022</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="22" t="n">
+      <c r="I40" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.516</v>
+        <v>0.401</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.141</v>
+        <v>0.09</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="G41" s="11" t="n">
         <v>0.003</v>
@@ -11469,283 +11761,283 @@
       <c r="H41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="22" t="n">
+      <c r="I41" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="C42" s="8" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.458</v>
+        <v>0.305</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.112</v>
+        <v>0.075</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I42" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.207</v>
+        <v>0.499</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.027</v>
+        <v>0.124</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.004</v>
+        <v>0.02</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="22" t="n">
+      <c r="I43" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C44" s="8" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.272</v>
+        <v>0.577</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.04</v>
+        <v>0.159</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.004</v>
+        <v>0.029</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H44" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="22" t="n">
+      <c r="I44" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.372</v>
+        <v>0.055</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.08</v>
+        <v>0.006</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="22" t="n">
+      <c r="I45" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C46" s="8" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.324</v>
+        <v>0.13</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.066</v>
+        <v>0.018</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.009</v>
+        <v>0.002</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="22" t="n">
+      <c r="I46" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>141</v>
-      </c>
       <c r="C47" s="8" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.229</v>
+        <v>0.445</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.02</v>
+        <v>0.098</v>
       </c>
       <c r="F47" s="11" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G47" s="11" t="n">
         <v>0.002</v>
-      </c>
-      <c r="G47" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="22" t="n">
+      <c r="I47" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C48" s="8" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.223</v>
+        <v>0.488</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.031</v>
+        <v>0.098</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H48" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="22" t="n">
+      <c r="I48" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.437</v>
+        <v>0.267</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.102</v>
+        <v>0.023</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.023</v>
+        <v>0.003</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="22" t="n">
+      <c r="I49" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C50" s="8" t="n">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.406</v>
+        <v>0.22</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.091</v>
+        <v>0.037</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.019</v>
+        <v>0.005</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H50" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I50" s="22" t="n">
+      <c r="I50" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.292</v>
+        <v>0.288</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>0.056</v>
@@ -11759,7 +12051,7 @@
       <c r="H51" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="22" t="n">
+      <c r="I51" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11792,111 +12084,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
-        <v>269</v>
+      <c r="A1" s="20" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="23" t="n">
-        <v>0.189</v>
+        <v>168</v>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>0.201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="23" t="n">
-        <v>0.184</v>
+        <v>199</v>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>0.181</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="23" t="n">
-        <v>0.163</v>
+        <v>150</v>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>0.153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>0.096</v>
+        <v>181</v>
+      </c>
+      <c r="B7" s="25" t="n">
+        <v>0.097</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="23" t="n">
-        <v>0.044</v>
+        <v>191</v>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>0.043</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="23" t="n">
-        <v>0.04</v>
+        <v>105</v>
+      </c>
+      <c r="B9" s="25" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="23" t="n">
-        <v>0.04</v>
+        <v>106</v>
+      </c>
+      <c r="B10" s="25" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>0.038</v>
+        <v>47</v>
+      </c>
+      <c r="B11" s="25" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="23" t="n">
+        <v>137</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <v>0.036</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>0.027</v>
+        <v>89</v>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>0.029</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>0.027</v>
+        <v>120</v>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>0.028</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" s="23" t="n">
+        <v>158</v>
+      </c>
+      <c r="B15" s="25" t="n">
         <v>0.024</v>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Cuadro R32" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Camino a la final" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Favoritos" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Avance Montecarlo'!$A$3:$G$51</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="315">
   <si>
     <t xml:space="preserve">Proyección Mundial 2026 — Archivo maestro</t>
   </si>
@@ -636,18 +637,24 @@
     <t xml:space="preserve">Argelia</t>
   </si>
   <si>
+    <t xml:space="preserve">3 – 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordania</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorito: Austria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favorito: Argentina</t>
   </si>
   <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordania</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorito: Austria</t>
-  </si>
-  <si>
     <t xml:space="preserve">Favorito: Argelia</t>
   </si>
   <si>
@@ -895,6 +902,81 @@
   </si>
   <si>
     <t xml:space="preserve">Probabilidad de ser campeón (top 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyección del cuadro — de octavos a la final (avanza el favorito del modelo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruta más probable partido a partido a partir del cuadro de dieciseisavos: en cada llave avanza el equipo con mayor probabilidad según el modelo (condicionado a los resultados reales al 16 jun). El equipo que avanza va en verde. Es un escenario único; su probabilidad conjunta es baja.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octavos de final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipo 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipo 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuartos de final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semifinales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tercer lugar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMPEÓN PROYECTADO: Argentina  (19% en la simulación)</t>
   </si>
 </sst>
 </file>
@@ -905,7 +987,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1037,6 +1119,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1125,7 +1231,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1227,6 +1333,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1495,13 +1613,13 @@
                   <c:v>0.993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.936</c:v>
+                  <c:v>0.938</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.425</c:v>
+                  <c:v>0.431</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.305</c:v>
+                  <c:v>0.308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1509,11 +1627,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="4112897"/>
-        <c:axId val="73643774"/>
+        <c:axId val="62862476"/>
+        <c:axId val="67442063"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4112897"/>
+        <c:axId val="62862476"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1545,7 +1663,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73643774"/>
+        <c:crossAx val="67442063"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1553,7 +1671,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73643774"/>
+        <c:axId val="67442063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1597,7 +1715,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4112897"/>
+        <c:crossAx val="62862476"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1734,16 +1852,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.968</c:v>
+                  <c:v>0.969</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.891</c:v>
+                  <c:v>0.893</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.55</c:v>
+                  <c:v>0.554</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22</c:v>
+                  <c:v>0.222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1751,11 +1869,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="70298180"/>
-        <c:axId val="13109993"/>
+        <c:axId val="90761700"/>
+        <c:axId val="15894947"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70298180"/>
+        <c:axId val="90761700"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1787,7 +1905,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13109993"/>
+        <c:crossAx val="15894947"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1795,7 +1913,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13109993"/>
+        <c:axId val="15894947"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1839,7 +1957,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70298180"/>
+        <c:crossAx val="90761700"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1976,16 +2094,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.939</c:v>
+                  <c:v>0.94</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.876</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.432</c:v>
+                  <c:v>0.435</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.401</c:v>
+                  <c:v>0.404</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1993,11 +2111,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="7117603"/>
-        <c:axId val="2795313"/>
+        <c:axId val="48350714"/>
+        <c:axId val="97781385"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7117603"/>
+        <c:axId val="48350714"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2029,7 +2147,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2795313"/>
+        <c:crossAx val="97781385"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2037,7 +2155,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2795313"/>
+        <c:axId val="97781385"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2081,7 +2199,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7117603"/>
+        <c:crossAx val="48350714"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2218,16 +2336,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.986</c:v>
+                  <c:v>0.999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.692</c:v>
+                  <c:v>0.703</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.64</c:v>
+                  <c:v>0.524</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.288</c:v>
+                  <c:v>0.304</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2235,11 +2353,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17273670"/>
-        <c:axId val="39020463"/>
+        <c:axId val="90890085"/>
+        <c:axId val="16663419"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17273670"/>
+        <c:axId val="90890085"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2271,7 +2389,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39020463"/>
+        <c:crossAx val="16663419"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2279,7 +2397,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39020463"/>
+        <c:axId val="16663419"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2323,7 +2441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17273670"/>
+        <c:crossAx val="90890085"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2484,34 +2602,34 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.201</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.181</c:v>
+                  <c:v>0.187</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.153</c:v>
+                  <c:v>0.154</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.097</c:v>
+                  <c:v>0.096</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.043</c:v>
+                  <c:v>0.044</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.042</c:v>
+                  <c:v>0.043</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.039</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.039</c:v>
+                  <c:v>0.036</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.036</c:v>
+                  <c:v>0.035</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.029</c:v>
+                  <c:v>0.028</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.028</c:v>
@@ -2525,11 +2643,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24412181"/>
-        <c:axId val="56258895"/>
+        <c:axId val="38588298"/>
+        <c:axId val="66101693"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24412181"/>
+        <c:axId val="38588298"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2561,7 +2679,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56258895"/>
+        <c:crossAx val="66101693"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2569,7 +2687,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56258895"/>
+        <c:axId val="66101693"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2611,7 +2729,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24412181"/>
+        <c:crossAx val="38588298"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2751,7 +2869,7 @@
                   <c:v>0.823</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.76</c:v>
+                  <c:v>0.761</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.577</c:v>
@@ -2765,11 +2883,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26998309"/>
-        <c:axId val="51513912"/>
+        <c:axId val="41300946"/>
+        <c:axId val="48528374"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26998309"/>
+        <c:axId val="41300946"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2801,7 +2919,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51513912"/>
+        <c:crossAx val="48528374"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2809,7 +2927,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51513912"/>
+        <c:axId val="48528374"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2853,7 +2971,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26998309"/>
+        <c:crossAx val="41300946"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2993,13 +3111,13 @@
                   <c:v>0.993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.947</c:v>
+                  <c:v>0.949</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.46</c:v>
+                  <c:v>0.465</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.286</c:v>
+                  <c:v>0.288</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3007,11 +3125,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="44159070"/>
-        <c:axId val="4489048"/>
+        <c:axId val="6951239"/>
+        <c:axId val="61967897"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="44159070"/>
+        <c:axId val="6951239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3043,7 +3161,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4489048"/>
+        <c:crossAx val="61967897"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3051,7 +3169,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4489048"/>
+        <c:axId val="61967897"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3095,7 +3213,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44159070"/>
+        <c:crossAx val="6951239"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3238,10 +3356,10 @@
                   <c:v>0.959</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.751</c:v>
+                  <c:v>0.759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.055</c:v>
+                  <c:v>0.056</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3249,11 +3367,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="56542734"/>
-        <c:axId val="11279968"/>
+        <c:axId val="57724364"/>
+        <c:axId val="67579763"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="56542734"/>
+        <c:axId val="57724364"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3285,7 +3403,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11279968"/>
+        <c:crossAx val="67579763"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3293,7 +3411,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11279968"/>
+        <c:axId val="67579763"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3337,7 +3455,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56542734"/>
+        <c:crossAx val="57724364"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3477,10 +3595,10 @@
                   <c:v>0.997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.944</c:v>
+                  <c:v>0.946</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.627</c:v>
+                  <c:v>0.632</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.13</c:v>
@@ -3491,11 +3609,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="89811315"/>
-        <c:axId val="71449825"/>
+        <c:axId val="5727989"/>
+        <c:axId val="46801446"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89811315"/>
+        <c:axId val="5727989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3527,7 +3645,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71449825"/>
+        <c:crossAx val="46801446"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3535,7 +3653,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71449825"/>
+        <c:axId val="46801446"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3579,7 +3697,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89811315"/>
+        <c:crossAx val="5727989"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3716,7 +3834,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.943</c:v>
+                  <c:v>0.944</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.922</c:v>
@@ -3725,7 +3843,7 @@
                   <c:v>0.854</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.124</c:v>
+                  <c:v>0.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3733,11 +3851,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="68495857"/>
-        <c:axId val="13826117"/>
+        <c:axId val="60947927"/>
+        <c:axId val="2018651"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="68495857"/>
+        <c:axId val="60947927"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3769,7 +3887,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13826117"/>
+        <c:crossAx val="2018651"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3777,7 +3895,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13826117"/>
+        <c:axId val="2018651"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3821,7 +3939,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68495857"/>
+        <c:crossAx val="60947927"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3958,7 +4076,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.961</c:v>
+                  <c:v>0.962</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.765</c:v>
@@ -3967,7 +4085,7 @@
                   <c:v>0.488</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.445</c:v>
+                  <c:v>0.446</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3975,11 +4093,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="44031909"/>
-        <c:axId val="45712669"/>
+        <c:axId val="32292965"/>
+        <c:axId val="46350341"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="44031909"/>
+        <c:axId val="32292965"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4011,7 +4129,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45712669"/>
+        <c:crossAx val="46350341"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4019,7 +4137,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45712669"/>
+        <c:axId val="46350341"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4063,7 +4181,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44031909"/>
+        <c:crossAx val="32292965"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4200,7 +4318,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.921</c:v>
+                  <c:v>0.922</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.764</c:v>
@@ -4209,7 +4327,7 @@
                   <c:v>0.658</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.267</c:v>
+                  <c:v>0.268</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4217,11 +4335,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="3678428"/>
-        <c:axId val="38247360"/>
+        <c:axId val="74953132"/>
+        <c:axId val="48438392"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="3678428"/>
+        <c:axId val="74953132"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4253,7 +4371,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38247360"/>
+        <c:crossAx val="48438392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4261,7 +4379,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38247360"/>
+        <c:axId val="48438392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4305,7 +4423,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3678428"/>
+        <c:crossAx val="74953132"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4445,13 +4563,13 @@
                   <c:v>0.998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.747</c:v>
+                  <c:v>0.751</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.547</c:v>
+                  <c:v>0.551</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.289</c:v>
+                  <c:v>0.292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4459,11 +4577,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5353455"/>
-        <c:axId val="26405346"/>
+        <c:axId val="913430"/>
+        <c:axId val="14114505"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5353455"/>
+        <c:axId val="913430"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4495,7 +4613,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26405346"/>
+        <c:crossAx val="14114505"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4503,7 +4621,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26405346"/>
+        <c:axId val="14114505"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4547,7 +4665,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5353455"/>
+        <c:crossAx val="913430"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8808,16 +8926,16 @@
         <v>0.099</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>49</v>
+        <v>201</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O70" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="P70" s="8" t="s">
-        <v>63</v>
+      <c r="P70" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8834,13 +8952,13 @@
         <v>78</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F71" s="8" t="n">
         <v>24</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>63</v>
@@ -8862,10 +8980,10 @@
         <v>65</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O71" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P71" s="8" t="s">
         <v>63</v>
@@ -8891,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>24</v>
@@ -8913,7 +9031,7 @@
         <v>65</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="O72" s="12" t="s">
         <v>199</v>
@@ -8936,7 +9054,7 @@
         <v>78</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F73" s="8" t="n">
         <v>63</v>
@@ -8964,7 +9082,7 @@
         <v>68</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O73" s="12" t="s">
         <v>200</v>
@@ -8993,7 +9111,7 @@
         <v>28</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>24</v>
@@ -9038,7 +9156,7 @@
         <v>136</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F75" s="8" t="n">
         <v>63</v>
@@ -9066,7 +9184,7 @@
         <v>165</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="O75" s="12" t="s">
         <v>199</v>
@@ -9108,7 +9226,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9122,22 +9240,22 @@
         <v>27</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9180,10 +9298,10 @@
         <v>0.8</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.936</v>
+        <v>0.938</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0.936</v>
+        <v>0.938</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9203,10 +9321,10 @@
         <v>0.137</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.425</v>
+        <v>0.431</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.425</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9226,10 +9344,10 @@
         <v>0.124</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.305</v>
+        <v>0.308</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.305</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9272,10 +9390,10 @@
         <v>0.599</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9364,10 +9482,10 @@
         <v>0.8</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.947</v>
+        <v>0.949</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.947</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9387,10 +9505,10 @@
         <v>0.158</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.46</v>
+        <v>0.465</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.46</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9410,10 +9528,10 @@
         <v>0.116</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.286</v>
+        <v>0.288</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.286</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9479,10 +9597,10 @@
         <v>0.317</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.751</v>
+        <v>0.759</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.751</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9502,10 +9620,10 @@
         <v>0.011</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9548,10 +9666,10 @@
         <v>0.785</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.944</v>
+        <v>0.946</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0.944</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9571,10 +9689,10 @@
         <v>0.23</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9617,10 +9735,10 @@
         <v>0.515</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.943</v>
+        <v>0.944</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>0.943</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9686,10 +9804,10 @@
         <v>0.037</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9709,10 +9827,10 @@
         <v>0.885</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9778,10 +9896,10 @@
         <v>0.23</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9801,10 +9919,10 @@
         <v>0.796</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9870,10 +9988,10 @@
         <v>0.151</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9916,17 +10034,17 @@
         <v>0.538</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.747</v>
+        <v>0.751</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>0.747</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="10" t="s">
         <v>173</v>
       </c>
       <c r="C38" s="8" t="n">
@@ -9939,10 +10057,10 @@
         <v>0.324</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>0.547</v>
+        <v>0.551</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>0.551</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9962,10 +10080,10 @@
         <v>0.148</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.289</v>
+        <v>0.292</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>0.289</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9985,10 +10103,10 @@
         <v>0.896</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.968</v>
+        <v>0.969</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>0.968</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10008,10 +10126,10 @@
         <v>0.747</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.891</v>
+        <v>0.893</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>0.891</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10031,10 +10149,10 @@
         <v>0.272</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.55</v>
+        <v>0.554</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>0.55</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10054,10 +10172,10 @@
         <v>0.085</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.22</v>
+        <v>0.222</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.22</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10077,10 +10195,10 @@
         <v>0.844</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.939</v>
+        <v>0.94</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>0.939</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10123,10 +10241,10 @@
         <v>0.22</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.432</v>
+        <v>0.435</v>
       </c>
       <c r="G46" s="17" t="n">
-        <v>0.432</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10146,10 +10264,10 @@
         <v>0.2</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.401</v>
+        <v>0.404</v>
       </c>
       <c r="G47" s="17" t="n">
-        <v>0.401</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10163,16 +10281,16 @@
         <v>1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.779</v>
+        <v>0.903</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.945</v>
+        <v>0.992</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.986</v>
+        <v>0.999</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>0.986</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10180,45 +10298,45 @@
         <v>198</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>24</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.114</v>
+        <v>0.079</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.488</v>
+        <v>0.534</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.692</v>
+        <v>0.703</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>0.692</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="15" t="s">
         <v>200</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>28</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.088</v>
+        <v>0.008</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.419</v>
+        <v>0.308</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="G50" s="16" t="n">
-        <v>0.64</v>
+        <v>0.524</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>0.524</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10226,22 +10344,22 @@
         <v>198</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.148</v>
+        <v>0.166</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.288</v>
+        <v>0.304</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>0.288</v>
+        <v>0.304</v>
       </c>
     </row>
   </sheetData>
@@ -10270,7 +10388,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -10300,7 +10418,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10309,67 +10427,67 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>69</v>
@@ -10377,129 +10495,129 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>73</v>
@@ -10507,33 +10625,33 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>84</v>
@@ -10541,53 +10659,53 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -10623,7 +10741,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10636,31 +10754,31 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10677,19 +10795,19 @@
         <v>0.998</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.849</v>
+        <v>0.85</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.653</v>
+        <v>0.654</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.507</v>
+        <v>0.508</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.321</v>
+        <v>0.323</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10703,22 +10821,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.986</v>
+        <v>0.999</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.829</v>
+        <v>0.852</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.622</v>
+        <v>0.64</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.455</v>
+        <v>0.473</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.299</v>
+        <v>0.312</v>
       </c>
       <c r="I5" s="16" t="n">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10732,22 +10850,22 @@
         <v>2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0.788</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.57</v>
+        <v>0.569</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.401</v>
+        <v>0.406</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.25</v>
+        <v>0.252</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10761,22 +10879,22 @@
         <v>4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.968</v>
+        <v>0.969</v>
       </c>
       <c r="E7" s="11" t="n">
         <v>0.728</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.54</v>
+        <v>0.545</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.322</v>
+        <v>0.326</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.181</v>
+        <v>0.18</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>0.097</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10790,22 +10908,22 @@
         <v>5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.939</v>
+        <v>0.94</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.663</v>
+        <v>0.676</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.378</v>
+        <v>0.386</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.2</v>
+        <v>0.204</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.098</v>
+        <v>0.099</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10822,19 +10940,19 @@
         <v>0.96</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.659</v>
+        <v>0.66</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.355</v>
+        <v>0.358</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.197</v>
+        <v>0.201</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.096</v>
+        <v>0.097</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10854,10 +10972,10 @@
         <v>0.654</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>0.09</v>
@@ -10883,16 +11001,16 @@
         <v>0.712</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.35</v>
+        <v>0.328</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.186</v>
+        <v>0.172</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.087</v>
+        <v>0.081</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10912,16 +11030,16 @@
         <v>0.592</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.391</v>
+        <v>0.39</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.176</v>
+        <v>0.173</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.083</v>
+        <v>0.081</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10944,13 +11062,13 @@
         <v>0.368</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.158</v>
+        <v>0.152</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.07</v>
+        <v>0.068</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10967,13 +11085,13 @@
         <v>0.997</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>0.289</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>0.067</v>
@@ -10993,16 +11111,16 @@
         <v>9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.276</v>
+        <v>0.282</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.128</v>
+        <v>0.13</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>0.058</v>
@@ -11022,22 +11140,22 @@
         <v>11</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.891</v>
+        <v>0.893</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.532</v>
+        <v>0.533</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.313</v>
+        <v>0.319</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.142</v>
+        <v>0.145</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>0.06</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11054,45 +11172,45 @@
         <v>0.876</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.527</v>
+        <v>0.536</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.253</v>
+        <v>0.258</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>0.106</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.042</v>
+        <v>0.041</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.747</v>
+        <v>0.765</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.444</v>
+        <v>0.407</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.208</v>
+        <v>0.189</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.079</v>
+        <v>0.085</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="I18" s="24" t="n">
         <v>0.01</v>
@@ -11100,28 +11218,28 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.765</v>
+        <v>0.751</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.406</v>
+        <v>0.445</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.187</v>
+        <v>0.207</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.084</v>
+        <v>0.075</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="I19" s="24" t="n">
         <v>0.01</v>
@@ -11141,16 +11259,16 @@
         <v>0.854</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.221</v>
+        <v>0.22</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.074</v>
+        <v>0.071</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="I20" s="24" t="n">
         <v>0.008</v>
@@ -11176,7 +11294,7 @@
         <v>0.19</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="H21" s="11" t="n">
         <v>0.021</v>
@@ -11187,25 +11305,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.936</v>
+        <v>0.761</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.485</v>
+        <v>0.393</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.169</v>
+        <v>0.142</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.046</v>
+        <v>0.042</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>0.011</v>
@@ -11216,28 +11334,28 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.76</v>
+        <v>0.938</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.393</v>
+        <v>0.486</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.141</v>
+        <v>0.165</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.041</v>
+        <v>0.044</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>0.003</v>
@@ -11257,10 +11375,10 @@
         <v>0.658</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.227</v>
+        <v>0.225</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>0.032</v>
@@ -11283,7 +11401,7 @@
         <v>27</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.947</v>
+        <v>0.949</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>0.353</v>
@@ -11312,16 +11430,16 @@
         <v>22</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.46</v>
+        <v>0.465</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.148</v>
+        <v>0.15</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>0.005</v>
@@ -11341,16 +11459,16 @@
         <v>23</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.627</v>
+        <v>0.632</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.234</v>
+        <v>0.231</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.073</v>
+        <v>0.07</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>0.006</v>
@@ -11361,7 +11479,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>198</v>
@@ -11370,16 +11488,16 @@
         <v>24</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.692</v>
+        <v>0.703</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.285</v>
+        <v>0.289</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.096</v>
+        <v>0.097</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>0.007</v>
@@ -11390,28 +11508,28 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.64</v>
+        <v>0.946</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.237</v>
+        <v>0.362</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.075</v>
+        <v>0.085</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0.001</v>
@@ -11419,28 +11537,28 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>0.944</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.364</v>
+        <v>0.285</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>0.087</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>0.001</v>
@@ -11448,28 +11566,28 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.943</v>
+        <v>0.524</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.285</v>
+        <v>0.182</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.088</v>
+        <v>0.057</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0.001</v>
@@ -11489,7 +11607,7 @@
         <v>0.764</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>0.075</v>
@@ -11501,7 +11619,7 @@
         <v>0.004</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11515,19 +11633,19 @@
         <v>31</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.547</v>
+        <v>0.551</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.214</v>
+        <v>0.215</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>0.064</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="I33" s="24" t="n">
         <v>0</v>
@@ -11544,13 +11662,13 @@
         <v>34</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.55</v>
+        <v>0.554</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.171</v>
+        <v>0.172</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>0.011</v>
@@ -11573,16 +11691,16 @@
         <v>42</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.751</v>
+        <v>0.759</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.194</v>
+        <v>0.197</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>0.038</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0.001</v>
@@ -11602,10 +11720,10 @@
         <v>40</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.425</v>
+        <v>0.431</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>0.025</v>
@@ -11631,7 +11749,7 @@
         <v>45</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="E37" s="11" t="n">
         <v>0.032</v>
@@ -11640,7 +11758,7 @@
         <v>0.008</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>0</v>
@@ -11660,13 +11778,13 @@
         <v>41</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.286</v>
+        <v>0.288</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.064</v>
+        <v>0.065</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>0.003</v>
@@ -11689,13 +11807,13 @@
         <v>57</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.289</v>
+        <v>0.292</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>0.002</v>
@@ -11718,13 +11836,13 @@
         <v>46</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.432</v>
+        <v>0.435</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>0.1</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>0.003</v>
@@ -11747,10 +11865,10 @@
         <v>50</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.401</v>
+        <v>0.404</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>0.019</v>
@@ -11776,16 +11894,16 @@
         <v>60</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.305</v>
+        <v>0.308</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>0.013</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H42" s="11" t="n">
         <v>0</v>
@@ -11808,13 +11926,13 @@
         <v>0.499</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>0</v>
@@ -11863,7 +11981,7 @@
         <v>83</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
       <c r="E45" s="11" t="n">
         <v>0.006</v>
@@ -11895,7 +12013,7 @@
         <v>0.13</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>0.002</v>
@@ -11921,13 +12039,13 @@
         <v>61</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="E47" s="11" t="n">
         <v>0.098</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0.002</v>
@@ -11953,7 +12071,7 @@
         <v>0.488</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>0.014</v>
@@ -11979,7 +12097,7 @@
         <v>85</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="E49" s="11" t="n">
         <v>0.023</v>
@@ -12008,10 +12126,10 @@
         <v>73</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.22</v>
+        <v>0.222</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.037</v>
+        <v>0.038</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>0.005</v>
@@ -12028,7 +12146,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>198</v>
@@ -12037,10 +12155,10 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.288</v>
+        <v>0.304</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>0.009</v>
@@ -12085,15 +12203,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12101,7 +12219,7 @@
         <v>168</v>
       </c>
       <c r="B4" s="25" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12109,7 +12227,7 @@
         <v>199</v>
       </c>
       <c r="B5" s="25" t="n">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12117,7 +12235,7 @@
         <v>150</v>
       </c>
       <c r="B6" s="25" t="n">
-        <v>0.153</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12125,7 +12243,7 @@
         <v>181</v>
       </c>
       <c r="B7" s="25" t="n">
-        <v>0.097</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12133,7 +12251,7 @@
         <v>191</v>
       </c>
       <c r="B8" s="25" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12141,7 +12259,7 @@
         <v>105</v>
       </c>
       <c r="B9" s="25" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12157,7 +12275,7 @@
         <v>47</v>
       </c>
       <c r="B11" s="25" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12165,7 +12283,7 @@
         <v>137</v>
       </c>
       <c r="B12" s="25" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12173,7 +12291,7 @@
         <v>89</v>
       </c>
       <c r="B13" s="25" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12202,4 +12320,311 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="27" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="27" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A35:C35"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="336">
   <si>
     <t xml:space="preserve">Proyección Mundial 2026 — Archivo maestro</t>
   </si>
@@ -556,7 +556,10 @@
     <t xml:space="preserve">Noruega</t>
   </si>
   <si>
-    <t xml:space="preserve">Favorito: Noruega</t>
+    <t xml:space="preserve">1 – 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ganó Noruega</t>
   </si>
   <si>
     <t xml:space="preserve">22 jun</t>
@@ -766,7 +769,7 @@
     <t xml:space="preserve">Costa de Marfil (2E)</t>
   </si>
   <si>
-    <t xml:space="preserve">Senegal (2I)</t>
+    <t xml:space="preserve">Noruega (2I)</t>
   </si>
   <si>
     <t xml:space="preserve">AT&amp;T, Dallas</t>
@@ -799,51 +802,51 @@
     <t xml:space="preserve">M81</t>
   </si>
   <si>
-    <t xml:space="preserve">Brasil (1D)</t>
+    <t xml:space="preserve">Marruecos (1D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senegal (3º I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">España (1G)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">República Checa (3º A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 jul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia (2K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria (2L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bélgica (1H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croacia (2J)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suiza (1B)</t>
   </si>
   <si>
     <t xml:space="preserve">Panamá (3º J)</t>
   </si>
   <si>
-    <t xml:space="preserve">M82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">España (1G)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">República Checa (3º A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 jul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colombia (2K)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria (2L)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bélgica (1H)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Croacia (2J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suiza (1B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noruega (3º I)</t>
-  </si>
-  <si>
     <t xml:space="preserve">M86</t>
   </si>
   <si>
@@ -874,7 +877,7 @@
     <t xml:space="preserve">M88</t>
   </si>
   <si>
-    <t xml:space="preserve">Marruecos (2D)</t>
+    <t xml:space="preserve">Brasil (2D)</t>
   </si>
   <si>
     <t xml:space="preserve">Uruguay (2G)</t>
@@ -901,7 +904,19 @@
     <t xml:space="preserve">Campeón</t>
   </si>
   <si>
-    <t xml:space="preserve">Probabilidad de ser campeón (top 12)</t>
+    <t xml:space="preserve">Probabilidad de ser campeón — modelo (con xG) + mercado (cuotas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcla 70% mercado / 30% modelo. Modelo = simulación condicionada a resultados reales y xG. Mercado = cuotas de campeón al 16 jun, sin margen de la casa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mercado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcla</t>
   </si>
   <si>
     <t xml:space="preserve">Proyección del cuadro — de octavos a la final (avanza el favorito del modelo)</t>
@@ -922,58 +937,106 @@
     <t xml:space="preserve">M89</t>
   </si>
   <si>
+    <t xml:space="preserve">4 jul · Lincoln Financial Field, Filadelfia</t>
+  </si>
+  <si>
     <t xml:space="preserve">M90</t>
   </si>
   <si>
+    <t xml:space="preserve">4 jul · NRG Stadium, Houston</t>
+  </si>
+  <si>
     <t xml:space="preserve">M91</t>
   </si>
   <si>
+    <t xml:space="preserve">5 jul · MetLife, Nueva York/NJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">M92</t>
   </si>
   <si>
+    <t xml:space="preserve">5 jul · Estadio Azteca, Ciudad de México</t>
+  </si>
+  <si>
     <t xml:space="preserve">M93</t>
   </si>
   <si>
+    <t xml:space="preserve">6 jul · AT&amp;T Stadium, Dallas</t>
+  </si>
+  <si>
     <t xml:space="preserve">M94</t>
   </si>
   <si>
+    <t xml:space="preserve">6 jul · Lumen Field, Seattle</t>
+  </si>
+  <si>
     <t xml:space="preserve">M95</t>
   </si>
   <si>
+    <t xml:space="preserve">7 jul · Mercedes-Benz, Atlanta</t>
+  </si>
+  <si>
     <t xml:space="preserve">M96</t>
   </si>
   <si>
+    <t xml:space="preserve">7 jul · BC Place, Vancouver</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cuartos de final</t>
   </si>
   <si>
     <t xml:space="preserve">M97</t>
   </si>
   <si>
+    <t xml:space="preserve">9 jul · Gillette Stadium, Boston</t>
+  </si>
+  <si>
     <t xml:space="preserve">M98</t>
   </si>
   <si>
+    <t xml:space="preserve">10 jul · SoFi Stadium, Los Ángeles</t>
+  </si>
+  <si>
     <t xml:space="preserve">M99</t>
   </si>
   <si>
+    <t xml:space="preserve">11 jul · Hard Rock Stadium, Miami</t>
+  </si>
+  <si>
     <t xml:space="preserve">M100</t>
   </si>
   <si>
+    <t xml:space="preserve">11 jul · Arrowhead Stadium, Kansas City</t>
+  </si>
+  <si>
     <t xml:space="preserve">Semifinales</t>
   </si>
   <si>
     <t xml:space="preserve">M101</t>
   </si>
   <si>
+    <t xml:space="preserve">14 jul · AT&amp;T Stadium, Dallas</t>
+  </si>
+  <si>
     <t xml:space="preserve">M102</t>
   </si>
   <si>
+    <t xml:space="preserve">15 jul · Mercedes-Benz, Atlanta</t>
+  </si>
+  <si>
     <t xml:space="preserve">M104</t>
   </si>
   <si>
+    <t xml:space="preserve">19 jul · MetLife, Nueva York/NJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tercer lugar</t>
   </si>
   <si>
     <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 jul · Hard Rock Stadium, Miami</t>
   </si>
   <si>
     <t xml:space="preserve">CAMPEÓN PROYECTADO: Argentina  (19% en la simulación)</t>
@@ -1231,7 +1294,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1332,8 +1395,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1613,13 +1684,13 @@
                   <c:v>0.993</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.938</c:v>
+                  <c:v>0.945</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.431</c:v>
+                  <c:v>0.407</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.308</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1627,11 +1698,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="62862476"/>
-        <c:axId val="67442063"/>
+        <c:axId val="23839170"/>
+        <c:axId val="76926340"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62862476"/>
+        <c:axId val="23839170"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1663,7 +1734,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67442063"/>
+        <c:crossAx val="76926340"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1671,7 +1742,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67442063"/>
+        <c:axId val="76926340"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1715,7 +1786,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62862476"/>
+        <c:crossAx val="23839170"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1852,16 +1923,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.969</c:v>
+                  <c:v>0.97</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.893</c:v>
+                  <c:v>0.891</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.554</c:v>
+                  <c:v>0.542</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.222</c:v>
+                  <c:v>0.219</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1869,11 +1940,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="90761700"/>
-        <c:axId val="15894947"/>
+        <c:axId val="37629653"/>
+        <c:axId val="42305007"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="90761700"/>
+        <c:axId val="37629653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1905,7 +1976,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15894947"/>
+        <c:crossAx val="42305007"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1913,7 +1984,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15894947"/>
+        <c:axId val="42305007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1957,7 +2028,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90761700"/>
+        <c:crossAx val="37629653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2094,16 +2165,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.94</c:v>
+                  <c:v>0.941</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.876</c:v>
+                  <c:v>0.874</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.435</c:v>
+                  <c:v>0.437</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.404</c:v>
+                  <c:v>0.402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2111,11 +2182,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="48350714"/>
-        <c:axId val="97781385"/>
+        <c:axId val="89119760"/>
+        <c:axId val="88656790"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48350714"/>
+        <c:axId val="89119760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2147,7 +2218,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97781385"/>
+        <c:crossAx val="88656790"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2155,7 +2226,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97781385"/>
+        <c:axId val="88656790"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2199,7 +2270,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48350714"/>
+        <c:crossAx val="89119760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2339,13 +2410,13 @@
                   <c:v>0.999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.703</c:v>
+                  <c:v>0.699</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.524</c:v>
+                  <c:v>0.511</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.304</c:v>
+                  <c:v>0.308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2353,11 +2424,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="90890085"/>
-        <c:axId val="16663419"/>
+        <c:axId val="47800045"/>
+        <c:axId val="23306735"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="90890085"/>
+        <c:axId val="47800045"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2389,7 +2460,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16663419"/>
+        <c:crossAx val="23306735"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2397,7 +2468,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16663419"/>
+        <c:axId val="23306735"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2441,7 +2512,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90890085"/>
+        <c:crossAx val="47800045"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2495,7 +2566,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Probabilidad de campeón</a:t>
+              <a:t>Probabilidad de campeón (mezcla)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2560,10 +2631,10 @@
                   <c:v>Francia</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Argentina</c:v>
+                  <c:v>España</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>España</c:v>
+                  <c:v>Argentina</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Inglaterra</c:v>
@@ -2575,67 +2646,67 @@
                   <c:v>Brasil</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Alemania</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Países Bajos</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Marruecos</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>México</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>Países Bajos</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Estados Unidos</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>Alemania</c:v>
+                  <c:v>Bélgica</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Bélgica</c:v>
+                  <c:v>Estados Unidos</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Favoritos!$B$4:$B$15</c:f>
+              <c:f>Favoritos!$D$4:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.2</c:v>
+                  <c:v>0.18</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.187</c:v>
+                  <c:v>0.15</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.154</c:v>
+                  <c:v>0.118</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.096</c:v>
+                  <c:v>0.105</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>0.083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.068</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.052</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0.044</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.043</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.039</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.036</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.035</c:v>
+                  <c:v>0.027</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.028</c:v>
+                  <c:v>0.024</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.028</c:v>
+                  <c:v>0.024</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.024</c:v>
+                  <c:v>0.023</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2643,11 +2714,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="38588298"/>
-        <c:axId val="66101693"/>
+        <c:axId val="79428459"/>
+        <c:axId val="10287035"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38588298"/>
+        <c:axId val="79428459"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2679,7 +2750,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66101693"/>
+        <c:crossAx val="10287035"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2687,7 +2758,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66101693"/>
+        <c:axId val="10287035"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2729,7 +2800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38588298"/>
+        <c:crossAx val="79428459"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2866,16 +2937,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.823</c:v>
+                  <c:v>0.841</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.761</c:v>
+                  <c:v>0.752</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.577</c:v>
+                  <c:v>0.554</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.499</c:v>
+                  <c:v>0.509</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2883,11 +2954,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41300946"/>
-        <c:axId val="48528374"/>
+        <c:axId val="35924931"/>
+        <c:axId val="29651642"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41300946"/>
+        <c:axId val="35924931"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2919,7 +2990,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48528374"/>
+        <c:crossAx val="29651642"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2927,7 +2998,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48528374"/>
+        <c:axId val="29651642"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2971,7 +3042,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41300946"/>
+        <c:crossAx val="35924931"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3108,16 +3179,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.993</c:v>
+                  <c:v>0.992</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.949</c:v>
+                  <c:v>0.942</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.465</c:v>
+                  <c:v>0.457</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.288</c:v>
+                  <c:v>0.289</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3125,11 +3196,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="6951239"/>
-        <c:axId val="61967897"/>
+        <c:axId val="83089903"/>
+        <c:axId val="50796481"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6951239"/>
+        <c:axId val="83089903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3161,7 +3232,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61967897"/>
+        <c:crossAx val="50796481"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3169,7 +3240,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61967897"/>
+        <c:axId val="50796481"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3213,7 +3284,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6951239"/>
+        <c:crossAx val="83089903"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3329,10 +3400,10 @@
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Brasil</c:v>
+                  <c:v>Marruecos</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Marruecos</c:v>
+                  <c:v>Brasil</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Escocia</c:v>
@@ -3350,16 +3421,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.96</c:v>
+                  <c:v>0.959</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.959</c:v>
+                  <c:v>0.958</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.759</c:v>
+                  <c:v>0.732</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.056</c:v>
+                  <c:v>0.058</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3367,11 +3438,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57724364"/>
-        <c:axId val="67579763"/>
+        <c:axId val="6862443"/>
+        <c:axId val="38190948"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57724364"/>
+        <c:axId val="6862443"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3403,7 +3474,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67579763"/>
+        <c:crossAx val="38190948"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3411,7 +3482,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67579763"/>
+        <c:axId val="38190948"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3455,7 +3526,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57724364"/>
+        <c:crossAx val="6862443"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3592,16 +3663,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.997</c:v>
+                  <c:v>0.998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.946</c:v>
+                  <c:v>0.949</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.632</c:v>
+                  <c:v>0.613</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.13</c:v>
+                  <c:v>0.117</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3609,11 +3680,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="5727989"/>
-        <c:axId val="46801446"/>
+        <c:axId val="38709939"/>
+        <c:axId val="62935892"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5727989"/>
+        <c:axId val="38709939"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3645,7 +3716,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46801446"/>
+        <c:crossAx val="62935892"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3653,7 +3724,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46801446"/>
+        <c:axId val="62935892"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3697,7 +3768,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5727989"/>
+        <c:crossAx val="38709939"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3834,16 +3905,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.944</c:v>
+                  <c:v>0.952</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.922</c:v>
+                  <c:v>0.926</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.854</c:v>
+                  <c:v>0.857</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.125</c:v>
+                  <c:v>0.109</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3851,11 +3922,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60947927"/>
-        <c:axId val="2018651"/>
+        <c:axId val="28883367"/>
+        <c:axId val="45924719"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60947927"/>
+        <c:axId val="28883367"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3887,7 +3958,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2018651"/>
+        <c:crossAx val="45924719"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3895,7 +3966,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2018651"/>
+        <c:axId val="45924719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3939,7 +4010,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60947927"/>
+        <c:crossAx val="28883367"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4076,16 +4147,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.962</c:v>
+                  <c:v>0.958</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.765</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.488</c:v>
+                  <c:v>0.485</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.446</c:v>
+                  <c:v>0.445</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4093,11 +4164,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="32292965"/>
-        <c:axId val="46350341"/>
+        <c:axId val="74171623"/>
+        <c:axId val="49703395"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32292965"/>
+        <c:axId val="74171623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4129,7 +4200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46350341"/>
+        <c:crossAx val="49703395"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4137,7 +4208,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46350341"/>
+        <c:axId val="49703395"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4181,7 +4252,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32292965"/>
+        <c:crossAx val="74171623"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4318,16 +4389,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.922</c:v>
+                  <c:v>0.916</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.764</c:v>
+                  <c:v>0.768</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.658</c:v>
+                  <c:v>0.65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.268</c:v>
+                  <c:v>0.267</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4335,11 +4406,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74953132"/>
-        <c:axId val="48438392"/>
+        <c:axId val="7424506"/>
+        <c:axId val="60103564"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74953132"/>
+        <c:axId val="7424506"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4371,7 +4442,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48438392"/>
+        <c:crossAx val="60103564"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4379,7 +4450,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48438392"/>
+        <c:axId val="60103564"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4423,7 +4494,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74953132"/>
+        <c:crossAx val="7424506"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4542,10 +4613,10 @@
                   <c:v>Francia</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Senegal</c:v>
+                  <c:v>Noruega</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Noruega</c:v>
+                  <c:v>Senegal</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Irak</c:v>
@@ -4560,16 +4631,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.998</c:v>
+                  <c:v>0.999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.751</c:v>
+                  <c:v>0.923</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.551</c:v>
+                  <c:v>0.754</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.292</c:v>
+                  <c:v>0.068</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4577,11 +4648,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="913430"/>
-        <c:axId val="14114505"/>
+        <c:axId val="27300597"/>
+        <c:axId val="39690640"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="913430"/>
+        <c:axId val="27300597"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4613,7 +4684,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14114505"/>
+        <c:crossAx val="39690640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4621,7 +4692,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14114505"/>
+        <c:axId val="39690640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4665,7 +4736,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="913430"/>
+        <c:crossAx val="27300597"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5074,13 +5145,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>160560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>256320</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>161640</xdr:rowOff>
@@ -5091,7 +5162,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="2585160" y="380880"/>
+        <a:off x="3994920" y="380880"/>
         <a:ext cx="5759640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -8059,16 +8130,16 @@
         <v>0.481</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O53" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="P53" s="8" t="s">
-        <v>63</v>
+      <c r="P53" s="13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8076,10 +8147,10 @@
         <v>166</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>113</v>
@@ -8113,7 +8184,7 @@
         <v>49</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O54" s="12" t="s">
         <v>168</v>
@@ -8127,7 +8198,7 @@
         <v>166</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>131</v>
@@ -8164,7 +8235,7 @@
         <v>68</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O55" s="12" t="s">
         <v>169</v>
@@ -8215,7 +8286,7 @@
         <v>165</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O56" s="12" t="s">
         <v>168</v>
@@ -8266,7 +8337,7 @@
         <v>65</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O57" s="12" t="s">
         <v>169</v>
@@ -8277,10 +8348,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>129</v>
@@ -8289,13 +8360,13 @@
         <v>136</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F58" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>11</v>
@@ -8317,10 +8388,10 @@
         <v>61</v>
       </c>
       <c r="N58" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O58" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P58" s="8" t="s">
         <v>63</v>
@@ -8328,10 +8399,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>124</v>
@@ -8340,13 +8411,13 @@
         <v>73</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F59" s="8" t="n">
         <v>73</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>34</v>
@@ -8368,10 +8439,10 @@
         <v>68</v>
       </c>
       <c r="N59" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="O59" s="12" t="s">
         <v>186</v>
-      </c>
-      <c r="O59" s="12" t="s">
-        <v>185</v>
       </c>
       <c r="P59" s="8" t="s">
         <v>63</v>
@@ -8379,10 +8450,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>129</v>
@@ -8391,13 +8462,13 @@
         <v>107</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>73</v>
@@ -8419,10 +8490,10 @@
         <v>49</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O60" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P60" s="8" t="s">
         <v>63</v>
@@ -8430,10 +8501,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>124</v>
@@ -8442,13 +8513,13 @@
         <v>73</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F61" s="8" t="n">
         <v>34</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H61" s="8" t="n">
         <v>11</v>
@@ -8470,10 +8541,10 @@
         <v>68</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O61" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P61" s="8" t="s">
         <v>63</v>
@@ -8481,25 +8552,25 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>113</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F62" s="8" t="n">
         <v>11</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>73</v>
@@ -8521,10 +8592,10 @@
         <v>49</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O62" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P62" s="8" t="s">
         <v>63</v>
@@ -8532,25 +8603,25 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>104</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F63" s="8" t="n">
         <v>34</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>4</v>
@@ -8572,10 +8643,10 @@
         <v>68</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O63" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P63" s="8" t="s">
         <v>63</v>
@@ -8583,10 +8654,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>118</v>
@@ -8595,13 +8666,13 @@
         <v>119</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F64" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>46</v>
@@ -8623,10 +8694,10 @@
         <v>65</v>
       </c>
       <c r="N64" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O64" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P64" s="8" t="s">
         <v>63</v>
@@ -8634,10 +8705,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>52</v>
@@ -8646,13 +8717,13 @@
         <v>46</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F65" s="8" t="n">
         <v>50</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>13</v>
@@ -8674,10 +8745,10 @@
         <v>68</v>
       </c>
       <c r="N65" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O65" s="12" t="s">
         <v>196</v>
-      </c>
-      <c r="O65" s="12" t="s">
-        <v>195</v>
       </c>
       <c r="P65" s="8" t="s">
         <v>63</v>
@@ -8685,10 +8756,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>118</v>
@@ -8697,13 +8768,13 @@
         <v>119</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F66" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>50</v>
@@ -8725,10 +8796,10 @@
         <v>65</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O66" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P66" s="8" t="s">
         <v>63</v>
@@ -8736,10 +8807,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>52</v>
@@ -8748,13 +8819,13 @@
         <v>53</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F67" s="8" t="n">
         <v>13</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H67" s="8" t="n">
         <v>46</v>
@@ -8776,10 +8847,10 @@
         <v>65</v>
       </c>
       <c r="N67" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="O67" s="12" t="s">
         <v>196</v>
-      </c>
-      <c r="O67" s="12" t="s">
-        <v>195</v>
       </c>
       <c r="P67" s="8" t="s">
         <v>63</v>
@@ -8787,25 +8858,25 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>189</v>
-      </c>
       <c r="C68" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D68" s="9" t="s">
         <v>115</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F68" s="8" t="n">
         <v>13</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>5</v>
@@ -8827,10 +8898,10 @@
         <v>61</v>
       </c>
       <c r="N68" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O68" s="12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P68" s="8" t="s">
         <v>63</v>
@@ -8838,25 +8909,25 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B69" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>189</v>
-      </c>
       <c r="C69" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>60</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F69" s="8" t="n">
         <v>46</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H69" s="8" t="n">
         <v>50</v>
@@ -8889,7 +8960,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>167</v>
@@ -8901,13 +8972,13 @@
         <v>132</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>28</v>
@@ -8926,13 +8997,13 @@
         <v>0.099</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O70" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P70" s="13" t="s">
         <v>51</v>
@@ -8940,7 +9011,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>167</v>
@@ -8952,13 +9023,13 @@
         <v>78</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F71" s="8" t="n">
         <v>24</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>63</v>
@@ -8980,10 +9051,10 @@
         <v>65</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O71" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P71" s="8" t="s">
         <v>63</v>
@@ -8991,10 +9062,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>118</v>
@@ -9003,13 +9074,13 @@
         <v>136</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F72" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>24</v>
@@ -9031,10 +9102,10 @@
         <v>65</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O72" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P72" s="8" t="s">
         <v>63</v>
@@ -9042,10 +9113,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>99</v>
@@ -9054,13 +9125,13 @@
         <v>78</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F73" s="8" t="n">
         <v>63</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H73" s="8" t="n">
         <v>28</v>
@@ -9082,10 +9153,10 @@
         <v>68</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O73" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P73" s="8" t="s">
         <v>63</v>
@@ -9093,10 +9164,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>52</v>
@@ -9105,13 +9176,13 @@
         <v>132</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F74" s="8" t="n">
         <v>28</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>24</v>
@@ -9144,10 +9215,10 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>52</v>
@@ -9156,13 +9227,13 @@
         <v>136</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F75" s="8" t="n">
         <v>63</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H75" s="8" t="n">
         <v>1</v>
@@ -9184,10 +9255,10 @@
         <v>165</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O75" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P75" s="8" t="s">
         <v>63</v>
@@ -9226,7 +9297,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9240,22 +9311,22 @@
         <v>27</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9269,10 +9340,10 @@
         <v>14</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.698</v>
+        <v>0.701</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.938</v>
+        <v>0.943</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>0.993</v>
@@ -9292,16 +9363,16 @@
         <v>25</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.269</v>
+        <v>0.27</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.8</v>
+        <v>0.815</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.938</v>
+        <v>0.945</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0.938</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9315,16 +9386,16 @@
         <v>40</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.137</v>
+        <v>0.122</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.431</v>
+        <v>0.407</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.431</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9338,16 +9409,16 @@
         <v>60</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.124</v>
+        <v>0.12</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.308</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>0.308</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9361,16 +9432,16 @@
         <v>19</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.415</v>
+        <v>0.433</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.685</v>
+        <v>0.706</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.823</v>
+        <v>0.841</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.823</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9384,16 +9455,16 @@
         <v>30</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.331</v>
+        <v>0.315</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.599</v>
+        <v>0.591</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.761</v>
+        <v>0.752</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.761</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9407,16 +9478,16 @@
         <v>56</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.144</v>
+        <v>0.134</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.396</v>
+        <v>0.377</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.577</v>
+        <v>0.554</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.577</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9430,16 +9501,16 @@
         <v>64</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.32</v>
+        <v>0.327</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.499</v>
+        <v>0.509</v>
       </c>
       <c r="G11" s="17" t="n">
-        <v>0.499</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9453,16 +9524,16 @@
         <v>17</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.696</v>
+        <v>0.703</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.926</v>
+        <v>0.922</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.993</v>
+        <v>0.992</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.993</v>
+        <v>0.992</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9476,16 +9547,16 @@
         <v>27</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.269</v>
+        <v>0.258</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.8</v>
+        <v>0.786</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.949</v>
+        <v>0.942</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.949</v>
+        <v>0.942</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9499,16 +9570,16 @@
         <v>22</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.025</v>
+        <v>0.027</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.158</v>
+        <v>0.167</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.465</v>
+        <v>0.457</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.465</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9522,16 +9593,16 @@
         <v>41</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.116</v>
+        <v>0.125</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.288</v>
+        <v>0.289</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.288</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9539,22 +9610,22 @@
         <v>103</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.838</v>
+        <v>0.841</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.96</v>
+        <v>0.959</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.96</v>
+        <v>0.959</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9562,22 +9633,22 @@
         <v>103</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.441</v>
+        <v>0.445</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.833</v>
+        <v>0.837</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.959</v>
+        <v>0.958</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.959</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9591,16 +9662,16 @@
         <v>42</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.317</v>
+        <v>0.31</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.759</v>
+        <v>0.732</v>
       </c>
       <c r="G18" s="16" t="n">
-        <v>0.759</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9617,13 +9688,13 @@
         <v>0.003</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9637,16 +9708,16 @@
         <v>10</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.746</v>
+        <v>0.759</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.933</v>
+        <v>0.941</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.997</v>
+        <v>0.998</v>
       </c>
       <c r="G20" s="16" t="n">
-        <v>0.997</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9660,16 +9731,16 @@
         <v>33</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.227</v>
+        <v>0.22</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.785</v>
+        <v>0.804</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.946</v>
+        <v>0.949</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>0.946</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9683,16 +9754,16 @@
         <v>23</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.023</v>
+        <v>0.019</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.632</v>
+        <v>0.613</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>0.632</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9706,16 +9777,16 @@
         <v>82</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.052</v>
+        <v>0.046</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.13</v>
+        <v>0.117</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.13</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9729,16 +9800,16 @@
         <v>38</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.254</v>
+        <v>0.263</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.515</v>
+        <v>0.534</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.944</v>
+        <v>0.952</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>0.944</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9752,16 +9823,16 @@
         <v>8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.442</v>
+        <v>0.434</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.789</v>
+        <v>0.78</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.922</v>
+        <v>0.926</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>0.922</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9775,16 +9846,16 @@
         <v>18</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.289</v>
+        <v>0.29</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.659</v>
+        <v>0.653</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.854</v>
+        <v>0.857</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>0.854</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9798,16 +9869,16 @@
         <v>45</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.037</v>
+        <v>0.033</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.125</v>
+        <v>0.109</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0.125</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9821,16 +9892,16 @@
         <v>2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.66</v>
+        <v>0.656</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.885</v>
+        <v>0.882</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.962</v>
+        <v>0.958</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>0.962</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9844,10 +9915,10 @@
         <v>16</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.235</v>
+        <v>0.234</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.598</v>
+        <v>0.594</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>0.765</v>
@@ -9867,16 +9938,16 @@
         <v>67</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>0.287</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.488</v>
+        <v>0.485</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.488</v>
+        <v>0.485</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9890,16 +9961,16 @@
         <v>61</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.046</v>
+        <v>0.05</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.23</v>
+        <v>0.237</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="G31" s="17" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9913,16 +9984,16 @@
         <v>9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.507</v>
+        <v>0.503</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.796</v>
+        <v>0.795</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.922</v>
+        <v>0.916</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>0.922</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9936,16 +10007,16 @@
         <v>29</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.22</v>
+        <v>0.229</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.572</v>
+        <v>0.577</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.764</v>
+        <v>0.768</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>0.764</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9962,13 +10033,13 @@
         <v>0.233</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.482</v>
+        <v>0.483</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9982,16 +10053,16 @@
         <v>85</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.151</v>
+        <v>0.146</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.268</v>
+        <v>0.267</v>
       </c>
       <c r="G35" s="17" t="n">
-        <v>0.268</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10005,16 +10076,16 @@
         <v>3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.92</v>
+        <v>0.872</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.99</v>
+        <v>0.984</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10022,22 +10093,22 @@
         <v>166</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.023</v>
+        <v>0.104</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.538</v>
+        <v>0.555</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.751</v>
+        <v>0.923</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>0.751</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10045,53 +10116,53 @@
         <v>166</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C38" s="8" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.045</v>
+        <v>0.022</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.324</v>
+        <v>0.444</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.551</v>
+        <v>0.754</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>0.551</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="18" t="s">
         <v>172</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>57</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.148</v>
+        <v>0.017</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="G39" s="17" t="n">
-        <v>0.292</v>
+        <v>0.068</v>
+      </c>
+      <c r="G39" s="19" t="n">
+        <v>0.068</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>4</v>
@@ -10100,21 +10171,21 @@
         <v>0.604</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.896</v>
+        <v>0.899</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>11</v>
@@ -10123,67 +10194,67 @@
         <v>0.314</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.893</v>
+        <v>0.891</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>0.893</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>186</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>34</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.068</v>
+        <v>0.069</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.272</v>
+        <v>0.269</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="G42" s="16" t="n">
-        <v>0.554</v>
+        <v>0.542</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>0.542</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>73</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.085</v>
+        <v>0.082</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>5</v>
@@ -10192,99 +10263,99 @@
         <v>0.54</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.844</v>
+        <v>0.846</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.94</v>
+        <v>0.941</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>0.94</v>
+        <v>0.941</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>13</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.737</v>
+        <v>0.735</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.876</v>
+        <v>0.874</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>0.876</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>46</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.059</v>
+        <v>0.061</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.435</v>
+        <v>0.437</v>
       </c>
       <c r="G46" s="17" t="n">
-        <v>0.435</v>
+        <v>0.437</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>50</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.2</v>
+        <v>0.195</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.404</v>
+        <v>0.402</v>
       </c>
       <c r="G47" s="17" t="n">
-        <v>0.404</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.903</v>
+        <v>0.905</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.992</v>
+        <v>0.993</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>0.999</v>
@@ -10295,33 +10366,33 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>24</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.079</v>
+        <v>0.076</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.534</v>
+        <v>0.531</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.703</v>
+        <v>0.699</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>0.703</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>28</v>
@@ -10330,36 +10401,36 @@
         <v>0.008</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.308</v>
+        <v>0.305</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.524</v>
+        <v>0.511</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>0.524</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.166</v>
+        <v>0.171</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.304</v>
+        <v>0.308</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>0.304</v>
+        <v>0.308</v>
       </c>
     </row>
   </sheetData>
@@ -10388,7 +10459,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -10418,7 +10489,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10427,67 +10498,67 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>69</v>
@@ -10495,129 +10566,129 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>73</v>
@@ -10625,33 +10696,33 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>84</v>
@@ -10659,53 +10730,53 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -10741,7 +10812,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -10754,31 +10825,31 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10792,30 +10863,30 @@
         <v>3</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.998</v>
+        <v>0.999</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.85</v>
+        <v>0.844</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.654</v>
+        <v>0.636</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.508</v>
+        <v>0.477</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.323</v>
+        <v>0.302</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>0.2</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>198</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>1</v>
@@ -10824,19 +10895,19 @@
         <v>0.999</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.852</v>
+        <v>0.85</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.64</v>
+        <v>0.636</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.473</v>
+        <v>0.465</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.312</v>
+        <v>0.307</v>
       </c>
       <c r="I5" s="16" t="n">
-        <v>0.187</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10850,109 +10921,109 @@
         <v>2</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.962</v>
+        <v>0.958</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.788</v>
+        <v>0.784</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.569</v>
+        <v>0.557</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.406</v>
+        <v>0.399</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.252</v>
+        <v>0.251</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>0.154</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.728</v>
+        <v>0.723</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.545</v>
+        <v>0.478</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.326</v>
+        <v>0.312</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.18</v>
+        <v>0.172</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>0.096</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>190</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.94</v>
+        <v>0.941</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.676</v>
+        <v>0.68</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.386</v>
+        <v>0.437</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.204</v>
+        <v>0.213</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.099</v>
+        <v>0.101</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.96</v>
+        <v>0.993</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.66</v>
+        <v>0.724</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.358</v>
+        <v>0.34</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.201</v>
+        <v>0.184</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.097</v>
+        <v>0.094</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10969,48 +11040,48 @@
         <v>0.959</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.654</v>
+        <v>0.656</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.353</v>
+        <v>0.34</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.09</v>
+        <v>0.094</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0.993</v>
+        <v>0.958</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.712</v>
+        <v>0.654</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.328</v>
+        <v>0.331</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.172</v>
+        <v>0.191</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11024,80 +11095,80 @@
         <v>8</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.922</v>
+        <v>0.926</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.592</v>
+        <v>0.595</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.39</v>
+        <v>0.388</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.173</v>
+        <v>0.174</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.993</v>
+        <v>0.998</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.586</v>
+        <v>0.728</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.368</v>
+        <v>0.323</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.152</v>
+        <v>0.184</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.068</v>
+        <v>0.086</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.028</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.997</v>
+        <v>0.992</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.706</v>
+        <v>0.58</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.289</v>
+        <v>0.362</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.158</v>
+        <v>0.149</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.067</v>
+        <v>0.068</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11111,19 +11182,19 @@
         <v>9</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.922</v>
+        <v>0.916</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.471</v>
+        <v>0.473</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.282</v>
+        <v>0.266</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="I15" s="24" t="n">
         <v>0.024</v>
@@ -11131,57 +11202,57 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>11</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.893</v>
+        <v>0.891</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.533</v>
+        <v>0.52</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.319</v>
+        <v>0.28</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.145</v>
+        <v>0.128</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.876</v>
+        <v>0.874</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.536</v>
+        <v>0.528</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.258</v>
+        <v>0.283</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.106</v>
+        <v>0.115</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="I17" s="24" t="n">
         <v>0.014</v>
@@ -11201,19 +11272,19 @@
         <v>0.765</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.407</v>
+        <v>0.409</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.189</v>
+        <v>0.182</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.085</v>
+        <v>0.082</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11227,22 +11298,22 @@
         <v>15</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.751</v>
+        <v>0.754</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.445</v>
+        <v>0.42</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.207</v>
+        <v>0.199</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="H19" s="11" t="n">
         <v>0.03</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.01</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11256,22 +11327,22 @@
         <v>18</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.854</v>
+        <v>0.857</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.423</v>
+        <v>0.428</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.22</v>
+        <v>0.232</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.071</v>
+        <v>0.077</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11285,22 +11356,22 @@
         <v>19</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.823</v>
+        <v>0.841</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.464</v>
+        <v>0.488</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.19</v>
+        <v>0.228</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.066</v>
+        <v>0.08</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11314,22 +11385,22 @@
         <v>30</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.761</v>
+        <v>0.752</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.393</v>
+        <v>0.372</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.142</v>
+        <v>0.147</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.042</v>
+        <v>0.045</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11343,19 +11414,19 @@
         <v>25</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.938</v>
+        <v>0.945</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.486</v>
+        <v>0.494</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.165</v>
+        <v>0.168</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>0.003</v>
@@ -11372,16 +11443,16 @@
         <v>20</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.658</v>
+        <v>0.65</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.097</v>
+        <v>0.086</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>0.01</v>
@@ -11392,28 +11463,28 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>94</v>
+        <v>204</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.949</v>
+        <v>0.699</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.353</v>
+        <v>0.286</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.158</v>
+        <v>0.106</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.035</v>
+        <v>0.029</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="I25" s="24" t="n">
         <v>0.002</v>
@@ -11421,28 +11492,28 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>88</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.465</v>
+        <v>0.942</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.15</v>
+        <v>0.339</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.056</v>
+        <v>0.14</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.018</v>
+        <v>0.031</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.002</v>
@@ -11450,57 +11521,57 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="C27" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.632</v>
+        <v>0.457</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.231</v>
+        <v>0.152</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.07</v>
+        <v>0.061</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>0.006</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.703</v>
+        <v>0.613</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.289</v>
+        <v>0.21</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.097</v>
+        <v>0.064</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.027</v>
+        <v>0.019</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0.001</v>
@@ -11508,28 +11579,28 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.946</v>
+        <v>0.923</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.362</v>
+        <v>0.353</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.085</v>
+        <v>0.107</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0.001</v>
@@ -11537,28 +11608,28 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.944</v>
+        <v>0.768</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.285</v>
+        <v>0.205</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.087</v>
+        <v>0.065</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>0.001</v>
@@ -11566,28 +11637,28 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.524</v>
+        <v>0.949</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.182</v>
+        <v>0.372</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.057</v>
+        <v>0.098</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0.001</v>
@@ -11595,22 +11666,22 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.764</v>
+        <v>0.952</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.2</v>
+        <v>0.306</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>0.019</v>
@@ -11619,24 +11690,24 @@
         <v>0.004</v>
       </c>
       <c r="I32" s="24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.551</v>
+        <v>0.511</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.215</v>
+        <v>0.181</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>0.064</v>
@@ -11645,36 +11716,36 @@
         <v>0.015</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="I33" s="24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="C34" s="8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.554</v>
+        <v>0.732</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.172</v>
+        <v>0.182</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.051</v>
+        <v>0.039</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I34" s="24" t="n">
         <v>0</v>
@@ -11682,28 +11753,28 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>103</v>
+        <v>180</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.759</v>
+        <v>0.542</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.197</v>
+        <v>0.173</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.038</v>
+        <v>0.05</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.009</v>
+        <v>0.011</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I35" s="24" t="n">
         <v>0</v>
@@ -11711,28 +11782,28 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C36" s="8" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.431</v>
+        <v>0.554</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.122</v>
+        <v>0.138</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>0.025</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I36" s="24" t="n">
         <v>0</v>
@@ -11740,28 +11811,28 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.125</v>
+        <v>0.402</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.032</v>
+        <v>0.085</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.008</v>
+        <v>0.019</v>
       </c>
       <c r="G37" s="11" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H37" s="11" t="n">
         <v>0.001</v>
-      </c>
-      <c r="H37" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="I37" s="24" t="n">
         <v>0</v>
@@ -11769,28 +11840,28 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="C38" s="8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.288</v>
+        <v>0.407</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.065</v>
+        <v>0.113</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.018</v>
+        <v>0.023</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>0</v>
@@ -11798,25 +11869,25 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.292</v>
+        <v>0.109</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.075</v>
+        <v>0.025</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>0</v>
@@ -11827,25 +11898,25 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.435</v>
+        <v>0.485</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0</v>
@@ -11856,25 +11927,25 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>194</v>
+        <v>48</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>190</v>
+        <v>43</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.404</v>
+        <v>0.3</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.089</v>
+        <v>0.069</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H41" s="11" t="n">
         <v>0</v>
@@ -11885,22 +11956,22 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C42" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.308</v>
+        <v>0.509</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.076</v>
+        <v>0.121</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>0.002</v>
@@ -11914,22 +11985,22 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C43" s="8" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.499</v>
+        <v>0.289</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.123</v>
+        <v>0.063</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0.003</v>
@@ -11943,25 +12014,25 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="C44" s="8" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.577</v>
+        <v>0.058</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.159</v>
+        <v>0.007</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H44" s="11" t="n">
         <v>0</v>
@@ -11972,19 +12043,19 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C45" s="8" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.056</v>
+        <v>0.117</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.006</v>
+        <v>0.014</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>0.001</v>
@@ -12001,25 +12072,25 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C46" s="8" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.13</v>
+        <v>0.445</v>
       </c>
       <c r="E46" s="11" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F46" s="11" t="n">
         <v>0.017</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="G46" s="11" t="n">
         <v>0.002</v>
-      </c>
-      <c r="G46" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="H46" s="11" t="n">
         <v>0</v>
@@ -12030,25 +12101,25 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.446</v>
+        <v>0.267</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.098</v>
+        <v>0.023</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.016</v>
+        <v>0.003</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
         <v>0</v>
@@ -12059,25 +12130,25 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C48" s="8" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.488</v>
+        <v>0.068</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.097</v>
+        <v>0.015</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.014</v>
+        <v>0.002</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H48" s="11" t="n">
         <v>0</v>
@@ -12088,25 +12159,25 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C49" s="8" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.268</v>
+        <v>0.219</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.023</v>
+        <v>0.037</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -12117,25 +12188,25 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C50" s="8" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.222</v>
+        <v>0.437</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.038</v>
+        <v>0.104</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H50" s="11" t="n">
         <v>0</v>
@@ -12146,22 +12217,22 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.304</v>
+        <v>0.308</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.009</v>
+        <v>0.013</v>
       </c>
       <c r="G51" s="11" t="n">
         <v>0.001</v>
@@ -12194,123 +12265,216 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
-        <v>289</v>
-      </c>
+      <c r="A1" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>288</v>
+      <c r="A3" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="25" t="n">
-        <v>0.2</v>
+      <c r="B4" s="27" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="25" t="n">
-        <v>0.187</v>
+      <c r="A5" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>0.154</v>
+      <c r="A6" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>0.096</v>
+      <c r="A7" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>0.105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="25" t="n">
+      <c r="A8" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>0.083</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>0.068</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>0.052</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="D11" s="27" t="n">
         <v>0.044</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="25" t="n">
-        <v>0.043</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="25" t="n">
-        <v>0.039</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="B12" s="27" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>0.027</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="25" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="B13" s="27" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="27" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="25" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="25" t="n">
-        <v>0.028</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="B15" s="25" t="n">
-        <v>0.024</v>
+      <c r="B15" s="27" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>0.023</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -12332,43 +12496,47 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="A2" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>292</v>
+      <c r="A4" s="29" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>120</v>
@@ -12376,10 +12544,13 @@
       <c r="C6" s="10" t="s">
         <v>168</v>
       </c>
+      <c r="D6" s="9" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>74</v>
@@ -12387,92 +12558,116 @@
       <c r="C7" s="10" t="s">
         <v>137</v>
       </c>
+      <c r="D7" s="9" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>89</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>158</v>
       </c>
+      <c r="D10" s="9" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>150</v>
       </c>
+      <c r="D11" s="9" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>181</v>
+        <v>312</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>106</v>
+        <v>314</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>303</v>
+      <c r="A15" s="29" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>168</v>
@@ -12480,10 +12675,13 @@
       <c r="C17" s="9" t="s">
         <v>137</v>
       </c>
+      <c r="D17" s="9" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>158</v>
@@ -12491,133 +12689,164 @@
       <c r="C18" s="10" t="s">
         <v>150</v>
       </c>
+      <c r="D18" s="9" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="27" t="s">
-        <v>308</v>
+      <c r="A22" s="29" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="B24" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>150</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
-        <v>287</v>
+      <c r="A27" s="29" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="27" t="s">
-        <v>312</v>
+      <c r="A31" s="29" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
+      <c r="A35" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A35:D35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="361">
   <si>
     <t xml:space="preserve">Proyección Mundial 2026 — Archivo maestro</t>
   </si>
@@ -244,6 +244,9 @@
     <t xml:space="preserve">1 – 0</t>
   </si>
   <si>
+    <t xml:space="preserve">0.48 – 0.69</t>
+  </si>
+  <si>
     <t xml:space="preserve">24 jun</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t xml:space="preserve">Ganó Suiza</t>
   </si>
   <si>
+    <t xml:space="preserve">2.06 – 0.23</t>
+  </si>
+  <si>
     <t xml:space="preserve">16:00</t>
   </si>
   <si>
@@ -314,6 +320,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ganó Canadá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75 – 0.18</t>
   </si>
   <si>
     <t xml:space="preserve">Favorito: Suiza</t>
@@ -1770,13 +1779,13 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.915</c:v>
+                  <c:v>0.919</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.212</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.16</c:v>
+                  <c:v>0.169</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1784,11 +1793,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42057454"/>
-        <c:axId val="46799463"/>
+        <c:axId val="72296756"/>
+        <c:axId val="61721441"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42057454"/>
+        <c:axId val="72296756"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1820,7 +1829,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46799463"/>
+        <c:crossAx val="61721441"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1828,7 +1837,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46799463"/>
+        <c:axId val="61721441"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1872,7 +1881,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42057454"/>
+        <c:crossAx val="72296756"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2012,13 +2021,13 @@
                   <c:v>0.999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.858</c:v>
+                  <c:v>0.856</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.528</c:v>
+                  <c:v>0.536</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.212</c:v>
+                  <c:v>0.213</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2026,11 +2035,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42691307"/>
-        <c:axId val="37398116"/>
+        <c:axId val="30387075"/>
+        <c:axId val="16387615"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42691307"/>
+        <c:axId val="30387075"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2062,7 +2071,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37398116"/>
+        <c:crossAx val="16387615"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2070,7 +2079,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37398116"/>
+        <c:axId val="16387615"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2114,7 +2123,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42691307"/>
+        <c:crossAx val="30387075"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2251,16 +2260,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.985</c:v>
+                  <c:v>0.983</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.805</c:v>
+                  <c:v>0.809</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.474</c:v>
+                  <c:v>0.473</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.374</c:v>
+                  <c:v>0.377</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2268,11 +2277,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="62353524"/>
-        <c:axId val="22788087"/>
+        <c:axId val="90138406"/>
+        <c:axId val="74420872"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62353524"/>
+        <c:axId val="90138406"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2304,7 +2313,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22788087"/>
+        <c:crossAx val="74420872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2312,7 +2321,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22788087"/>
+        <c:axId val="74420872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2356,7 +2365,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62353524"/>
+        <c:crossAx val="90138406"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2493,16 +2502,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.999</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.951</c:v>
+                  <c:v>0.948</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.461</c:v>
+                  <c:v>0.465</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.175</c:v>
+                  <c:v>0.178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2510,11 +2519,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="34603658"/>
-        <c:axId val="21825954"/>
+        <c:axId val="37614205"/>
+        <c:axId val="22047197"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34603658"/>
+        <c:axId val="37614205"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2546,7 +2555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21825954"/>
+        <c:crossAx val="22047197"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2554,7 +2563,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21825954"/>
+        <c:axId val="22047197"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2598,7 +2607,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34603658"/>
+        <c:crossAx val="37614205"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2738,16 +2747,16 @@
                   <c:v>Países Bajos</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>Marruecos</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>Colombia</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>Noruega</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>Marruecos</c:v>
+                  <c:v>Estados Unidos</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Estados Unidos</c:v>
+                  <c:v>Noruega</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2759,40 +2768,40 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.166</c:v>
+                  <c:v>0.174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.162</c:v>
+                  <c:v>0.154</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.118</c:v>
+                  <c:v>0.126</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.108</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.077</c:v>
+                  <c:v>0.065</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.067</c:v>
+                  <c:v>0.062</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.05</c:v>
+                  <c:v>0.054</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.039</c:v>
+                  <c:v>0.041</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0.029</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>0.028</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.027</c:v>
-                </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.024</c:v>
+                  <c:v>0.025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2800,11 +2809,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="60468062"/>
-        <c:axId val="67673165"/>
+        <c:axId val="71479370"/>
+        <c:axId val="98092989"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60468062"/>
+        <c:axId val="71479370"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2836,7 +2845,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67673165"/>
+        <c:crossAx val="98092989"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2844,7 +2853,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67673165"/>
+        <c:axId val="98092989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2886,7 +2895,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60468062"/>
+        <c:crossAx val="71479370"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3029,10 +3038,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.37</c:v>
+                  <c:v>0.385</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.366</c:v>
+                  <c:v>0.352</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3040,11 +3049,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19410721"/>
-        <c:axId val="33187669"/>
+        <c:axId val="16640892"/>
+        <c:axId val="84053474"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19410721"/>
+        <c:axId val="16640892"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3076,7 +3085,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33187669"/>
+        <c:crossAx val="84053474"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3084,7 +3093,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33187669"/>
+        <c:axId val="84053474"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3128,7 +3137,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19410721"/>
+        <c:crossAx val="16640892"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3265,16 +3274,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.987</c:v>
+                  <c:v>0.988</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.919</c:v>
+                  <c:v>0.916</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.448</c:v>
+                  <c:v>0.445</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.411</c:v>
+                  <c:v>0.405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3282,11 +3291,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17637216"/>
-        <c:axId val="36115240"/>
+        <c:axId val="5649725"/>
+        <c:axId val="56388020"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17637216"/>
+        <c:axId val="5649725"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3318,7 +3327,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36115240"/>
+        <c:crossAx val="56388020"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3326,7 +3335,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36115240"/>
+        <c:axId val="56388020"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3370,7 +3379,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17637216"/>
+        <c:crossAx val="5649725"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3507,16 +3516,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.951</c:v>
+                  <c:v>0.954</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.948</c:v>
+                  <c:v>0.944</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.783</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.079</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3524,11 +3533,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52839270"/>
-        <c:axId val="15240752"/>
+        <c:axId val="50592062"/>
+        <c:axId val="66125057"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52839270"/>
+        <c:axId val="50592062"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3560,7 +3569,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15240752"/>
+        <c:crossAx val="66125057"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3568,7 +3577,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15240752"/>
+        <c:axId val="66125057"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3612,7 +3621,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52839270"/>
+        <c:crossAx val="50592062"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3752,13 +3761,13 @@
                   <c:v>0.996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.96</c:v>
+                  <c:v>0.961</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.764</c:v>
+                  <c:v>0.763</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.081</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3766,11 +3775,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="85783393"/>
-        <c:axId val="36228055"/>
+        <c:axId val="37518120"/>
+        <c:axId val="92393629"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85783393"/>
+        <c:axId val="37518120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3802,7 +3811,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36228055"/>
+        <c:crossAx val="92393629"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3810,7 +3819,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36228055"/>
+        <c:axId val="92393629"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3854,7 +3863,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85783393"/>
+        <c:crossAx val="37518120"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3991,16 +4000,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.954</c:v>
+                  <c:v>0.951</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.89</c:v>
+                  <c:v>0.891</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.865</c:v>
+                  <c:v>0.868</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.134</c:v>
+                  <c:v>0.136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4008,11 +4017,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="84889758"/>
-        <c:axId val="35740542"/>
+        <c:axId val="5551920"/>
+        <c:axId val="76626066"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84889758"/>
+        <c:axId val="5551920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4044,7 +4053,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35740542"/>
+        <c:crossAx val="76626066"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4052,7 +4061,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35740542"/>
+        <c:axId val="76626066"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4096,7 +4105,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84889758"/>
+        <c:crossAx val="5551920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4233,16 +4242,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.974</c:v>
+                  <c:v>0.972</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.752</c:v>
+                  <c:v>0.749</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.57</c:v>
+                  <c:v>0.562</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.35</c:v>
+                  <c:v>0.357</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4250,11 +4259,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="89159604"/>
-        <c:axId val="70069808"/>
+        <c:axId val="93209502"/>
+        <c:axId val="1455594"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89159604"/>
+        <c:axId val="93209502"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4286,7 +4295,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70069808"/>
+        <c:crossAx val="1455594"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4294,7 +4303,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70069808"/>
+        <c:axId val="1455594"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4338,7 +4347,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89159604"/>
+        <c:crossAx val="93209502"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4475,16 +4484,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.875</c:v>
+                  <c:v>0.876</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.712</c:v>
+                  <c:v>0.72</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.655</c:v>
+                  <c:v>0.643</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.396</c:v>
+                  <c:v>0.392</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4492,11 +4501,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="62930812"/>
-        <c:axId val="7339637"/>
+        <c:axId val="62927146"/>
+        <c:axId val="85320551"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="62930812"/>
+        <c:axId val="62927146"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4528,7 +4537,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7339637"/>
+        <c:crossAx val="85320551"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4536,7 +4545,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7339637"/>
+        <c:axId val="85320551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4580,7 +4589,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62930812"/>
+        <c:crossAx val="62927146"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4720,13 +4729,13 @@
                   <c:v>0.998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.981</c:v>
+                  <c:v>0.98</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.618</c:v>
+                  <c:v>0.619</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.106</c:v>
+                  <c:v>0.108</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4734,11 +4743,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41271727"/>
-        <c:axId val="45873374"/>
+        <c:axId val="6255145"/>
+        <c:axId val="22132771"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41271727"/>
+        <c:axId val="6255145"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4770,7 +4779,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45873374"/>
+        <c:crossAx val="22132771"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4778,7 +4787,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45873374"/>
+        <c:axId val="22132771"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4822,7 +4831,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41271727"/>
+        <c:crossAx val="6255145"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5912,7 +5921,7 @@
         <v>69</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5920,7 +5929,7 @@
         <v>45</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>68</v>
@@ -5957,16 +5966,16 @@
         <v>67</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>49</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R8" s="8" t="s">
         <v>67</v>
@@ -5977,13 +5986,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>50</v>
@@ -6014,16 +6023,16 @@
         <v>67</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>57</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R9" s="8" t="s">
         <v>67</v>
@@ -6031,25 +6040,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>64</v>
@@ -6083,30 +6092,30 @@
         <v>69</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>56</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>19</v>
@@ -6137,15 +6146,15 @@
         <v>53</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>63</v>
@@ -6154,16 +6163,16 @@
         <v>47</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>19</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>64</v>
@@ -6182,13 +6191,13 @@
         <v>0.149</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P12" s="13" t="s">
         <v>53</v>
@@ -6197,30 +6206,30 @@
         <v>69</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" s="8" t="n">
         <v>56</v>
@@ -6239,13 +6248,13 @@
         <v>0.211</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P13" s="13" t="s">
         <v>53</v>
@@ -6254,30 +6263,30 @@
         <v>69</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>19</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>30</v>
@@ -6299,13 +6308,13 @@
         <v>67</v>
       </c>
       <c r="N14" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q14" s="14" t="s">
         <v>61</v>
@@ -6316,25 +6325,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>64</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H15" s="8" t="n">
         <v>56</v>
@@ -6356,13 +6365,13 @@
         <v>67</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O15" s="15" t="s">
         <v>66</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q15" s="14" t="s">
         <v>61</v>
@@ -6373,25 +6382,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>17</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H16" s="8" t="n">
         <v>41</v>
@@ -6410,13 +6419,13 @@
         <v>0.262</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P16" s="13" t="s">
         <v>53</v>
@@ -6425,30 +6434,30 @@
         <v>69</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>27</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H17" s="8" t="n">
         <v>22</v>
@@ -6470,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P17" s="13" t="s">
         <v>53</v>
@@ -6482,30 +6491,30 @@
         <v>61</v>
       </c>
       <c r="R17" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>17</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H18" s="8" t="n">
         <v>27</v>
@@ -6527,13 +6536,13 @@
         <v>67</v>
       </c>
       <c r="N18" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q18" s="14" t="s">
         <v>69</v>
@@ -6544,25 +6553,25 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>104</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>22</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>41</v>
@@ -6584,13 +6593,13 @@
         <v>67</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O19" s="15" t="s">
         <v>66</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q19" s="14" t="s">
         <v>61</v>
@@ -6601,25 +6610,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>55</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>22</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>17</v>
@@ -6641,13 +6650,13 @@
         <v>67</v>
       </c>
       <c r="N20" s="10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q20" s="14" t="s">
         <v>61</v>
@@ -6658,25 +6667,25 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>55</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>41</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>27</v>
@@ -6698,13 +6707,13 @@
         <v>67</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q21" s="14" t="s">
         <v>61</v>
@@ -6715,25 +6724,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>6</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>7</v>
@@ -6767,30 +6776,30 @@
         <v>61</v>
       </c>
       <c r="R22" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>83</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>42</v>
@@ -6809,13 +6818,13 @@
         <v>0.503</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P23" s="13" t="s">
         <v>53</v>
@@ -6824,30 +6833,30 @@
         <v>61</v>
       </c>
       <c r="R23" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>42</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>7</v>
@@ -6869,16 +6878,16 @@
         <v>67</v>
       </c>
       <c r="N24" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R24" s="8" t="s">
         <v>67</v>
@@ -6886,25 +6895,25 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>6</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H25" s="8" t="n">
         <v>83</v>
@@ -6926,13 +6935,13 @@
         <v>67</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q25" s="14" t="s">
         <v>51</v>
@@ -6943,25 +6952,25 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>65</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>7</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H26" s="8" t="n">
         <v>83</v>
@@ -6983,13 +6992,13 @@
         <v>67</v>
       </c>
       <c r="N26" s="10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q26" s="14" t="s">
         <v>51</v>
@@ -7000,25 +7009,25 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F27" s="8" t="n">
         <v>42</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>6</v>
@@ -7040,16 +7049,16 @@
         <v>67</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R27" s="8" t="s">
         <v>67</v>
@@ -7057,25 +7066,25 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>10</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H28" s="8" t="n">
         <v>82</v>
@@ -7094,13 +7103,13 @@
         <v>0.089</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N28" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O28" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="O28" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="P28" s="13" t="s">
         <v>53</v>
@@ -7109,30 +7118,30 @@
         <v>51</v>
       </c>
       <c r="R28" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="E29" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F29" s="8" t="n">
         <v>33</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H29" s="8" t="n">
         <v>23</v>
@@ -7154,10 +7163,10 @@
         <v>69</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="P29" s="13" t="s">
         <v>53</v>
@@ -7166,30 +7175,30 @@
         <v>61</v>
       </c>
       <c r="R29" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>10</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H30" s="8" t="n">
         <v>33</v>
@@ -7211,13 +7220,13 @@
         <v>67</v>
       </c>
       <c r="N30" s="10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q30" s="14" t="s">
         <v>69</v>
@@ -7228,25 +7237,25 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>141</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>23</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H31" s="8" t="n">
         <v>82</v>
@@ -7268,13 +7277,13 @@
         <v>67</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="P31" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q31" s="14" t="s">
         <v>69</v>
@@ -7285,25 +7294,25 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>23</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>10</v>
@@ -7325,16 +7334,16 @@
         <v>67</v>
       </c>
       <c r="N32" s="16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O32" s="15" t="s">
         <v>66</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R32" s="8" t="s">
         <v>67</v>
@@ -7342,25 +7351,25 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="E33" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>82</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H33" s="8" t="n">
         <v>33</v>
@@ -7382,16 +7391,16 @@
         <v>67</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O33" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="P33" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R33" s="8" t="s">
         <v>67</v>
@@ -7399,25 +7408,25 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H34" s="8" t="n">
         <v>18</v>
@@ -7436,7 +7445,7 @@
         <v>0.335</v>
       </c>
       <c r="M34" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N34" s="16" t="s">
         <v>66</v>
@@ -7451,30 +7460,30 @@
         <v>61</v>
       </c>
       <c r="R34" s="8" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>55</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F35" s="8" t="n">
         <v>38</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>45</v>
@@ -7493,13 +7502,13 @@
         <v>0.338</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N35" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="O35" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="O35" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="P35" s="13" t="s">
         <v>53</v>
@@ -7508,30 +7517,30 @@
         <v>61</v>
       </c>
       <c r="R35" s="8" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>38</v>
@@ -7553,13 +7562,13 @@
         <v>67</v>
       </c>
       <c r="N36" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O36" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q36" s="14" t="s">
         <v>69</v>
@@ -7570,25 +7579,25 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>45</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H37" s="8" t="n">
         <v>18</v>
@@ -7610,16 +7619,16 @@
         <v>67</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O37" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P37" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R37" s="8" t="s">
         <v>67</v>
@@ -7627,25 +7636,25 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>18</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H38" s="8" t="n">
         <v>38</v>
@@ -7667,13 +7676,13 @@
         <v>67</v>
       </c>
       <c r="N38" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q38" s="14" t="s">
         <v>69</v>
@@ -7684,25 +7693,25 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="E39" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>45</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H39" s="8" t="n">
         <v>8</v>
@@ -7724,16 +7733,16 @@
         <v>67</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R39" s="8" t="s">
         <v>67</v>
@@ -7741,25 +7750,25 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>61</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H40" s="8" t="n">
         <v>16</v>
@@ -7790,7 +7799,7 @@
         <v>53</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R40" s="8" t="s">
         <v>67</v>
@@ -7798,10 +7807,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>64</v>
@@ -7810,13 +7819,13 @@
         <v>65</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F41" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H41" s="8" t="n">
         <v>67</v>
@@ -7835,7 +7844,7 @@
         <v>0.029</v>
       </c>
       <c r="M41" s="15" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N41" s="16" t="s">
         <v>66</v>
@@ -7850,15 +7859,15 @@
         <v>51</v>
       </c>
       <c r="R41" s="8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>64</v>
@@ -7867,13 +7876,13 @@
         <v>65</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>61</v>
@@ -7895,13 +7904,13 @@
         <v>67</v>
       </c>
       <c r="N42" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="P42" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q42" s="14" t="s">
         <v>51</v>
@@ -7912,25 +7921,25 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>16</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>67</v>
@@ -7952,13 +7961,13 @@
         <v>67</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="P43" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q43" s="14" t="s">
         <v>69</v>
@@ -7969,25 +7978,25 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F44" s="8" t="n">
         <v>67</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H44" s="8" t="n">
         <v>61</v>
@@ -8009,13 +8018,13 @@
         <v>67</v>
       </c>
       <c r="N44" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="O44" s="12" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="P44" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q44" s="14" t="s">
         <v>61</v>
@@ -8026,25 +8035,25 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>56</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>16</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H45" s="8" t="n">
         <v>2</v>
@@ -8066,16 +8075,16 @@
         <v>67</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O45" s="12" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="P45" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R45" s="8" t="s">
         <v>67</v>
@@ -8083,25 +8092,25 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>9</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H46" s="8" t="n">
         <v>29</v>
@@ -8140,25 +8149,25 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F47" s="8" t="n">
         <v>20</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H47" s="8" t="n">
         <v>85</v>
@@ -8177,7 +8186,7 @@
         <v>0.202</v>
       </c>
       <c r="M47" s="15" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N47" s="16" t="s">
         <v>66</v>
@@ -8197,25 +8206,25 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F48" s="8" t="n">
         <v>9</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H48" s="8" t="n">
         <v>20</v>
@@ -8237,13 +8246,13 @@
         <v>67</v>
       </c>
       <c r="N48" s="10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="O48" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P48" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q48" s="14" t="s">
         <v>61</v>
@@ -8254,25 +8263,25 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F49" s="8" t="n">
         <v>85</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H49" s="8" t="n">
         <v>29</v>
@@ -8294,16 +8303,16 @@
         <v>67</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O49" s="12" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="P49" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R49" s="8" t="s">
         <v>67</v>
@@ -8311,25 +8320,25 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F50" s="8" t="n">
         <v>29</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="H50" s="8" t="n">
         <v>20</v>
@@ -8351,13 +8360,13 @@
         <v>67</v>
       </c>
       <c r="N50" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O50" s="12" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P50" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q50" s="14" t="s">
         <v>61</v>
@@ -8368,25 +8377,25 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F51" s="8" t="n">
         <v>85</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H51" s="8" t="n">
         <v>9</v>
@@ -8408,16 +8417,16 @@
         <v>67</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="O51" s="12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="P51" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="R51" s="8" t="s">
         <v>67</v>
@@ -8425,25 +8434,25 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F52" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H52" s="8" t="n">
         <v>15</v>
@@ -8462,13 +8471,13 @@
         <v>0.18</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N52" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="O52" s="12" t="s">
         <v>188</v>
-      </c>
-      <c r="O52" s="12" t="s">
-        <v>185</v>
       </c>
       <c r="P52" s="13" t="s">
         <v>53</v>
@@ -8482,25 +8491,25 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F53" s="8" t="n">
         <v>57</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H53" s="8" t="n">
         <v>31</v>
@@ -8519,13 +8528,13 @@
         <v>0.64</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O53" s="12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="P53" s="13" t="s">
         <v>53</v>
@@ -8539,25 +8548,25 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F54" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>57</v>
@@ -8579,13 +8588,13 @@
         <v>67</v>
       </c>
       <c r="N54" s="10" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O54" s="12" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q54" s="14" t="s">
         <v>51</v>
@@ -8596,25 +8605,25 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B55" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>193</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="F55" s="8" t="n">
         <v>31</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H55" s="8" t="n">
         <v>15</v>
@@ -8636,16 +8645,16 @@
         <v>67</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O55" s="12" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R55" s="8" t="s">
         <v>67</v>
@@ -8653,25 +8662,25 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F56" s="8" t="n">
         <v>31</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H56" s="8" t="n">
         <v>3</v>
@@ -8693,16 +8702,16 @@
         <v>67</v>
       </c>
       <c r="N56" s="10" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="O56" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="P56" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q56" s="14" t="s">
         <v>185</v>
-      </c>
-      <c r="P56" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q56" s="14" t="s">
-        <v>182</v>
       </c>
       <c r="R56" s="8" t="s">
         <v>67</v>
@@ -8710,25 +8719,25 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F57" s="8" t="n">
         <v>15</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H57" s="8" t="n">
         <v>57</v>
@@ -8750,13 +8759,13 @@
         <v>67</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="O57" s="12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P57" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q57" s="14" t="s">
         <v>69</v>
@@ -8767,25 +8776,25 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F58" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H58" s="8" t="n">
         <v>11</v>
@@ -8804,13 +8813,13 @@
         <v>0.255</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="N58" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="O58" s="12" t="s">
         <v>203</v>
-      </c>
-      <c r="O58" s="12" t="s">
-        <v>200</v>
       </c>
       <c r="P58" s="13" t="s">
         <v>53</v>
@@ -8824,25 +8833,25 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F59" s="8" t="n">
         <v>73</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H59" s="8" t="n">
         <v>34</v>
@@ -8864,16 +8873,16 @@
         <v>69</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="O59" s="12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P59" s="13" t="s">
         <v>53</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R59" s="8" t="s">
         <v>67</v>
@@ -8881,25 +8890,25 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F60" s="8" t="n">
         <v>4</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H60" s="8" t="n">
         <v>73</v>
@@ -8921,13 +8930,13 @@
         <v>67</v>
       </c>
       <c r="N60" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="O60" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="P60" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q60" s="14" t="s">
         <v>51</v>
@@ -8938,25 +8947,25 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F61" s="8" t="n">
         <v>34</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H61" s="8" t="n">
         <v>11</v>
@@ -8978,16 +8987,16 @@
         <v>67</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O61" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P61" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R61" s="8" t="s">
         <v>67</v>
@@ -8995,25 +9004,25 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F62" s="8" t="n">
         <v>11</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="H62" s="8" t="n">
         <v>73</v>
@@ -9035,13 +9044,13 @@
         <v>67</v>
       </c>
       <c r="N62" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O62" s="12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P62" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q62" s="14" t="s">
         <v>51</v>
@@ -9052,25 +9061,25 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F63" s="8" t="n">
         <v>34</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="H63" s="8" t="n">
         <v>4</v>
@@ -9092,16 +9101,16 @@
         <v>67</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="O63" s="12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="P63" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R63" s="8" t="s">
         <v>67</v>
@@ -9109,25 +9118,25 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F64" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H64" s="8" t="n">
         <v>46</v>
@@ -9166,10 +9175,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>55</v>
@@ -9178,13 +9187,13 @@
         <v>48</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F65" s="8" t="n">
         <v>50</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H65" s="8" t="n">
         <v>13</v>
@@ -9203,19 +9212,19 @@
         <v>0.638</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="O65" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P65" s="13" t="s">
         <v>53</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R65" s="8" t="s">
         <v>67</v>
@@ -9223,25 +9232,25 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F66" s="8" t="n">
         <v>5</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H66" s="8" t="n">
         <v>50</v>
@@ -9263,13 +9272,13 @@
         <v>67</v>
       </c>
       <c r="N66" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O66" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P66" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q66" s="14" t="s">
         <v>69</v>
@@ -9280,10 +9289,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>55</v>
@@ -9292,13 +9301,13 @@
         <v>56</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F67" s="8" t="n">
         <v>13</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H67" s="8" t="n">
         <v>46</v>
@@ -9320,13 +9329,13 @@
         <v>67</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="O67" s="12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P67" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q67" s="14" t="s">
         <v>69</v>
@@ -9337,25 +9346,25 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F68" s="8" t="n">
         <v>13</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H68" s="8" t="n">
         <v>5</v>
@@ -9377,13 +9386,13 @@
         <v>67</v>
       </c>
       <c r="N68" s="16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O68" s="15" t="s">
         <v>66</v>
       </c>
       <c r="P68" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q68" s="14" t="s">
         <v>61</v>
@@ -9394,25 +9403,25 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>65</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F69" s="8" t="n">
         <v>46</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H69" s="8" t="n">
         <v>50</v>
@@ -9434,13 +9443,13 @@
         <v>67</v>
       </c>
       <c r="N69" s="16" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O69" s="15" t="s">
         <v>66</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q69" s="14" t="s">
         <v>61</v>
@@ -9451,25 +9460,25 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F70" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H70" s="8" t="n">
         <v>28</v>
@@ -9488,13 +9497,13 @@
         <v>0.073</v>
       </c>
       <c r="M70" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="N70" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="O70" s="12" t="s">
         <v>225</v>
-      </c>
-      <c r="O70" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="P70" s="13" t="s">
         <v>53</v>
@@ -9508,25 +9517,25 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F71" s="8" t="n">
         <v>24</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="H71" s="8" t="n">
         <v>63</v>
@@ -9545,13 +9554,13 @@
         <v>0.207</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O71" s="12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P71" s="13" t="s">
         <v>53</v>
@@ -9565,25 +9574,25 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F72" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H72" s="8" t="n">
         <v>24</v>
@@ -9605,13 +9614,13 @@
         <v>67</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O72" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P72" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q72" s="14" t="s">
         <v>69</v>
@@ -9622,25 +9631,25 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F73" s="8" t="n">
         <v>63</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H73" s="8" t="n">
         <v>28</v>
@@ -9662,16 +9671,16 @@
         <v>67</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O73" s="12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="P73" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R73" s="8" t="s">
         <v>67</v>
@@ -9679,25 +9688,25 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>55</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F74" s="8" t="n">
         <v>28</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H74" s="8" t="n">
         <v>24</v>
@@ -9719,13 +9728,13 @@
         <v>67</v>
       </c>
       <c r="N74" s="10" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O74" s="12" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P74" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q74" s="14" t="s">
         <v>61</v>
@@ -9736,25 +9745,25 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>55</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F75" s="8" t="n">
         <v>63</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H75" s="8" t="n">
         <v>1</v>
@@ -9776,16 +9785,16 @@
         <v>67</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O75" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P75" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="R75" s="8" t="s">
         <v>67</v>
@@ -9824,7 +9833,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -9838,22 +9847,22 @@
         <v>27</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9867,7 +9876,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.953</v>
+        <v>0.947</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>1</v>
@@ -9890,16 +9899,16 @@
         <v>25</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.047</v>
+        <v>0.053</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.762</v>
+        <v>0.77</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.915</v>
+        <v>0.919</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.915</v>
+        <v>0.919</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9916,13 +9925,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.183</v>
+        <v>0.173</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.212</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.212</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9939,27 +9948,27 @@
         <v>0</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.16</v>
+        <v>0.169</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.16</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>30</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.547</v>
+        <v>0.585</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>1</v>
@@ -9973,19 +9982,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>19</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.453</v>
+        <v>0.415</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.996</v>
+        <v>0.995</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>1</v>
@@ -9996,10 +10005,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>64</v>
@@ -10008,21 +10017,21 @@
         <v>0</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.37</v>
+        <v>0.385</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.37</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>56</v>
@@ -10034,64 +10043,64 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.366</v>
+        <v>0.352</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.366</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>17</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.706</v>
+        <v>0.713</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.912</v>
+        <v>0.913</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="G12" s="17" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>27</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.238</v>
+        <v>0.232</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.701</v>
+        <v>0.703</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.919</v>
+        <v>0.916</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.919</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>22</v>
@@ -10100,21 +10109,21 @@
         <v>0.033</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.187</v>
+        <v>0.183</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.448</v>
+        <v>0.445</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>0.448</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>41</v>
@@ -10123,73 +10132,73 @@
         <v>0.023</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.2</v>
+        <v>0.201</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.411</v>
+        <v>0.405</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>0.411</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.824</v>
+        <v>0.826</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.951</v>
+        <v>0.954</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>0.951</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.427</v>
+        <v>0.432</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.815</v>
+        <v>0.813</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.948</v>
+        <v>0.944</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.948</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>42</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>0.345</v>
@@ -10203,42 +10212,42 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>83</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E19" s="11" t="n">
         <v>0.016</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.079</v>
+        <v>0.08</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.079</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>10</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.697</v>
+        <v>0.689</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.89</v>
+        <v>0.887</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>0.996</v>
@@ -10249,56 +10258,56 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>33</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.263</v>
+        <v>0.27</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.762</v>
+        <v>0.759</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.96</v>
+        <v>0.961</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.96</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>23</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.318</v>
+        <v>0.324</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>82</v>
@@ -10310,41 +10319,41 @@
         <v>0.03</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>38</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.296</v>
+        <v>0.292</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.561</v>
+        <v>0.551</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.954</v>
+        <v>0.951</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>0.954</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>8</v>
@@ -10353,44 +10362,44 @@
         <v>0.37</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.72</v>
+        <v>0.721</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.89</v>
+        <v>0.891</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.89</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>18</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.318</v>
+        <v>0.323</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.676</v>
+        <v>0.686</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.865</v>
+        <v>0.868</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.865</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>45</v>
@@ -10399,211 +10408,211 @@
         <v>0.016</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.694</v>
+        <v>0.692</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.911</v>
+        <v>0.908</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.974</v>
+        <v>0.972</v>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.974</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>16</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.21</v>
+        <v>0.212</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>67</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.07</v>
+        <v>0.069</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.57</v>
+        <v>0.562</v>
       </c>
       <c r="G30" s="17" t="n">
-        <v>0.57</v>
+        <v>0.562</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>61</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.163</v>
+        <v>0.169</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.35</v>
+        <v>0.357</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0.35</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>9</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.46</v>
+        <v>0.456</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.875</v>
+        <v>0.876</v>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.875</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>29</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.215</v>
+        <v>0.222</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.526</v>
+        <v>0.537</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.712</v>
+        <v>0.72</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.712</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>20</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.492</v>
+        <v>0.48</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.655</v>
+        <v>0.643</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.655</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>85</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.087</v>
+        <v>0.085</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.246</v>
+        <v>0.245</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.396</v>
+        <v>0.392</v>
       </c>
       <c r="G35" s="20" t="n">
-        <v>0.396</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C36" s="8" t="n">
         <v>3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.684</v>
+        <v>0.68</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>0.969</v>
@@ -10617,85 +10626,85 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C37" s="8" t="n">
         <v>31</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.296</v>
+        <v>0.298</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C38" s="8" t="n">
         <v>15</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.618</v>
+        <v>0.619</v>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.618</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>57</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>0.017</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C40" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.947</v>
+        <v>0.945</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>0.994</v>
@@ -10709,33 +10718,33 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C41" s="8" t="n">
         <v>11</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.036</v>
+        <v>0.039</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>0.739</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.858</v>
+        <v>0.856</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.858</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>73</v>
@@ -10747,18 +10756,18 @@
         <v>0.165</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.528</v>
+        <v>0.536</v>
       </c>
       <c r="G42" s="20" t="n">
-        <v>0.528</v>
+        <v>0.536</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>34</v>
@@ -10767,159 +10776,159 @@
         <v>0.006</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.102</v>
+        <v>0.101</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.212</v>
+        <v>0.213</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.212</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>13</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.684</v>
+        <v>0.68</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.922</v>
+        <v>0.916</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.985</v>
+        <v>0.983</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.985</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.248</v>
+        <v>0.244</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.666</v>
+        <v>0.671</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.805</v>
+        <v>0.809</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>0.805</v>
+        <v>0.809</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>46</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.05</v>
+        <v>0.056</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.252</v>
+        <v>0.253</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>50</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.16</v>
+        <v>0.159</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="G47" s="20" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.867</v>
+        <v>0.866</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.992</v>
+        <v>0.993</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="G48" s="17" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>24</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.127</v>
+        <v>0.129</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.951</v>
+        <v>0.948</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.951</v>
+        <v>0.948</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>28</v>
@@ -10931,18 +10940,18 @@
         <v>0.2</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.461</v>
+        <v>0.465</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>0.461</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
@@ -10951,13 +10960,13 @@
         <v>0.001</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.175</v>
+        <v>0.178</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0.175</v>
+        <v>0.178</v>
       </c>
     </row>
   </sheetData>
@@ -10986,7 +10995,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -11016,7 +11025,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -11025,285 +11034,285 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>275</v>
-      </c>
       <c r="C12" s="22" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="C15" s="22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -11339,7 +11348,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -11352,97 +11361,97 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.974</v>
+        <v>0.972</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.813</v>
+        <v>0.815</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.587</v>
+        <v>0.59</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.438</v>
+        <v>0.435</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.301</v>
+        <v>0.298</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.195</v>
+        <v>0.193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.836</v>
+        <v>0.84</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.624</v>
+        <v>0.632</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.442</v>
+        <v>0.45</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.297</v>
+        <v>0.296</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.188</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>3</v>
@@ -11451,27 +11460,27 @@
         <v>0.998</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.798</v>
+        <v>0.794</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.582</v>
+        <v>0.577</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.404</v>
+        <v>0.394</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.241</v>
+        <v>0.238</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>4</v>
@@ -11480,306 +11489,306 @@
         <v>0.999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.857</v>
+        <v>0.856</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.544</v>
+        <v>0.55</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>0.352</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>13</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.985</v>
+        <v>0.983</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.722</v>
+        <v>0.715</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.478</v>
+        <v>0.467</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.229</v>
+        <v>0.224</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.951</v>
+        <v>0.954</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.658</v>
+        <v>0.662</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>0.316</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.184</v>
+        <v>0.182</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.087</v>
+        <v>0.088</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>6</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0.948</v>
+        <v>0.944</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.644</v>
+        <v>0.645</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>0.3</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.167</v>
+        <v>0.166</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>0.079</v>
       </c>
       <c r="I10" s="25" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1</v>
+        <v>0.996</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.681</v>
+        <v>0.679</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.276</v>
+        <v>0.32</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.145</v>
+        <v>0.177</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.07</v>
+        <v>0.076</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.996</v>
+        <v>0.988</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.679</v>
+        <v>0.601</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.317</v>
+        <v>0.332</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.174</v>
+        <v>0.146</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="I12" s="25" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>98</v>
+        <v>215</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>97</v>
+        <v>214</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.987</v>
+        <v>0.809</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.596</v>
+        <v>0.508</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.339</v>
+        <v>0.311</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.148</v>
+        <v>0.138</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.067</v>
+        <v>0.066</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>212</v>
+        <v>49</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>211</v>
+        <v>45</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.805</v>
+        <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.507</v>
+        <v>0.663</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.314</v>
+        <v>0.26</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.068</v>
+        <v>0.06</v>
       </c>
       <c r="I14" s="25" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.858</v>
+        <v>0.98</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.577</v>
+        <v>0.579</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.306</v>
+        <v>0.302</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.123</v>
+        <v>0.136</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.055</v>
+        <v>0.058</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.981</v>
+        <v>0.856</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.577</v>
+        <v>0.586</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.293</v>
+        <v>0.307</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.133</v>
+        <v>0.127</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.054</v>
+        <v>0.058</v>
       </c>
       <c r="I16" s="25" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>8</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.89</v>
+        <v>0.891</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.498</v>
+        <v>0.504</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.277</v>
+        <v>0.274</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="I17" s="25" t="n">
         <v>0.02</v>
@@ -11787,10 +11796,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="8" t="n">
         <v>19</v>
@@ -11799,45 +11808,45 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.662</v>
+        <v>0.668</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.337</v>
+        <v>0.348</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.136</v>
+        <v>0.14</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.05</v>
+        <v>0.053</v>
       </c>
       <c r="I18" s="25" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>151</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>148</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>18</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.865</v>
+        <v>0.868</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.449</v>
+        <v>0.445</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.224</v>
+        <v>0.215</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.089</v>
+        <v>0.087</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="I19" s="25" t="n">
         <v>0.012</v>
@@ -11845,115 +11854,115 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>164</v>
+        <v>80</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.752</v>
+        <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.391</v>
+        <v>0.619</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.162</v>
+        <v>0.277</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.072</v>
+        <v>0.094</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="I20" s="25" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>23</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.318</v>
+        <v>0.324</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.143</v>
+        <v>0.14</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="I21" s="25" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1</v>
+        <v>0.749</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.58</v>
+        <v>0.382</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.235</v>
+        <v>0.156</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.07</v>
+        <v>0.067</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.02</v>
+        <v>0.024</v>
       </c>
       <c r="I22" s="25" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.875</v>
+        <v>0.445</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.339</v>
+        <v>0.195</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.143</v>
+        <v>0.086</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.048</v>
+        <v>0.037</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="I23" s="25" t="n">
         <v>0.004</v>
@@ -11961,28 +11970,28 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.448</v>
+        <v>0.948</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.195</v>
+        <v>0.391</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.092</v>
+        <v>0.171</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.039</v>
+        <v>0.048</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="I24" s="25" t="n">
         <v>0.004</v>
@@ -11990,28 +11999,28 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.618</v>
+        <v>0.876</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.266</v>
+        <v>0.336</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.105</v>
+        <v>0.138</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="I25" s="25" t="n">
         <v>0.004</v>
@@ -12019,31 +12028,31 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.951</v>
+        <v>0.619</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.39</v>
+        <v>0.265</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.169</v>
+        <v>0.106</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.047</v>
+        <v>0.038</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="I26" s="25" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12057,48 +12066,48 @@
         <v>25</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.915</v>
+        <v>0.919</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.377</v>
+        <v>0.372</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>0.15</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.043</v>
+        <v>0.048</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="I27" s="25" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="C28" s="8" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.411</v>
+        <v>0.961</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.155</v>
+        <v>0.339</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.063</v>
+        <v>0.095</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.02</v>
+        <v>0.028</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="I28" s="25" t="n">
         <v>0.002</v>
@@ -12106,57 +12115,57 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>27</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.919</v>
+        <v>0.916</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.339</v>
+        <v>0.335</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.126</v>
+        <v>0.12</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="I29" s="25" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C30" s="8" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.96</v>
+        <v>0.405</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.329</v>
+        <v>0.153</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.09</v>
+        <v>0.061</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="I30" s="25" t="n">
         <v>0.001</v>
@@ -12164,54 +12173,54 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>38</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.954</v>
+        <v>0.951</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.297</v>
+        <v>0.293</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.091</v>
+        <v>0.085</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>0.004</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.655</v>
+        <v>0.465</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.157</v>
+        <v>0.122</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.044</v>
+        <v>0.041</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0.002</v>
@@ -12222,28 +12231,28 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="C33" s="8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.783</v>
+        <v>0.213</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.214</v>
+        <v>0.081</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I33" s="25" t="n">
         <v>0</v>
@@ -12251,22 +12260,22 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="C34" s="8" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.474</v>
+        <v>0.72</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.108</v>
+        <v>0.123</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>0.005</v>
@@ -12280,25 +12289,25 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>221</v>
+        <v>177</v>
       </c>
       <c r="C35" s="8" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.461</v>
+        <v>0.643</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.124</v>
+        <v>0.152</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.008</v>
+        <v>0.009</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0.002</v>
@@ -12318,7 +12327,7 @@
         <v>40</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.16</v>
+        <v>0.169</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>0.039</v>
@@ -12338,25 +12347,25 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.712</v>
+        <v>0.783</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.124</v>
+        <v>0.214</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.025</v>
+        <v>0.04</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.004</v>
+        <v>0.009</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>0.001</v>
@@ -12367,22 +12376,22 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="C38" s="8" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.212</v>
+        <v>0.377</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.079</v>
+        <v>0.09</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.023</v>
+        <v>0.028</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>0.005</v>
@@ -12396,28 +12405,28 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>214</v>
+        <v>81</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="C39" s="8" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.374</v>
+        <v>0.385</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.09</v>
+        <v>0.067</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I39" s="25" t="n">
         <v>0</v>
@@ -12425,28 +12434,28 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="C40" s="8" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.37</v>
+        <v>0.473</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.07</v>
+        <v>0.108</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.01</v>
+        <v>0.031</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I40" s="25" t="n">
         <v>0</v>
@@ -12463,16 +12472,16 @@
         <v>60</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.212</v>
+        <v>0.2</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.046</v>
+        <v>0.038</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.009</v>
+        <v>0.008</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H41" s="11" t="n">
         <v>0</v>
@@ -12483,25 +12492,25 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" s="8" t="n">
         <v>56</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.366</v>
+        <v>0.352</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.068</v>
+        <v>0.058</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H42" s="11" t="n">
         <v>0</v>
@@ -12512,19 +12521,19 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C43" s="8" t="n">
         <v>83</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.079</v>
+        <v>0.08</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.009</v>
+        <v>0.01</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>0.001</v>
@@ -12541,19 +12550,19 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C44" s="8" t="n">
         <v>82</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="F44" s="11" t="n">
         <v>0.001</v>
@@ -12570,22 +12579,22 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C45" s="8" t="n">
         <v>45</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>0.001</v>
@@ -12599,19 +12608,19 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C46" s="8" t="n">
         <v>61</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.35</v>
+        <v>0.357</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>0.005</v>
@@ -12628,25 +12637,25 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>67</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.57</v>
+        <v>0.562</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.116</v>
+        <v>0.113</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H47" s="11" t="n">
         <v>0</v>
@@ -12657,19 +12666,19 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C48" s="8" t="n">
         <v>85</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.396</v>
+        <v>0.392</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.034</v>
+        <v>0.032</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>0.004</v>
@@ -12686,19 +12695,19 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C49" s="8" t="n">
         <v>57</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>0.003</v>
@@ -12715,19 +12724,19 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C50" s="8" t="n">
         <v>73</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.528</v>
+        <v>0.536</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>0.005</v>
@@ -12744,22 +12753,22 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C51" s="8" t="n">
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.175</v>
+        <v>0.178</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="G51" s="11" t="n">
         <v>0.001</v>
@@ -12801,7 +12810,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -12809,7 +12818,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
@@ -12817,184 +12826,184 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B4" s="28" t="n">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
       <c r="C4" s="28" t="n">
-        <v>0.177</v>
+        <v>0.19</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.166</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B5" s="28" t="n">
-        <v>0.195</v>
+        <v>0.193</v>
       </c>
       <c r="C5" s="28" t="n">
-        <v>0.148</v>
+        <v>0.137</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.162</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B6" s="28" t="n">
-        <v>0.188</v>
+        <v>0.19</v>
       </c>
       <c r="C6" s="28" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>0.118</v>
+        <v>0.099</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0.126</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B7" s="28" t="n">
-        <v>0.102</v>
+        <v>0.103</v>
       </c>
       <c r="C7" s="28" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="D7" s="20" t="n">
-        <v>0.108</v>
+        <v>0.127</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>0.027</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>0.099</v>
+        <v>0.081</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>0.077</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B9" s="28" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>0.081</v>
+        <v>0.074</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B10" s="28" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="C10" s="28" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.05</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B11" s="28" t="n">
         <v>0.02</v>
       </c>
       <c r="C11" s="28" t="n">
-        <v>0.047</v>
+        <v>0.05</v>
       </c>
       <c r="D11" s="28" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="B12" s="28" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="C12" s="28" t="n">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="D12" s="28" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="B13" s="28" t="n">
-        <v>0.02</v>
+        <v>0.051</v>
       </c>
       <c r="C13" s="28" t="n">
-        <v>0.032</v>
+        <v>0.019</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B14" s="28" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="C14" s="28" t="n">
-        <v>0.022</v>
+        <v>0.029</v>
       </c>
       <c r="D14" s="28" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="B15" s="28" t="n">
-        <v>0.029</v>
+        <v>0.022</v>
       </c>
       <c r="C15" s="28" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="D15" s="28" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
   </sheetData>
@@ -13028,7 +13037,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -13036,7 +13045,7 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="29" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -13044,307 +13053,307 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="30" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>186</v>
+        <v>80</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="30" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="30" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13352,18 +13361,18 @@
         <v>67</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Partidos A-L'!$A$3:$R$75</definedName>
@@ -343,13 +343,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -368,7 +368,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -420,13 +420,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -445,7 +445,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -497,13 +497,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -522,7 +522,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -574,13 +574,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -599,7 +599,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -651,13 +651,13 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -676,7 +676,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -726,13 +726,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -751,7 +751,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -803,13 +803,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -828,7 +828,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -880,13 +880,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -905,7 +905,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -957,13 +957,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -982,7 +982,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1034,13 +1034,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1059,7 +1059,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1111,13 +1111,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1136,7 +1136,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1188,13 +1188,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1213,7 +1213,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1265,13 +1265,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1290,7 +1290,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1342,7 +1342,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1357,9 +1357,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1379,9 +1379,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1401,9 +1401,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1423,9 +1423,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1445,9 +1445,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1467,9 +1467,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1489,9 +1489,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1511,9 +1511,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <c:chart r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1533,9 +1533,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <c:chart r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1555,9 +1555,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <c:chart r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1577,9 +1577,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <c:chart r:id="rId11"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1599,9 +1599,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <c:chart r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1611,7 +1611,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -1626,9 +1626,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4965,12 +4965,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 – 4</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Japón</t>
+          <t>Ganó Japón</t>
         </is>
       </c>
       <c r="O37" s="12" t="inlineStr">
@@ -4978,9 +4978,9 @@
           <t>Japón</t>
         </is>
       </c>
-      <c r="P37" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P37" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q37" s="14" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 – 0</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>Favorito: España</t>
+          <t>Ganó España</t>
         </is>
       </c>
       <c r="O42" s="12" t="inlineStr">
@@ -5383,9 +5383,9 @@
           <t>España</t>
         </is>
       </c>
-      <c r="P42" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P42" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q42" s="14" t="inlineStr">
@@ -5420,7 +5420,7 @@
           <t>Hard Rock Stadium, Miami</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
@@ -5449,24 +5449,24 @@
       <c r="L43" s="11" t="n">
         <v>0.147</v>
       </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="10" t="inlineStr">
-        <is>
-          <t>Favorito: Uruguay</t>
-        </is>
-      </c>
-      <c r="O43" s="12" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="P43" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M43" s="15" t="inlineStr">
+        <is>
+          <t>2 – 2</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="O43" s="15" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="P43" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q43" s="14" t="inlineStr">
@@ -5825,7 +5825,7 @@
           <t>SoFi Stadium, Los Angeles</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>Bélgica</t>
         </is>
@@ -5854,24 +5854,24 @@
       <c r="L48" s="11" t="n">
         <v>0.266</v>
       </c>
-      <c r="M48" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N48" s="10" t="inlineStr">
-        <is>
-          <t>Favorito: Bélgica</t>
-        </is>
-      </c>
-      <c r="O48" s="12" t="inlineStr">
-        <is>
-          <t>Bélgica</t>
-        </is>
-      </c>
-      <c r="P48" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>0 – 0</t>
+        </is>
+      </c>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="P48" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q48" s="14" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="M49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="N49" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Egipto</t>
+          <t>Ganó Egipto</t>
         </is>
       </c>
       <c r="O49" s="12" t="inlineStr">
@@ -5950,9 +5950,9 @@
           <t>Egipto</t>
         </is>
       </c>
-      <c r="P49" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P49" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q49" s="14" t="inlineStr">
@@ -8191,10 +8191,10 @@
         <v>0.77</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -8218,10 +8218,10 @@
         <v>0.173</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -8245,10 +8245,10 @@
         <v>0.057</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.175</v>
+        <v>0.177</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.175</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="8">
@@ -8326,10 +8326,10 @@
         <v>0.006</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="11">
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="12">
@@ -8407,10 +8407,10 @@
         <v>0.593</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.885</v>
+        <v>0.893</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.885</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="14">
@@ -8434,10 +8434,10 @@
         <v>0.407</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -8461,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="16">
@@ -8542,10 +8542,10 @@
         <v>0.148</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.829</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="19">
@@ -8650,10 +8650,10 @@
         <v>0.098</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="23">
@@ -8691,17 +8691,17 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.715</v>
+        <v>0.369</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.992</v>
+        <v>0.789</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1</v>
@@ -8718,23 +8718,23 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.079</v>
+        <v>0.551</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.312</v>
+        <v>0.99</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -8745,23 +8745,23 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.185</v>
+        <v>0.08</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.67</v>
+        <v>0.221</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.867</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.867</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -8779,16 +8779,16 @@
         <v>45</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -8806,16 +8806,16 @@
         <v>2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.832</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.908</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.973</v>
+        <v>1</v>
       </c>
       <c r="G28" s="17" t="n">
-        <v>0.973</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -8826,23 +8826,23 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.212</v>
+        <v>0.038</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.578</v>
+        <v>0.593</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.754</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.754</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -8851,25 +8851,25 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.346</v>
+        <v>0.208</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="G30" s="17" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.435</v>
+      </c>
+      <c r="G30" s="20" t="n">
+        <v>0.435</v>
       </c>
     </row>
     <row r="31">
@@ -8887,16 +8887,16 @@
         <v>61</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.169</v>
+        <v>0.267</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.361</v>
+        <v>0.317</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0.361</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="32">
@@ -8907,23 +8907,23 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.456</v>
+        <v>0.522</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.738</v>
+        <v>0.707</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
       <c r="G32" s="17" t="n">
-        <v>0.879</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -8934,23 +8934,23 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.222</v>
+        <v>0.188</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.537</v>
+        <v>0.742</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.725</v>
+        <v>0.876</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.725</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="34">
@@ -8968,16 +8968,16 @@
         <v>20</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.237</v>
+        <v>0.29</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.48</v>
+        <v>0.466</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.649</v>
+        <v>0.717</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.649</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="35">
@@ -8986,7 +8986,7 @@
           <t>H</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Nueva Zelanda</t>
         </is>
@@ -8995,16 +8995,16 @@
         <v>85</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.245</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="G35" s="20" t="n">
-        <v>0.396</v>
+        <v>0.126</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>0.126</v>
       </c>
     </row>
     <row r="36">
@@ -9055,10 +9055,10 @@
         <v>0.79</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="38">
@@ -9082,10 +9082,10 @@
         <v>0.224</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.639</v>
+        <v>0.642</v>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.639</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="39">
@@ -9109,10 +9109,10 @@
         <v>0.017</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="40">
@@ -9163,10 +9163,10 @@
         <v>0.739</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.862</v>
+        <v>0.864</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.862</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="42">
@@ -9190,10 +9190,10 @@
         <v>0.165</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.57</v>
+        <v>0.583</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.57</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="43">
@@ -9217,10 +9217,10 @@
         <v>0.101</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.224</v>
+        <v>0.226</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.224</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="44">
@@ -9271,10 +9271,10 @@
         <v>0.671</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -9325,10 +9325,10 @@
         <v>0.159</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.394</v>
+        <v>0.399</v>
       </c>
       <c r="G47" s="20" t="n">
-        <v>0.394</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="48">
@@ -9379,10 +9379,10 @@
         <v>0.781</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.96</v>
+        <v>0.962</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.96</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="50">
@@ -9406,10 +9406,10 @@
         <v>0.2</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.48</v>
+        <v>0.486</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>0.48</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="51">
@@ -9433,10 +9433,10 @@
         <v>0.027</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
     </row>
   </sheetData>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>Paraguay (3º C)</t>
+          <t>Escocia (3º D)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>Suecia (2F)</t>
+          <t>Japón (2F)</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>Escocia (3º D)</t>
+          <t>Paraguay (3º C)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>Senegal (3º I)</t>
+          <t>Irán (3º H)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>RD Congo (3º K)</t>
+          <t>Ghana (3º J)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Ghana (3º J)</t>
+          <t>Senegal (3º I)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr"/>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>Bélgica (1H)</t>
+          <t>Egipto (1H)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>Ecuador (3º E)</t>
+          <t>Suecia (3º F)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>Egipto (2H)</t>
+          <t>Bélgica (2H)</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>Uruguay (2G)</t>
+          <t>Cabo Verde (2G)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -10025,67 +10025,67 @@
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.852</v>
+        <v>0.854</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.643</v>
+        <v>0.616</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.453</v>
+        <v>0.456</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.3</v>
+        <v>0.315</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.192</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.973</v>
+        <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.579</v>
+        <v>0.644</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.427</v>
+        <v>0.451</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.291</v>
+        <v>0.302</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="6">
@@ -10106,19 +10106,19 @@
         <v>0.998</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.839</v>
+        <v>0.826</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.581</v>
+        <v>0.571</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.396</v>
+        <v>0.389</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.237</v>
+        <v>0.228</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="7">
@@ -10139,19 +10139,19 @@
         <v>0.999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.856</v>
+        <v>0.819</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.535</v>
+        <v>0.532</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.186</v>
+        <v>0.184</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -10172,16 +10172,16 @@
         <v>0.985</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>0.479</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.229</v>
+        <v>0.231</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="I8" s="20" t="n">
         <v>0.053</v>
@@ -10190,7 +10190,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -10199,31 +10199,31 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.719</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.329</v>
+        <v>0.37</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.182</v>
+        <v>0.214</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.09</v>
+        <v>0.098</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.039</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -10232,25 +10232,25 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.713</v>
+        <v>0.754</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.332</v>
+        <v>0.324</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.191</v>
+        <v>0.18</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="11">
@@ -10271,82 +10271,82 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>0.21</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.093</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>1</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.615</v>
+        <v>0.513</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.34</v>
+        <v>0.319</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>0.065</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.8139999999999999</v>
+        <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.514</v>
+        <v>0.588</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.316</v>
+        <v>0.325</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.14</v>
+        <v>0.134</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.066</v>
+        <v>0.064</v>
       </c>
       <c r="I13" s="24" t="n">
         <v>0.026</v>
@@ -10355,67 +10355,67 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.617</v>
+        <v>0.676</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.363</v>
+        <v>0.264</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.156</v>
+        <v>0.135</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.065</v>
+        <v>0.062</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.265</v>
+        <v>0.337</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.135</v>
+        <v>0.144</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="16">
@@ -10433,22 +10433,22 @@
         <v>31</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.987</v>
+        <v>0.988</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.64</v>
+        <v>0.632</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.313</v>
+        <v>0.302</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.137</v>
+        <v>0.133</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="17">
@@ -10466,22 +10466,22 @@
         <v>11</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.862</v>
+        <v>0.864</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.587</v>
+        <v>0.614</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.307</v>
+        <v>0.32</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.126</v>
+        <v>0.124</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18">
@@ -10502,19 +10502,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.675</v>
+        <v>0.66</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.348</v>
+        <v>0.343</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.138</v>
+        <v>0.137</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="19">
@@ -10532,22 +10532,22 @@
         <v>18</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.197</v>
+        <v>0.248</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.077</v>
+        <v>0.097</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.03</v>
+        <v>0.037</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="20">
@@ -10568,10 +10568,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.629</v>
+        <v>0.608</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.279</v>
+        <v>0.272</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.093</v>
@@ -10580,7 +10580,7 @@
         <v>0.03</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -10598,22 +10598,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.754</v>
+        <v>0.435</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.364</v>
+        <v>0.212</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.149</v>
+        <v>0.09</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.065</v>
+        <v>0.039</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.023</v>
+        <v>0.015</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="22">
@@ -10631,19 +10631,19 @@
         <v>24</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.96</v>
+        <v>0.962</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.175</v>
+        <v>0.18</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="I22" s="24" t="n">
         <v>0.004</v>
@@ -10664,19 +10664,19 @@
         <v>15</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.639</v>
+        <v>0.642</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.291</v>
+        <v>0.294</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>0.004</v>
@@ -10685,94 +10685,94 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.879</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.335</v>
+        <v>0.366</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.137</v>
+        <v>0.147</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>0.046</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.876</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.372</v>
+        <v>0.266</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.147</v>
+        <v>0.108</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.342</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.139</v>
+        <v>0.279</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.061</v>
+        <v>0.107</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.025</v>
+        <v>0.036</v>
       </c>
       <c r="H26" s="11" t="n">
         <v>0.01</v>
@@ -10784,28 +10784,28 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.8</v>
+        <v>0.341</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.275</v>
+        <v>0.132</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.104</v>
+        <v>0.056</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>0.01</v>
@@ -10829,13 +10829,13 @@
         <v>27</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.885</v>
+        <v>0.893</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.101</v>
+        <v>0.102</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>0.028</v>
@@ -10862,16 +10862,16 @@
         <v>22</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>0.002</v>
@@ -10898,13 +10898,13 @@
         <v>0.922</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.249</v>
+        <v>0.247</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0.004</v>
@@ -10928,22 +10928,22 @@
         <v>38</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.879</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.236</v>
+        <v>0.262</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.063</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>0.003</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="32">
@@ -10961,13 +10961,13 @@
         <v>28</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.48</v>
+        <v>0.486</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.125</v>
+        <v>0.127</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="G32" s="11" t="n">
         <v>0.008</v>
@@ -10982,28 +10982,28 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Uzbekistán</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.394</v>
+        <v>0.717</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.092</v>
+        <v>0.17</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.03</v>
+        <v>0.048</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>0.002</v>
@@ -11015,25 +11015,25 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Uzbekistán</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.725</v>
+        <v>0.399</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.122</v>
+        <v>0.092</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>0.005</v>
@@ -11048,28 +11048,28 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.224</v>
+        <v>1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.083</v>
+        <v>0.205</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.024</v>
+        <v>0.048</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0.001</v>
@@ -11081,28 +11081,28 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.226</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.168</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>0.001</v>
@@ -11114,31 +11114,31 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.649</v>
+        <v>0.478</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.152</v>
+        <v>0.109</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I37" s="24" t="n">
         <v>0</v>
@@ -11147,28 +11147,28 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.478</v>
+        <v>0.829</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.109</v>
+        <v>0.187</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.031</v>
+        <v>0.038</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0.001</v>
@@ -11192,13 +11192,13 @@
         <v>40</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.175</v>
+        <v>0.177</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>0.002</v>
@@ -11225,13 +11225,13 @@
         <v>64</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.388</v>
+        <v>0.387</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>0.001</v>
@@ -11258,7 +11258,7 @@
         <v>60</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>0.037</v>
@@ -11291,13 +11291,13 @@
         <v>56</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>0.001</v>
@@ -11360,7 +11360,7 @@
         <v>0.181</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="F44" s="11" t="n">
         <v>0.001</v>
@@ -11390,16 +11390,16 @@
         <v>45</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
         <v>0</v>
@@ -11423,13 +11423,13 @@
         <v>61</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.361</v>
+        <v>0.317</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>0</v>
@@ -11456,13 +11456,13 @@
         <v>67</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.101</v>
+        <v>0.107</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0.002</v>
@@ -11489,13 +11489,13 @@
         <v>85</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.396</v>
+        <v>0.126</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.033</v>
+        <v>0.006</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
@@ -11522,16 +11522,16 @@
         <v>57</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -11555,10 +11555,10 @@
         <v>73</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.57</v>
+        <v>0.583</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>0.005</v>
@@ -11588,10 +11588,10 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>0.008</v>
@@ -11673,13 +11673,13 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>0.19</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="5">
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.188</v>
+        <v>0.202</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.137</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.152</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="6">
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.192</v>
+        <v>0.189</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.099</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="7">
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.127</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="8">
@@ -11743,7 +11743,7 @@
         <v>0.081</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="9">
@@ -11769,7 +11769,7 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0.064</v>
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0.05</v>
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.038</v>
+        <v>0.042</v>
       </c>
       <c r="C12" s="27" t="n">
         <v>0.026</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="13">
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="C14" s="27" t="n">
         <v>0.029</v>
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>0.026</v>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -2479,7 +2479,7 @@
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.02 – 1.39</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.08 – 0.35</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.17 – 0.32</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.51 – 0.99</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.56 – 0.23</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.89 – 1.22</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.05 – 0.48</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.61 – 1.01</t>
         </is>
       </c>
     </row>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.05 – 2.13</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.947</v>
+        <v>0.949</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>1</v>
@@ -8185,16 +8185,16 @@
         <v>25</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.77</v>
+        <v>0.762</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8215,13 +8215,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.173</v>
+        <v>0.184</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.2</v>
+        <v>0.211</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.2</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="7">
@@ -8242,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.177</v>
+        <v>0.168</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.177</v>
+        <v>0.168</v>
       </c>
     </row>
     <row r="8">
@@ -8266,7 +8266,7 @@
         <v>30</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.585</v>
+        <v>0.588</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>1</v>
@@ -8293,10 +8293,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.415</v>
+        <v>0.412</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>1</v>
@@ -8323,13 +8323,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="11">
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="12">
@@ -8374,7 +8374,7 @@
         <v>17</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.994</v>
+        <v>0.993</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>1</v>
@@ -8401,16 +8401,16 @@
         <v>27</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.593</v>
+        <v>0.613</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.893</v>
+        <v>0.892</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.893</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="14">
@@ -8431,13 +8431,13 @@
         <v>0.001</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.407</v>
+        <v>0.387</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.792</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="15">
@@ -8461,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.124</v>
+        <v>0.136</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.124</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="16">
@@ -8482,10 +8482,10 @@
         <v>6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.633</v>
+        <v>0.624</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.868</v>
+        <v>0.863</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>1</v>
@@ -8509,10 +8509,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.334</v>
+        <v>0.341</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.985</v>
+        <v>0.983</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>1</v>
@@ -8536,16 +8536,16 @@
         <v>42</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.148</v>
+        <v>0.154</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.829</v>
+        <v>0.841</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.829</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="19">
@@ -8620,13 +8620,13 @@
         <v>0.002</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.78</v>
+        <v>0.777</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.922</v>
+        <v>0.92</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.922</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="22">
@@ -8647,13 +8647,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.098</v>
+        <v>0.103</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.341</v>
+        <v>0.357</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.341</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="23">
@@ -8674,13 +8674,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.122</v>
+        <v>0.12</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.181</v>
+        <v>0.182</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.181</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="24">
@@ -8698,10 +8698,10 @@
         <v>18</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.789</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1</v>
@@ -8725,10 +8725,10 @@
         <v>8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.551</v>
+        <v>0.57</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.99</v>
+        <v>0.993</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>1</v>
@@ -8752,16 +8752,16 @@
         <v>38</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.221</v>
+        <v>0.19</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.929</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="27">
@@ -8806,10 +8806,10 @@
         <v>2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.832</v>
+        <v>0.83</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>1</v>
@@ -8836,13 +8836,13 @@
         <v>0.038</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.593</v>
+        <v>0.598</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="30">
@@ -8860,16 +8860,16 @@
         <v>16</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.208</v>
+        <v>0.214</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.435</v>
+        <v>0.44</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.435</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="31">
@@ -8890,13 +8890,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.267</v>
+        <v>0.258</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.317</v>
+        <v>0.31</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0.317</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="32">
@@ -8917,7 +8917,7 @@
         <v>0.522</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.707</v>
+        <v>0.706</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>1</v>
@@ -8944,13 +8944,13 @@
         <v>0.188</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.876</v>
+        <v>0.875</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.876</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="34">
@@ -8974,10 +8974,10 @@
         <v>0.466</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.717</v>
+        <v>0.715</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.717</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="35">
@@ -8998,13 +8998,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="36">
@@ -9022,7 +9022,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.68</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>0.969</v>
@@ -9055,10 +9055,10 @@
         <v>0.79</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.988</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="38">
@@ -9076,16 +9076,16 @@
         <v>15</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>0.224</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.642</v>
+        <v>0.644</v>
       </c>
       <c r="G38" s="17" t="n">
-        <v>0.642</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="39">
@@ -9103,16 +9103,16 @@
         <v>57</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>0.017</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.117</v>
+        <v>0.112</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.117</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="40">
@@ -9130,10 +9130,10 @@
         <v>4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.945</v>
+        <v>0.949</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.994</v>
+        <v>0.995</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>0.999</v>
@@ -9157,16 +9157,16 @@
         <v>11</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="E41" s="11" t="n">
         <v>0.739</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.864</v>
+        <v>0.867</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.864</v>
+        <v>0.867</v>
       </c>
     </row>
     <row r="42">
@@ -9190,10 +9190,10 @@
         <v>0.165</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.583</v>
+        <v>0.575</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.583</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="43">
@@ -9217,10 +9217,10 @@
         <v>0.101</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.226</v>
+        <v>0.223</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.226</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="44">
@@ -9238,16 +9238,16 @@
         <v>13</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.916</v>
+        <v>0.922</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.985</v>
+        <v>0.986</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.985</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="45">
@@ -9265,16 +9265,16 @@
         <v>5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.244</v>
+        <v>0.243</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.671</v>
+        <v>0.672</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -9292,16 +9292,16 @@
         <v>46</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.056</v>
+        <v>0.049</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.253</v>
+        <v>0.243</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.478</v>
+        <v>0.474</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.478</v>
+        <v>0.474</v>
       </c>
     </row>
     <row r="47">
@@ -9319,16 +9319,16 @@
         <v>50</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.159</v>
+        <v>0.163</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
       <c r="G47" s="20" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="48">
@@ -9346,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.866</v>
+        <v>0.865</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>0.993</v>
@@ -9376,13 +9376,13 @@
         <v>0.129</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.781</v>
+        <v>0.782</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.962</v>
+        <v>0.961</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.962</v>
+        <v>0.961</v>
       </c>
     </row>
     <row r="50">
@@ -9403,13 +9403,13 @@
         <v>0.005</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.2</v>
+        <v>0.199</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.486</v>
+        <v>0.484</v>
       </c>
       <c r="G50" s="20" t="n">
-        <v>0.486</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="51">
@@ -9427,7 +9427,7 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>0.027</v>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>Paraguay (3º C)</t>
+          <t>Suecia (3º F)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>Irán (3º H)</t>
+          <t>Paraguay (3º C)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Ghana (3º J)</t>
+          <t>Senegal (3º I)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Senegal (3º I)</t>
+          <t>Ghana (3º J)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr"/>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>Suecia (3º F)</t>
+          <t>Ecuador (3º E)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -10040,19 +10040,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.854</v>
+        <v>0.851</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.616</v>
+        <v>0.615</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="H4" s="11" t="n">
         <v>0.315</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -10073,19 +10073,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.85</v>
+        <v>0.846</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.644</v>
+        <v>0.647</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.302</v>
+        <v>0.303</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.189</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="6">
@@ -10106,19 +10106,19 @@
         <v>0.998</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.571</v>
+        <v>0.574</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.389</v>
+        <v>0.393</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.228</v>
+        <v>0.232</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.13</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="7">
@@ -10139,19 +10139,19 @@
         <v>0.999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.819</v>
+        <v>0.82</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.532</v>
+        <v>0.53</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.184</v>
+        <v>0.181</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="8">
@@ -10169,22 +10169,22 @@
         <v>13</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.985</v>
+        <v>0.986</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.729</v>
+        <v>0.732</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.479</v>
+        <v>0.48</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>0.053</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -10205,247 +10205,247 @@
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.214</v>
+        <v>0.206</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.098</v>
+        <v>0.093</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.042</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.754</v>
+        <v>0.778</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.324</v>
+        <v>0.34</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.18</v>
+        <v>0.201</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.779</v>
+        <v>0.752</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.352</v>
+        <v>0.32</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.21</v>
+        <v>0.182</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.8149999999999999</v>
+        <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.513</v>
+        <v>0.577</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.319</v>
+        <v>0.326</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.137</v>
+        <v>0.134</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.065</v>
+        <v>0.066</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.588</v>
+        <v>0.517</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.325</v>
+        <v>0.322</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.134</v>
+        <v>0.138</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>0.064</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.676</v>
+        <v>0.596</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.264</v>
+        <v>0.354</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.135</v>
+        <v>0.151</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.583</v>
+        <v>0.677</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.337</v>
+        <v>0.261</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.144</v>
+        <v>0.13</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.988</v>
+        <v>0.867</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.632</v>
+        <v>0.609</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.302</v>
+        <v>0.32</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.133</v>
+        <v>0.124</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>0.021</v>
@@ -10454,34 +10454,34 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.864</v>
+        <v>0.987</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.614</v>
+        <v>0.633</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.32</v>
+        <v>0.302</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.124</v>
+        <v>0.131</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
@@ -10502,19 +10502,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.66</v>
+        <v>0.664</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="G18" s="11" t="n">
         <v>0.137</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="19">
@@ -10535,19 +10535,19 @@
         <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.51</v>
+        <v>0.541</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.248</v>
+        <v>0.288</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.097</v>
+        <v>0.116</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.037</v>
+        <v>0.046</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="20">
@@ -10568,46 +10568,46 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.608</v>
+        <v>0.615</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.272</v>
+        <v>0.27</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.435</v>
+        <v>0.961</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.212</v>
+        <v>0.397</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.039</v>
+        <v>0.046</v>
       </c>
       <c r="H21" s="11" t="n">
         <v>0.015</v>
@@ -10619,64 +10619,64 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.962</v>
+        <v>0.357</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.398</v>
+        <v>0.14</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.18</v>
+        <v>0.063</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.047</v>
+        <v>0.027</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.642</v>
+        <v>0.44</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.294</v>
+        <v>0.219</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.111</v>
+        <v>0.095</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.039</v>
+        <v>0.041</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>0.004</v>
@@ -10685,64 +10685,64 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.366</v>
+        <v>0.269</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.147</v>
+        <v>0.109</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.046</v>
+        <v>0.039</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.876</v>
+        <v>0.644</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.266</v>
+        <v>0.288</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.108</v>
+        <v>0.103</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>0.036</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="I25" s="24" t="n">
         <v>0.003</v>
@@ -10751,31 +10751,31 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.279</v>
+        <v>0.364</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.107</v>
+        <v>0.142</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.036</v>
+        <v>0.044</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.003</v>
@@ -10784,40 +10784,40 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.341</v>
+        <v>0.136</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.132</v>
+        <v>0.055</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.056</v>
+        <v>0.022</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -10826,22 +10826,22 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.893</v>
+        <v>0.792</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.281</v>
+        <v>0.246</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.102</v>
+        <v>0.09</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0.001</v>
@@ -10850,7 +10850,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -10859,22 +10859,22 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.124</v>
+        <v>0.892</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.043</v>
+        <v>0.267</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.016</v>
+        <v>0.094</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0.001</v>
@@ -10895,19 +10895,19 @@
         <v>33</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.922</v>
+        <v>0.92</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.247</v>
+        <v>0.242</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.073</v>
+        <v>0.065</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>0.001</v>
@@ -10916,61 +10916,61 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.262</v>
+        <v>0.168</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.049</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.486</v>
+        <v>0.929</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.127</v>
+        <v>0.239</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.043</v>
+        <v>0.057</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0.002</v>
@@ -10982,28 +10982,28 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.717</v>
+        <v>0.484</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>0.002</v>
@@ -11015,28 +11015,28 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Uzbekistán</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.399</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.092</v>
+        <v>0.212</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.03</v>
+        <v>0.048</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>0.001</v>
@@ -11048,28 +11048,28 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1</v>
+        <v>0.474</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.205</v>
+        <v>0.109</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.048</v>
+        <v>0.032</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0.001</v>
@@ -11081,28 +11081,28 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.226</v>
+        <v>0.841</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.024</v>
+        <v>0.044</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>0.001</v>
@@ -11114,25 +11114,25 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.478</v>
+        <v>0.223</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.109</v>
+        <v>0.082</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.032</v>
+        <v>0.024</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>0.005</v>
@@ -11147,31 +11147,31 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.829</v>
+        <v>0.168</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.187</v>
+        <v>0.032</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.038</v>
+        <v>0.007</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>0</v>
@@ -11180,31 +11180,31 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Uzbekistán</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.177</v>
+        <v>0.403</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.034</v>
+        <v>0.091</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.007</v>
+        <v>0.029</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>0</v>
@@ -11213,25 +11213,25 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.387</v>
+        <v>0.211</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.051</v>
+        <v>0.043</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="G40" s="11" t="n">
         <v>0.001</v>
@@ -11246,28 +11246,28 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.2</v>
+        <v>0.699</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.037</v>
+        <v>0.109</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.007</v>
+        <v>0.013</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H41" s="11" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -11288,16 +11288,16 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.354</v>
+        <v>0.385</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.042</v>
+        <v>0.05</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>0.001</v>
@@ -11312,28 +11312,28 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.352</v>
       </c>
       <c r="E43" s="11" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G43" s="11" t="n">
         <v>0.001</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>0</v>
@@ -11345,25 +11345,25 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Haití</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.181</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.015</v>
+        <v>0.001</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
@@ -11378,25 +11378,25 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Túnez</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>0</v>
@@ -11411,25 +11411,25 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Túnez</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.317</v>
+        <v>0</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>0</v>
@@ -11444,7 +11444,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -11453,19 +11453,19 @@
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.107</v>
+        <v>0.033</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H47" s="11" t="n">
         <v>0</v>
@@ -11489,7 +11489,7 @@
         <v>85</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>0.006</v>
@@ -11522,16 +11522,16 @@
         <v>57</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.117</v>
+        <v>0.112</v>
       </c>
       <c r="E49" s="11" t="n">
         <v>0.02</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -11555,13 +11555,13 @@
         <v>73</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.583</v>
+        <v>0.575</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="G50" s="11" t="n">
         <v>0</v>
@@ -11591,10 +11591,10 @@
         <v>0.195</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="G51" s="11" t="n">
         <v>0.001</v>
@@ -11673,10 +11673,10 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.13</v>
+        <v>0.137</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.19</v>
+        <v>0.187</v>
       </c>
       <c r="D4" s="17" t="n">
         <v>0.172</v>
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>0.137</v>
+        <v>0.135</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.157</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="6">
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.189</v>
+        <v>0.195</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="7">
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>0.119</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="8">
@@ -11737,45 +11737,45 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.039</v>
+        <v>0.036</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>0.074</v>
+        <v>0.068</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>0.064</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.037</v>
+        <v>0.035</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>0.064</v>
+        <v>0.068</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="11">
@@ -11785,42 +11785,42 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>0.05</v>
+        <v>0.055</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.042</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.042</v>
+        <v>0.05</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>0.026</v>
+        <v>0.021</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.053</v>
+        <v>0.039</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>0.029</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="C14" s="27" t="n">
         <v>0.026</v>
       </c>
-      <c r="C14" s="27" t="n">
-        <v>0.029</v>
-      </c>
       <c r="D14" s="27" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="15">
@@ -11849,13 +11849,13 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.021</v>
+        <v>0.019</v>
       </c>
       <c r="C15" s="27" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="D15" s="27" t="n">
         <v>0.026</v>
-      </c>
-      <c r="D15" s="27" t="n">
-        <v>0.025</v>
       </c>
     </row>
   </sheetData>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -12397,7 +12397,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: Argentina  (19% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: Argentina  (20% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -6342,12 +6342,12 @@
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 – 0</t>
         </is>
       </c>
       <c r="N54" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Francia</t>
+          <t>Ganó Francia</t>
         </is>
       </c>
       <c r="O54" s="12" t="inlineStr">
@@ -6355,9 +6355,9 @@
           <t>Francia</t>
         </is>
       </c>
-      <c r="P54" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P54" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q54" s="14" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="M55" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 – 2</t>
         </is>
       </c>
       <c r="N55" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Noruega</t>
+          <t>Ganó Noruega</t>
         </is>
       </c>
       <c r="O55" s="12" t="inlineStr">
@@ -6436,9 +6436,9 @@
           <t>Noruega</t>
         </is>
       </c>
-      <c r="P55" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P55" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q55" s="14" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 – 0</t>
         </is>
       </c>
       <c r="N72" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Argentina</t>
+          <t>Ganó Argentina</t>
         </is>
       </c>
       <c r="O72" s="12" t="inlineStr">
@@ -7813,9 +7813,9 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="P72" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P72" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q72" s="14" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 – 2</t>
         </is>
       </c>
       <c r="N73" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Argelia</t>
+          <t>Ganó Argelia</t>
         </is>
       </c>
       <c r="O73" s="12" t="inlineStr">
@@ -7894,9 +7894,9 @@
           <t>Argelia</t>
         </is>
       </c>
-      <c r="P73" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P73" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q73" s="14" t="inlineStr">
@@ -8191,10 +8191,10 @@
         <v>0.762</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -8245,10 +8245,10 @@
         <v>0.054</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="8">
@@ -8326,10 +8326,10 @@
         <v>0.004</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="11">
@@ -8407,10 +8407,10 @@
         <v>0.613</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.892</v>
+        <v>0.896</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.892</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="14">
@@ -8434,10 +8434,10 @@
         <v>0.387</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.792</v>
+        <v>0.797</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.792</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="15">
@@ -8461,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="16">
@@ -8542,10 +8542,10 @@
         <v>0.154</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.841</v>
+        <v>0.849</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.841</v>
+        <v>0.849</v>
       </c>
     </row>
     <row r="19">
@@ -8569,10 +8569,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20">
@@ -8623,10 +8623,10 @@
         <v>0.777</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.92</v>
+        <v>0.922</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.92</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="22">
@@ -8650,10 +8650,10 @@
         <v>0.103</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.357</v>
+        <v>0.353</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.357</v>
+        <v>0.353</v>
       </c>
     </row>
     <row r="23">
@@ -8758,10 +8758,10 @@
         <v>0.19</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.929</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.929</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -8866,10 +8866,10 @@
         <v>0.214</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
     </row>
     <row r="31">
@@ -8974,10 +8974,10 @@
         <v>0.466</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.715</v>
+        <v>0.711</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.715</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="35">
@@ -9001,10 +9001,10 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="36">
@@ -9022,16 +9022,16 @@
         <v>3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.776</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="G36" s="17" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -9049,16 +9049,16 @@
         <v>31</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.298</v>
+        <v>0.224</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
       <c r="G37" s="17" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -9067,7 +9067,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
@@ -9076,16 +9076,16 @@
         <v>15</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.224</v>
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>0.644</v>
+        <v>0.53</v>
+      </c>
+      <c r="G38" s="20" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="39">
@@ -9103,16 +9103,16 @@
         <v>57</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.112</v>
+        <v>0.074</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.112</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="40">
@@ -9190,10 +9190,10 @@
         <v>0.165</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.575</v>
+        <v>0.577</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.575</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="43">
@@ -9217,10 +9217,10 @@
         <v>0.101</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.223</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="44">
@@ -9244,10 +9244,10 @@
         <v>0.922</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.986</v>
+        <v>0.987</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.986</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="45">
@@ -9271,10 +9271,10 @@
         <v>0.672</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -9298,10 +9298,10 @@
         <v>0.243</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.474</v>
+        <v>0.472</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.474</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="47">
@@ -9325,10 +9325,10 @@
         <v>0.163</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.403</v>
+        <v>0.404</v>
       </c>
       <c r="G47" s="20" t="n">
-        <v>0.403</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="48">
@@ -9346,10 +9346,10 @@
         <v>1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.865</v>
+        <v>0.999</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>1</v>
@@ -9373,16 +9373,16 @@
         <v>24</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.129</v>
+        <v>0.001</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.782</v>
+        <v>0.715</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="50">
@@ -9391,7 +9391,7 @@
           <t>L</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Argelia</t>
         </is>
@@ -9400,16 +9400,16 @@
         <v>28</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.199</v>
+        <v>0.285</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="G50" s="20" t="n">
-        <v>0.484</v>
+        <v>0.784</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>0.784</v>
       </c>
     </row>
     <row r="51">
@@ -9427,16 +9427,16 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.195</v>
+        <v>0.015</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0.195</v>
+        <v>0.015</v>
       </c>
     </row>
   </sheetData>
@@ -10040,19 +10040,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.851</v>
+        <v>0.856</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.615</v>
+        <v>0.621</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.458</v>
+        <v>0.476</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.315</v>
+        <v>0.324</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="5">
@@ -10073,19 +10073,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.846</v>
+        <v>0.859</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.647</v>
+        <v>0.654</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.45</v>
+        <v>0.464</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.303</v>
+        <v>0.311</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.195</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="6">
@@ -10103,22 +10103,22 @@
         <v>3</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0.998</v>
+        <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.824</v>
+        <v>0.833</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.574</v>
+        <v>0.586</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.393</v>
+        <v>0.408</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.232</v>
+        <v>0.24</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="7">
@@ -10139,23 +10139,23 @@
         <v>0.999</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.82</v>
+        <v>0.821</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.53</v>
+        <v>0.531</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.34</v>
+        <v>0.344</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.181</v>
+        <v>0.178</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
@@ -10169,21 +10169,21 @@
         <v>13</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.986</v>
+        <v>0.987</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.732</v>
+        <v>0.735</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.48</v>
+        <v>0.483</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>0.233</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="I8" s="20" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="I8" s="24" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -10205,13 +10205,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.206</v>
+        <v>0.211</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>0.093</v>
@@ -10223,67 +10223,67 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.778</v>
+        <v>0.757</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.34</v>
+        <v>0.322</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.201</v>
+        <v>0.188</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.083</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.752</v>
+        <v>0.773</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.32</v>
+        <v>0.321</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.182</v>
+        <v>0.19</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="12">
@@ -10307,16 +10307,16 @@
         <v>0.577</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.326</v>
+        <v>0.323</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.066</v>
+        <v>0.062</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="13">
@@ -10334,22 +10334,22 @@
         <v>5</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.517</v>
+        <v>0.531</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.322</v>
+        <v>0.333</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.138</v>
+        <v>0.142</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>0.064</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="14">
@@ -10373,79 +10373,79 @@
         <v>0.596</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.151</v>
+        <v>0.144</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1</v>
+        <v>0.867</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.677</v>
+        <v>0.609</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.261</v>
+        <v>0.337</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.13</v>
+        <v>0.131</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.609</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.32</v>
+        <v>0.233</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.124</v>
+        <v>0.116</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>0.021</v>
@@ -10466,22 +10466,22 @@
         <v>31</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.633</v>
+        <v>0.701</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.302</v>
+        <v>0.332</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.131</v>
+        <v>0.127</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>0.055</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18">
@@ -10502,13 +10502,13 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.664</v>
+        <v>0.667</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.137</v>
+        <v>0.136</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>0.052</v>
@@ -10538,13 +10538,13 @@
         <v>0.541</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.288</v>
+        <v>0.287</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.116</v>
+        <v>0.112</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
       <c r="I19" s="24" t="n">
         <v>0.017</v>
@@ -10568,10 +10568,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.27</v>
+        <v>0.274</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>0.092</v>
@@ -10598,22 +10598,22 @@
         <v>24</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.961</v>
+        <v>0.962</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.397</v>
+        <v>0.369</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.175</v>
+        <v>0.17</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.046</v>
+        <v>0.042</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="22">
@@ -10631,22 +10631,22 @@
         <v>23</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.357</v>
+        <v>0.353</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.14</v>
+        <v>0.133</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.027</v>
+        <v>0.024</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="23">
@@ -10664,16 +10664,16 @@
         <v>16</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.219</v>
+        <v>0.214</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.095</v>
+        <v>0.093</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>0.014</v>
@@ -10700,13 +10700,13 @@
         <v>0.875</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.269</v>
+        <v>0.267</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.109</v>
+        <v>0.111</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>0.012</v>
@@ -10718,28 +10718,28 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.644</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.288</v>
+        <v>0.365</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.103</v>
+        <v>0.142</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>0.012</v>
@@ -10751,34 +10751,34 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.364</v>
+        <v>0.185</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.142</v>
+        <v>0.058</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.044</v>
+        <v>0.023</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="27">
@@ -10796,22 +10796,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>0.055</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>0.004</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="28">
@@ -10829,16 +10829,16 @@
         <v>41</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.792</v>
+        <v>0.797</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.246</v>
+        <v>0.248</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>0.007</v>
@@ -10862,16 +10862,16 @@
         <v>27</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.892</v>
+        <v>0.896</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.267</v>
+        <v>0.269</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>0.005</v>
@@ -10895,16 +10895,16 @@
         <v>33</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.92</v>
+        <v>0.922</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.242</v>
+        <v>0.231</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.065</v>
+        <v>0.062</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0.003</v>
@@ -10916,31 +10916,31 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.715</v>
+        <v>0.784</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.168</v>
+        <v>0.202</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.049</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0</v>
@@ -10949,28 +10949,28 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.929</v>
+        <v>0.711</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.239</v>
+        <v>0.165</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.057</v>
+        <v>0.05</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0.002</v>
@@ -10982,31 +10982,31 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.484</v>
+        <v>0.472</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.13</v>
+        <v>0.109</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.045</v>
+        <v>0.033</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I33" s="24" t="n">
         <v>0</v>
@@ -11015,28 +11015,28 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1</v>
+        <v>0.224</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.212</v>
+        <v>0.083</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.048</v>
+        <v>0.025</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>0.001</v>
@@ -11048,31 +11048,31 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.474</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.109</v>
+        <v>0.244</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.032</v>
+        <v>0.056</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I35" s="24" t="n">
         <v>0</v>
@@ -11081,28 +11081,28 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.841</v>
+        <v>1</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.202</v>
+        <v>0.209</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.044</v>
+        <v>0.051</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>0.001</v>
@@ -11114,28 +11114,28 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Uzbekistán</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.223</v>
+        <v>0.404</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.082</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>0.001</v>
@@ -11159,13 +11159,13 @@
         <v>40</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.168</v>
+        <v>0.165</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>0.001</v>
@@ -11180,28 +11180,28 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Uzbekistán</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.403</v>
+        <v>0.849</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.091</v>
+        <v>0.195</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.029</v>
+        <v>0.04</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>0.001</v>
@@ -11213,28 +11213,28 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.211</v>
+        <v>0.074</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.043</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.01</v>
+        <v>0.002</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0</v>
@@ -11246,28 +11246,28 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.699</v>
+        <v>0.211</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.109</v>
+        <v>0.043</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H41" s="11" t="n">
         <v>0</v>
@@ -11291,10 +11291,10 @@
         <v>64</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>0.005</v>
@@ -11327,7 +11327,7 @@
         <v>0.352</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>0.004</v>
@@ -11357,10 +11357,10 @@
         <v>83</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
         <v>0</v>
@@ -11393,7 +11393,7 @@
         <v>0.182</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>0.001</v>
@@ -11459,7 +11459,7 @@
         <v>0.31</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>0.003</v>
@@ -11477,28 +11477,28 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Nueva Zelanda</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.128</v>
+        <v>0.699</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.006</v>
+        <v>0.109</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.001</v>
+        <v>0.013</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H48" s="11" t="n">
         <v>0</v>
@@ -11510,28 +11510,28 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.112</v>
+        <v>0.127</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>73</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.575</v>
+        <v>0.577</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>0.06</v>
@@ -11588,16 +11588,16 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.195</v>
+        <v>0.015</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.029</v>
+        <v>0.002</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H51" s="11" t="n">
         <v>0</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.137</v>
+        <v>0.138</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>0.187</v>
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.135</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="6">
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.195</v>
+        <v>0.196</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.098</v>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.126</v>
@@ -11737,23 +11737,23 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>0.08</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>0.068</v>
@@ -11765,11 +11765,11 @@
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0.068</v>
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0.055</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="C14" s="27" t="n">
         <v>0.026</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="15">
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>0.028</v>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -6797,7 +6797,7 @@
           <t>Gillette Stadium, Boston</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
@@ -6826,24 +6826,24 @@
       <c r="L60" s="11" t="n">
         <v>0.018</v>
       </c>
-      <c r="M60" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N60" s="10" t="inlineStr">
-        <is>
-          <t>Favorito: Inglaterra</t>
-        </is>
-      </c>
-      <c r="O60" s="12" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="P60" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M60" s="15" t="inlineStr">
+        <is>
+          <t>0 – 0</t>
+        </is>
+      </c>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="O60" s="15" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="P60" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q60" s="14" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="M61" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 – 1</t>
         </is>
       </c>
       <c r="N61" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Croacia</t>
+          <t>Ganó Croacia</t>
         </is>
       </c>
       <c r="O61" s="12" t="inlineStr">
@@ -6922,9 +6922,9 @@
           <t>Croacia</t>
         </is>
       </c>
-      <c r="P61" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P61" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q61" s="14" t="inlineStr">
@@ -7314,12 +7314,12 @@
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 – 0</t>
         </is>
       </c>
       <c r="N66" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Portugal</t>
+          <t>Ganó Portugal</t>
         </is>
       </c>
       <c r="O66" s="12" t="inlineStr">
@@ -7327,9 +7327,9 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="P66" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P66" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q66" s="14" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 – 0</t>
         </is>
       </c>
       <c r="N67" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Colombia</t>
+          <t>Ganó Colombia</t>
         </is>
       </c>
       <c r="O67" s="12" t="inlineStr">
@@ -7408,9 +7408,9 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="P67" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P67" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q67" s="14" t="inlineStr">
@@ -8191,10 +8191,10 @@
         <v>0.762</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.931</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="6">
@@ -8218,10 +8218,10 @@
         <v>0.184</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.211</v>
+        <v>0.21</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>0.211</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="7">
@@ -8245,10 +8245,10 @@
         <v>0.054</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.165</v>
+        <v>0.162</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.165</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="8">
@@ -8326,10 +8326,10 @@
         <v>0.004</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="11">
@@ -8407,10 +8407,10 @@
         <v>0.613</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.896</v>
+        <v>0.886</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.896</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="14">
@@ -8434,10 +8434,10 @@
         <v>0.387</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
     </row>
     <row r="15">
@@ -8461,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="16">
@@ -8542,10 +8542,10 @@
         <v>0.154</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.849</v>
+        <v>0.833</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.849</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="19">
@@ -8569,10 +8569,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -8623,10 +8623,10 @@
         <v>0.777</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.922</v>
+        <v>0.917</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.922</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="22">
@@ -8650,10 +8650,10 @@
         <v>0.103</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="23">
@@ -8758,10 +8758,10 @@
         <v>0.19</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="27">
@@ -8839,10 +8839,10 @@
         <v>0.598</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.699</v>
+        <v>0.696</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.699</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="30">
@@ -8866,10 +8866,10 @@
         <v>0.214</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.433</v>
+        <v>0.424</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.433</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="31">
@@ -8947,10 +8947,10 @@
         <v>0.743</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.875</v>
+        <v>0.874</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.875</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="34">
@@ -8974,10 +8974,10 @@
         <v>0.466</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.711</v>
+        <v>0.704</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.711</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="35">
@@ -9082,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.53</v>
+        <v>0.511</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0.53</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="39">
@@ -9109,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="40">
@@ -9130,16 +9130,16 @@
         <v>4</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.949</v>
+        <v>0.707</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.995</v>
+        <v>0.998</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="G40" s="17" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -9150,23 +9150,23 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.739</v>
+        <v>0.218</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -9177,23 +9177,23 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.01</v>
+        <v>0.254</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.165</v>
+        <v>0.785</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.577</v>
+        <v>0.985</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.577</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="43">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="n">
         <v>0.006</v>
       </c>
-      <c r="E43" s="11" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>0.224</v>
-      </c>
       <c r="G43" s="19" t="n">
-        <v>0.224</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="44">
@@ -9238,16 +9238,16 @@
         <v>13</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.662</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.922</v>
+        <v>1</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -9265,16 +9265,16 @@
         <v>5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.243</v>
+        <v>0.338</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.672</v>
+        <v>0.998</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.8120000000000001</v>
+        <v>1</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>0.8120000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -9292,16 +9292,16 @@
         <v>46</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.243</v>
+        <v>0.002</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.472</v>
+        <v>0.354</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.472</v>
+        <v>0.354</v>
       </c>
     </row>
     <row r="47">
@@ -9310,7 +9310,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>Uzbekistán</t>
         </is>
@@ -9319,16 +9319,16 @@
         <v>50</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.163</v>
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0.404</v>
+        <v>0.12</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="48">
@@ -9379,10 +9379,10 @@
         <v>0.715</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.962</v>
+        <v>0.953</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.962</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="50">
@@ -9406,10 +9406,10 @@
         <v>0.285</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="51">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Senegal (3º I)</t>
+          <t>RD Congo (3º K)</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Ghana (3º J)</t>
+          <t>Senegal (3º I)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr"/>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>Croacia (2J)</t>
+          <t>Ghana (2J)</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -10025,67 +10025,67 @@
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.856</v>
+        <v>0.901</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.621</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.476</v>
+        <v>0.487</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.324</v>
+        <v>0.333</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.203</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.859</v>
+        <v>0.862</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.654</v>
+        <v>0.626</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.464</v>
+        <v>0.452</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.311</v>
+        <v>0.307</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.196</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="6">
@@ -10106,19 +10106,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.833</v>
+        <v>0.835</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.586</v>
+        <v>0.588</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.24</v>
+        <v>0.235</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.138</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="7">
@@ -10136,26 +10136,26 @@
         <v>4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.821</v>
+        <v>0.83</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.531</v>
+        <v>0.542</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.344</v>
+        <v>0.33</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
@@ -10169,22 +10169,22 @@
         <v>13</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.735</v>
+        <v>0.767</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.483</v>
+        <v>0.493</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.233</v>
+        <v>0.239</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>0.05</v>
+        <v>0.114</v>
+      </c>
+      <c r="I8" s="20" t="n">
+        <v>0.051</v>
       </c>
     </row>
     <row r="9">
@@ -10205,52 +10205,52 @@
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.366</v>
+        <v>0.388</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.211</v>
+        <v>0.213</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.757</v>
+        <v>0.728</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.322</v>
+        <v>0.435</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.188</v>
+        <v>0.189</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="11">
@@ -10271,82 +10271,82 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.773</v>
+        <v>0.788</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.19</v>
+        <v>0.194</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>0.08</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.577</v>
+        <v>0.765</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.323</v>
+        <v>0.33</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.125</v>
+        <v>0.18</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.062</v>
+        <v>0.081</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.027</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.8120000000000001</v>
+        <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.531</v>
+        <v>0.577</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.333</v>
+        <v>0.323</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.142</v>
+        <v>0.124</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="I13" s="24" t="n">
         <v>0.026</v>
@@ -10376,76 +10376,76 @@
         <v>0.353</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.144</v>
+        <v>0.143</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0.867</v>
+        <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.609</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.337</v>
+        <v>0.231</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.131</v>
+        <v>0.114</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1</v>
+        <v>0.985</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.233</v>
+        <v>0.325</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.116</v>
+        <v>0.137</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.053</v>
+        <v>0.056</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>0.021</v>
@@ -10469,19 +10469,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.701</v>
+        <v>0.702</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>0.055</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="18">
@@ -10502,19 +10502,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.667</v>
+        <v>0.674</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="19">
@@ -10535,13 +10535,13 @@
         <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.541</v>
+        <v>0.54</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.287</v>
+        <v>0.284</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="H19" s="11" t="n">
         <v>0.045</v>
@@ -10568,13 +10568,13 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.274</v>
+        <v>0.273</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.092</v>
+        <v>0.095</v>
       </c>
       <c r="H20" s="11" t="n">
         <v>0.028</v>
@@ -10586,28 +10586,28 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.962</v>
+        <v>0.424</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.369</v>
+        <v>0.214</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.17</v>
+        <v>0.094</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="H21" s="11" t="n">
         <v>0.013</v>
@@ -10619,28 +10619,28 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.353</v>
+        <v>0.874</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.133</v>
+        <v>0.28</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.059</v>
+        <v>0.111</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.024</v>
+        <v>0.039</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>0.011</v>
@@ -10652,100 +10652,100 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.433</v>
+        <v>0.349</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.214</v>
+        <v>0.132</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.093</v>
+        <v>0.057</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.04</v>
+        <v>0.022</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.875</v>
+        <v>0.931</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.267</v>
+        <v>0.365</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.111</v>
+        <v>0.141</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.953</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.365</v>
+        <v>0.279</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.142</v>
+        <v>0.119</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.042</v>
+        <v>0.029</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="26">
@@ -10763,19 +10763,19 @@
         <v>15</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.53</v>
+        <v>0.511</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.185</v>
+        <v>0.167</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.002</v>
@@ -10796,16 +10796,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>0.004</v>
@@ -10829,19 +10829,19 @@
         <v>41</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0.001</v>
@@ -10862,16 +10862,16 @@
         <v>27</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.896</v>
+        <v>0.886</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="H29" s="11" t="n">
         <v>0.005</v>
@@ -10895,16 +10895,16 @@
         <v>33</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.922</v>
+        <v>0.917</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0.003</v>
@@ -10928,19 +10928,19 @@
         <v>28</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.202</v>
+        <v>0.162</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0</v>
@@ -10949,28 +10949,28 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.711</v>
+        <v>0.927</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.165</v>
+        <v>0.238</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0.002</v>
@@ -10982,31 +10982,31 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.472</v>
+        <v>0.704</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.109</v>
+        <v>0.155</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I33" s="24" t="n">
         <v>0</v>
@@ -11015,31 +11015,31 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.224</v>
+        <v>0.162</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.083</v>
+        <v>0.031</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.025</v>
+        <v>0.006</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I34" s="24" t="n">
         <v>0</v>
@@ -11048,31 +11048,31 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.244</v>
+        <v>0.189</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.056</v>
+        <v>0.041</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I35" s="24" t="n">
         <v>0</v>
@@ -11096,13 +11096,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.209</v>
+        <v>0.193</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.051</v>
+        <v>0.039</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>0.001</v>
@@ -11114,31 +11114,31 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Uzbekistán</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.404</v>
+        <v>0.21</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.043</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.028</v>
+        <v>0.01</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I37" s="24" t="n">
         <v>0</v>
@@ -11147,25 +11147,25 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.165</v>
+        <v>0.354</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="G38" s="11" t="n">
         <v>0.001</v>
@@ -11180,31 +11180,31 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.849</v>
+        <v>0.383</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.195</v>
+        <v>0.05</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>0</v>
@@ -11213,28 +11213,28 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.074</v>
+        <v>0.352</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.043</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0</v>
@@ -11246,28 +11246,28 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Haití</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.211</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.043</v>
+        <v>0.001</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G41" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H41" s="11" t="n">
         <v>0</v>
@@ -11279,28 +11279,28 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.384</v>
+        <v>0.182</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.051</v>
+        <v>0.012</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H42" s="11" t="n">
         <v>0</v>
@@ -11312,28 +11312,28 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Túnez</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.352</v>
+        <v>0</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>0</v>
@@ -11345,25 +11345,25 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.01</v>
+        <v>0.31</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
@@ -11378,28 +11378,28 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.182</v>
+        <v>0.696</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.013</v>
+        <v>0.11</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.001</v>
+        <v>0.015</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H45" s="11" t="n">
         <v>0</v>
@@ -11411,25 +11411,25 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Túnez</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G46" s="11" t="n">
         <v>0</v>
@@ -11444,25 +11444,25 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.31</v>
+        <v>0.073</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.032</v>
+        <v>0.008</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
@@ -11477,28 +11477,28 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.699</v>
+        <v>1</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.109</v>
+        <v>0.096</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="G48" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H48" s="11" t="n">
         <v>0</v>
@@ -11510,25 +11510,25 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Nueva Zelanda</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.127</v>
+        <v>0.006</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G49" s="11" t="n">
         <v>0</v>
@@ -11543,28 +11543,28 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistán</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.577</v>
+        <v>0.12</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H50" s="11" t="n">
         <v>0</v>
@@ -11591,10 +11591,10 @@
         <v>0.015</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G51" s="11" t="n">
         <v>0</v>
@@ -11673,13 +11673,13 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.138</v>
+        <v>0.134</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>0.187</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.172</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="5">
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.203</v>
+        <v>0.194</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.135</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
     </row>
     <row r="6">
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.196</v>
+        <v>0.208</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.098</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.127</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="7">
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.126</v>
@@ -11737,19 +11737,19 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.026</v>
+        <v>0.036</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>0.08</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>0.064</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
@@ -11765,17 +11765,17 @@
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0.068</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="11">
@@ -11785,13 +11785,13 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0.055</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.046</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="12">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="C12" s="27" t="n">
         <v>0.021</v>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="C13" s="27" t="n">
         <v>0.024</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="C14" s="27" t="n">
         <v>0.026</v>
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>0.028</v>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -12397,7 +12397,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: Argentina  (20% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: Argentina  (21% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -3102,12 +3102,12 @@
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 – 1</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Suiza</t>
+          <t>Ganó Suiza</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -3115,9 +3115,9 @@
           <t>Suiza</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P14" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q14" s="14" t="inlineStr">
@@ -3152,7 +3152,7 @@
           <t>Lumen Field, Seattle</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Bosnia y Herzegovina</t>
         </is>
@@ -3181,24 +3181,24 @@
       <c r="L15" s="11" t="n">
         <v>0.393</v>
       </c>
-      <c r="M15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Parejo</t>
-        </is>
-      </c>
-      <c r="O15" s="15" t="inlineStr">
-        <is>
-          <t>Empate</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>3 – 1</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>Ganó Bosnia y Herzegovina</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>Bosnia y Herzegovina</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.30 – 0.16</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.17 – 0.96</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="R48" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.90 – 0.68</t>
         </is>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="R49" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.29 – 1.96</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="R55" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.06 – 1.69</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="R60" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.40 – 0.18</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="R66" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.59 – 0.33</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.949</v>
+        <v>0.95</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>1</v>
@@ -8185,16 +8185,16 @@
         <v>25</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>0.762</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.931</v>
+        <v>0.924</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.931</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="6">
@@ -8215,7 +8215,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0.21</v>
@@ -8242,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.054</v>
+        <v>0.055</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.162</v>
+        <v>0.154</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.162</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="8">
@@ -8266,7 +8266,7 @@
         <v>30</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="E8" s="11" t="n">
         <v>1</v>
@@ -8293,10 +8293,10 @@
         <v>19</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.412</v>
+        <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>1</v>
@@ -8311,7 +8311,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Bosnia y Herzegovina</t>
         </is>
@@ -8323,13 +8323,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.383</v>
+        <v>1</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -8338,7 +8338,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Catar</t>
         </is>
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0.352</v>
+        <v>0</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -8404,13 +8404,13 @@
         <v>0.006</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.613</v>
+        <v>0.608</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.886</v>
+        <v>0.873</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.886</v>
+        <v>0.873</v>
       </c>
     </row>
     <row r="14">
@@ -8431,13 +8431,13 @@
         <v>0.001</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.387</v>
+        <v>0.392</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.794</v>
+        <v>0.776</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.794</v>
+        <v>0.776</v>
       </c>
     </row>
     <row r="15">
@@ -8461,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.134</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="16">
@@ -8482,10 +8482,10 @@
         <v>6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.624</v>
+        <v>0.618</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.863</v>
+        <v>0.861</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>1</v>
@@ -8509,10 +8509,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.341</v>
+        <v>0.344</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.983</v>
+        <v>0.981</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>1</v>
@@ -8536,16 +8536,16 @@
         <v>42</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.154</v>
+        <v>0.158</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.833</v>
+        <v>0.799</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>0.833</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="19">
@@ -8590,7 +8590,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.998</v>
+        <v>0.997</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>1</v>
@@ -8617,16 +8617,16 @@
         <v>33</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>0.777</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.917</v>
+        <v>0.914</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.917</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="22">
@@ -8647,13 +8647,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="23">
@@ -8674,13 +8674,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="24">
@@ -8698,10 +8698,10 @@
         <v>18</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.367</v>
+        <v>0.375</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1</v>
@@ -8725,7 +8725,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.57</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>0.993</v>
@@ -8752,16 +8752,16 @@
         <v>38</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.19</v>
+        <v>0.188</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.927</v>
+        <v>0.907</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.927</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="27">
@@ -8806,10 +8806,10 @@
         <v>2</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.83</v>
+        <v>0.826</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.93</v>
+        <v>0.927</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>1</v>
@@ -8833,16 +8833,16 @@
         <v>67</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.038</v>
+        <v>0.04</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.598</v>
+        <v>0.599</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.696</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.696</v>
+        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -8860,16 +8860,16 @@
         <v>16</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.214</v>
+        <v>0.213</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.424</v>
+        <v>0.408</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.424</v>
+        <v>0.408</v>
       </c>
     </row>
     <row r="31">
@@ -8890,13 +8890,13 @@
         <v>0</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.258</v>
+        <v>0.261</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.31</v>
+        <v>0.312</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0.31</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="32">
@@ -8914,10 +8914,10 @@
         <v>29</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.522</v>
+        <v>0.524</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.706</v>
+        <v>0.708</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>1</v>
@@ -8941,16 +8941,16 @@
         <v>9</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.188</v>
+        <v>0.199</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.743</v>
+        <v>0.757</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.874</v>
+        <v>0.882</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.874</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="34">
@@ -8968,16 +8968,16 @@
         <v>20</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.29</v>
+        <v>0.277</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.466</v>
+        <v>0.458</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.704</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.704</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -8998,13 +8998,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="36">
@@ -9022,7 +9022,7 @@
         <v>3</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.776</v>
+        <v>0.771</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>31</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.224</v>
+        <v>0.229</v>
       </c>
       <c r="E37" s="11" t="n">
         <v>1</v>
@@ -9082,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.511</v>
+        <v>0.499</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0.511</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="39">
@@ -9109,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.073</v>
+        <v>0.058</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.073</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="40">
@@ -9157,16 +9157,16 @@
         <v>73</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.218</v>
+        <v>0.224</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="42">
@@ -9187,13 +9187,13 @@
         <v>0.254</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.785</v>
+        <v>0.779</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.985</v>
+        <v>0.981</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.985</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="43">
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="44">
@@ -9238,7 +9238,7 @@
         <v>13</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.662</v>
+        <v>0.637</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>1</v>
@@ -9265,10 +9265,10 @@
         <v>5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.338</v>
+        <v>0.363</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.998</v>
+        <v>0.996</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>1</v>
@@ -9295,13 +9295,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.354</v>
+        <v>0.364</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.354</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="47">
@@ -9325,10 +9325,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.12</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>0.12</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -9376,13 +9376,13 @@
         <v>0.001</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.715</v>
+        <v>0.711</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.953</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.953</v>
+        <v>0.9419999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -9403,13 +9403,13 @@
         <v>0</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.285</v>
+        <v>0.289</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.781</v>
+        <v>0.745</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>0.781</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="51">
@@ -9433,10 +9433,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
     </row>
   </sheetData>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>Suiza (2B)</t>
+          <t>Canadá (2B)</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Canadá (1B)</t>
+          <t>Suiza (1B)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -10040,19 +10040,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.901</v>
+        <v>0.903</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>0.487</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.333</v>
+        <v>0.328</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.208</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="5">
@@ -10073,19 +10073,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.862</v>
+        <v>0.858</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.626</v>
+        <v>0.62</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.452</v>
+        <v>0.445</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.307</v>
+        <v>0.304</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.194</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="6">
@@ -10109,16 +10109,16 @@
         <v>0.835</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.588</v>
+        <v>0.579</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.407</v>
+        <v>0.408</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.235</v>
+        <v>0.234</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="7">
@@ -10139,19 +10139,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.83</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.542</v>
+        <v>0.522</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.33</v>
+        <v>0.303</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.176</v>
+        <v>0.16</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -10172,151 +10172,151 @@
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.493</v>
+        <v>0.482</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.239</v>
+        <v>0.237</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.746</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.388</v>
+        <v>0.461</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.213</v>
+        <v>0.215</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.092</v>
+        <v>0.109</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.728</v>
+        <v>0.819</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.435</v>
+        <v>0.391</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.189</v>
+        <v>0.213</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.083</v>
+        <v>0.093</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.788</v>
+        <v>0.784</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.327</v>
+        <v>0.342</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.194</v>
+        <v>0.182</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.08</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.765</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.18</v>
+        <v>0.204</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="13">
@@ -10337,16 +10337,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.577</v>
+        <v>0.574</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.323</v>
+        <v>0.32</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.124</v>
+        <v>0.123</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="I13" s="24" t="n">
         <v>0.026</v>
@@ -10370,19 +10370,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.596</v>
+        <v>0.6</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.353</v>
+        <v>0.361</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.143</v>
+        <v>0.151</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.061</v>
+        <v>0.064</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="15">
@@ -10403,85 +10403,85 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.231</v>
+        <v>0.233</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.114</v>
+        <v>0.117</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.985</v>
+        <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.667</v>
+        <v>0.701</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.325</v>
+        <v>0.336</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.137</v>
+        <v>0.13</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>1</v>
+        <v>0.981</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.702</v>
+        <v>0.66</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.333</v>
+        <v>0.315</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.126</v>
+        <v>0.129</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18">
@@ -10502,19 +10502,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.674</v>
+        <v>0.681</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.342</v>
+        <v>0.316</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.138</v>
+        <v>0.133</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="19">
@@ -10538,10 +10538,10 @@
         <v>0.54</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.284</v>
+        <v>0.297</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.111</v>
+        <v>0.118</v>
       </c>
       <c r="H19" s="11" t="n">
         <v>0.045</v>
@@ -10568,16 +10568,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.63</v>
+        <v>0.592</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.273</v>
+        <v>0.279</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.095</v>
+        <v>0.096</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="I20" s="24" t="n">
         <v>0.008</v>
@@ -10598,22 +10598,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.424</v>
+        <v>0.408</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.214</v>
+        <v>0.205</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.094</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="22">
@@ -10631,19 +10631,19 @@
         <v>9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.874</v>
+        <v>0.882</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.28</v>
+        <v>0.298</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.111</v>
+        <v>0.12</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.039</v>
+        <v>0.042</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="I22" s="24" t="n">
         <v>0.004</v>
@@ -10664,19 +10664,19 @@
         <v>23</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>0.022</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>0.003</v>
@@ -10697,22 +10697,22 @@
         <v>25</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.931</v>
+        <v>0.924</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.365</v>
+        <v>0.391</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.141</v>
+        <v>0.153</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.041</v>
+        <v>0.045</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="25">
@@ -10730,16 +10730,16 @@
         <v>24</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.953</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.279</v>
+        <v>0.265</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.119</v>
+        <v>0.11</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>0.008999999999999999</v>
@@ -10763,19 +10763,19 @@
         <v>15</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.511</v>
+        <v>0.499</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.167</v>
+        <v>0.152</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.056</v>
+        <v>0.055</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.002</v>
@@ -10784,7 +10784,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -10793,22 +10793,22 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.134</v>
+        <v>0.776</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.052</v>
+        <v>0.239</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.018</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.024</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="I27" s="24" t="n">
         <v>0.001</v>
@@ -10817,7 +10817,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -10826,22 +10826,22 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.794</v>
+        <v>0.125</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.247</v>
+        <v>0.048</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0.001</v>
@@ -10862,13 +10862,13 @@
         <v>27</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.886</v>
+        <v>0.873</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.266</v>
+        <v>0.255</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.091</v>
+        <v>0.094</v>
       </c>
       <c r="G29" s="11" t="n">
         <v>0.023</v>
@@ -10895,52 +10895,52 @@
         <v>33</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.917</v>
+        <v>0.914</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.23</v>
+        <v>0.228</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.781</v>
+        <v>0.799</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.162</v>
+        <v>0.188</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.054</v>
+        <v>0.04</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0</v>
@@ -10949,28 +10949,28 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.927</v>
+        <v>0.745</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.238</v>
+        <v>0.145</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.052</v>
+        <v>0.046</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0.002</v>
@@ -10982,28 +10982,28 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.704</v>
+        <v>0.907</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.155</v>
+        <v>0.23</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.041</v>
+        <v>0.05</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>0.002</v>
@@ -11015,31 +11015,31 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.162</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.031</v>
+        <v>0.144</v>
       </c>
       <c r="F34" s="11" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G34" s="11" t="n">
         <v>0.006</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="H34" s="11" t="n">
         <v>0.001</v>
-      </c>
-      <c r="H34" s="11" t="n">
-        <v>0</v>
       </c>
       <c r="I34" s="24" t="n">
         <v>0</v>
@@ -11048,28 +11048,28 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0.001</v>
@@ -11081,31 +11081,31 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.193</v>
+        <v>0.112</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.039</v>
+        <v>0.015</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I36" s="24" t="n">
         <v>0</v>
@@ -11114,25 +11114,25 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.21</v>
+        <v>0.364</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.043</v>
+        <v>0.024</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>0.001</v>
@@ -11147,28 +11147,28 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.354</v>
+        <v>0.21</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.023</v>
+        <v>0.047</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -11180,28 +11180,28 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.383</v>
+        <v>0.154</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.05</v>
+        <v>0.034</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>0</v>
@@ -11213,7 +11213,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -11222,19 +11222,19 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.352</v>
+        <v>1</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.043</v>
+        <v>0.133</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0</v>
@@ -11246,22 +11246,22 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>0</v>
@@ -11279,25 +11279,25 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Haití</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.182</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G42" s="11" t="n">
         <v>0</v>
@@ -11312,25 +11312,25 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Túnez</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0</v>
@@ -11345,25 +11345,25 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Túnez</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G44" s="11" t="n">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -11387,19 +11387,19 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.696</v>
+        <v>0.312</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.11</v>
+        <v>0.034</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
         <v>0</v>
@@ -11423,10 +11423,10 @@
         <v>85</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>0.001</v>
@@ -11456,10 +11456,10 @@
         <v>57</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.073</v>
+        <v>0.058</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>0.001</v>
@@ -11489,13 +11489,13 @@
         <v>73</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.096</v>
+        <v>0.098</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="E49" s="11" t="n">
         <v>0.002</v>
@@ -11555,16 +11555,16 @@
         <v>50</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.12</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H50" s="11" t="n">
         <v>0</v>
@@ -11588,10 +11588,10 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>0</v>
@@ -11673,13 +11673,13 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.187</v>
+        <v>0.191</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.171</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="5">
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.194</v>
+        <v>0.191</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.135</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="6">
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.208</v>
+        <v>0.202</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>0.098</v>
+        <v>0.117</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.131</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="7">
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>0.116</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="8">
@@ -11737,45 +11737,45 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>0.08</v>
       </c>
       <c r="D8" s="20" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>0.068</v>
+        <v>0.063</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>0.068</v>
+        <v>0.063</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.057</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="11">
@@ -11785,26 +11785,26 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>0.055</v>
+        <v>0.049</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.045</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.051</v>
+        <v>0.042</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="D12" s="27" t="n">
         <v>0.03</v>
@@ -11813,17 +11813,17 @@
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="14">
@@ -11836,10 +11836,10 @@
         <v>0.026</v>
       </c>
       <c r="C14" s="27" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="15">
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>0.028</v>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -12397,7 +12397,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: Argentina  (21% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: Argentina  (20% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -2616,12 +2616,12 @@
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 – 3</t>
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr">
         <is>
-          <t>Favorito: México</t>
+          <t>Ganó México</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -2629,9 +2629,9 @@
           <t>México</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P8" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q8" s="14" t="inlineStr">
@@ -2666,7 +2666,7 @@
           <t>Estadio BBVA, Monterrey</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Sudáfrica</t>
         </is>
@@ -2674,7 +2674,7 @@
       <c r="F9" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Corea del Sur</t>
         </is>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 – 0</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Corea del Sur</t>
+          <t>Ganó Sudáfrica</t>
         </is>
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+          <t>Sudáfrica</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q9" s="14" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 – 2</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Marruecos</t>
+          <t>Ganó Marruecos</t>
         </is>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -4087,9 +4087,9 @@
           <t>Marruecos</t>
         </is>
       </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P26" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 – 3</t>
         </is>
       </c>
       <c r="N27" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Brasil</t>
+          <t>Ganó Brasil</t>
         </is>
       </c>
       <c r="O27" s="12" t="inlineStr">
@@ -4168,9 +4168,9 @@
           <t>Brasil</t>
         </is>
       </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P27" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
@@ -8158,7 +8158,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
         <v>1</v>
@@ -8178,23 +8178,23 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.762</v>
+        <v>1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.924</v>
+        <v>1</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>0.924</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -8203,25 +8203,25 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>Sudáfrica</t>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.21</v>
+        <v>0.907</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>0.907</v>
       </c>
     </row>
     <row r="7">
@@ -8242,13 +8242,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8259,17 +8259,17 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>1</v>
@@ -8286,14 +8286,14 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>1</v>
@@ -8313,17 +8313,17 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>1</v>
@@ -8407,10 +8407,10 @@
         <v>0.608</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.873</v>
+        <v>0.882</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.873</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="14">
@@ -8434,10 +8434,10 @@
         <v>0.392</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.776</v>
+        <v>0.762</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.776</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="15">
@@ -8461,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16">
@@ -8482,10 +8482,10 @@
         <v>6</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>0.618</v>
+        <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.861</v>
+        <v>1</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>1</v>
@@ -8509,10 +8509,10 @@
         <v>7</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.344</v>
+        <v>0</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.981</v>
+        <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>1</v>
@@ -8527,7 +8527,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Escocia</t>
         </is>
@@ -8536,16 +8536,16 @@
         <v>42</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.799</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <v>0.799</v>
+        <v>0.305</v>
+      </c>
+      <c r="G18" s="20" t="n">
+        <v>0.305</v>
       </c>
     </row>
     <row r="19">
@@ -8569,10 +8569,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -8623,10 +8623,10 @@
         <v>0.777</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.914</v>
+        <v>0.917</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.914</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="22">
@@ -8650,10 +8650,10 @@
         <v>0.102</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="G22" s="20" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
     </row>
     <row r="23">
@@ -8677,10 +8677,10 @@
         <v>0.121</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="24">
@@ -8758,10 +8758,10 @@
         <v>0.188</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.907</v>
+        <v>0.908</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.907</v>
+        <v>0.908</v>
       </c>
     </row>
     <row r="27">
@@ -8866,10 +8866,10 @@
         <v>0.213</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.408</v>
+        <v>0.397</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.408</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="31">
@@ -8893,10 +8893,10 @@
         <v>0.261</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="32">
@@ -8947,10 +8947,10 @@
         <v>0.757</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.882</v>
+        <v>0.884</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.882</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="34">
@@ -8974,10 +8974,10 @@
         <v>0.458</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="35">
@@ -9001,10 +9001,10 @@
         <v>0.076</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="36">
@@ -9082,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.499</v>
+        <v>0.509</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0.499</v>
+        <v>0.509</v>
       </c>
     </row>
     <row r="39">
@@ -9109,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.058</v>
+        <v>0.026</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.058</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="40">
@@ -9163,10 +9163,10 @@
         <v>0.224</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -9298,10 +9298,10 @@
         <v>0.004</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.364</v>
+        <v>0.351</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.364</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="47">
@@ -9325,10 +9325,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="48">
@@ -9379,10 +9379,10 @@
         <v>0.711</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.954</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="50">
@@ -9406,10 +9406,10 @@
         <v>0.289</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="51">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>Corea del Sur (2A)</t>
+          <t>Sudáfrica (2A)</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina (3º B)</t>
+          <t>Senegal (3º I)</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Senegal (3º I)</t>
+          <t>Corea del Sur (3º A)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr"/>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>Suiza (1B)</t>
+          <t>Bosnia y Herzegovina (1B)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -10040,19 +10040,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.903</v>
+        <v>0.899</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.487</v>
+        <v>0.479</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.328</v>
+        <v>0.323</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -10073,19 +10073,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.858</v>
+        <v>0.862</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.62</v>
+        <v>0.622</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.304</v>
+        <v>0.306</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="6">
@@ -10106,19 +10106,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.835</v>
+        <v>0.836</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.579</v>
+        <v>0.585</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.408</v>
+        <v>0.414</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>0.135</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="7">
@@ -10142,16 +10142,16 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.522</v>
+        <v>0.505</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.303</v>
+        <v>0.293</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.16</v>
+        <v>0.156</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="8">
@@ -10172,16 +10172,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.768</v>
+        <v>0.764</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.482</v>
+        <v>0.478</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.237</v>
+        <v>0.233</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.113</v>
+        <v>0.111</v>
       </c>
       <c r="I8" s="20" t="n">
         <v>0.05</v>
@@ -10205,19 +10205,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.746</v>
+        <v>0.742</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.461</v>
+        <v>0.458</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.215</v>
+        <v>0.211</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="10">
@@ -10238,19 +10238,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.819</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.391</v>
+        <v>0.416</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.213</v>
+        <v>0.226</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="11">
@@ -10271,19 +10271,19 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.784</v>
+        <v>0.873</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.342</v>
+        <v>0.349</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.182</v>
+        <v>0.183</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.092</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="12">
@@ -10304,85 +10304,85 @@
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.728</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.35</v>
+        <v>0.318</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.204</v>
+        <v>0.186</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.08</v>
+        <v>0.073</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.574</v>
+        <v>0.6</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.32</v>
+        <v>0.375</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.123</v>
+        <v>0.159</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.061</v>
+        <v>0.068</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.6</v>
+        <v>0.574</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.361</v>
+        <v>0.32</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.151</v>
+        <v>0.123</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="15">
@@ -10403,19 +10403,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.702</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.233</v>
+        <v>0.232</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.117</v>
+        <v>0.116</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="16">
@@ -10436,13 +10436,13 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.701</v>
+        <v>0.702</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>0.057</v>
@@ -10469,16 +10469,16 @@
         <v>0.981</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.66</v>
+        <v>0.648</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.315</v>
+        <v>0.308</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.129</v>
+        <v>0.125</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="I17" s="24" t="n">
         <v>0.02</v>
@@ -10487,67 +10487,67 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.681</v>
+        <v>0.537</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.316</v>
+        <v>0.303</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.133</v>
+        <v>0.122</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.049</v>
+        <v>0.046</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.54</v>
+        <v>0.671</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.297</v>
+        <v>0.311</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.118</v>
+        <v>0.128</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="20">
@@ -10568,19 +10568,19 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.592</v>
+        <v>0.761</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.279</v>
+        <v>0.36</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.096</v>
+        <v>0.124</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.027</v>
+        <v>0.036</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21">
@@ -10598,22 +10598,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.408</v>
+        <v>0.397</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.205</v>
+        <v>0.199</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.035</v>
+        <v>0.032</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="22">
@@ -10631,22 +10631,22 @@
         <v>9</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.882</v>
+        <v>0.884</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.298</v>
+        <v>0.304</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>0.012</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="23">
@@ -10664,19 +10664,19 @@
         <v>23</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.131</v>
+        <v>0.137</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.053</v>
+        <v>0.059</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.022</v>
+        <v>0.024</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>0.003</v>
@@ -10685,61 +10685,61 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.924</v>
+        <v>0.509</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.391</v>
+        <v>0.165</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.153</v>
+        <v>0.057</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.045</v>
+        <v>0.021</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.907</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.265</v>
+        <v>0.27</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.11</v>
+        <v>0.078</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>0.008999999999999999</v>
@@ -10751,31 +10751,31 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.499</v>
+        <v>0.954</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.152</v>
+        <v>0.269</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.055</v>
+        <v>0.112</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.006</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.002</v>
@@ -10784,7 +10784,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -10793,31 +10793,31 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0.776</v>
+        <v>0.13</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.239</v>
+        <v>0.045</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.019</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -10826,22 +10826,22 @@
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.125</v>
+        <v>0.762</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.048</v>
+        <v>0.222</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.017</v>
+        <v>0.09</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.008</v>
+        <v>0.027</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0.001</v>
@@ -10862,19 +10862,19 @@
         <v>27</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.873</v>
+        <v>0.882</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.255</v>
+        <v>0.252</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.094</v>
+        <v>0.103</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0.001</v>
@@ -10895,13 +10895,13 @@
         <v>33</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.914</v>
+        <v>0.917</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.228</v>
+        <v>0.231</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="G30" s="11" t="n">
         <v>0.011</v>
@@ -10916,31 +10916,31 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.799</v>
+        <v>0.908</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.188</v>
+        <v>0.219</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0</v>
@@ -10961,16 +10961,16 @@
         <v>28</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.745</v>
+        <v>0.715</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.145</v>
+        <v>0.138</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.046</v>
+        <v>0.044</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0.002</v>
@@ -10982,31 +10982,31 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.907</v>
+        <v>0.679</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.23</v>
+        <v>0.148</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.05</v>
+        <v>0.034</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I33" s="24" t="n">
         <v>0</v>
@@ -11015,7 +11015,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -11024,16 +11024,16 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0.6840000000000001</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.144</v>
+        <v>0.198</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>0.006</v>
@@ -11048,28 +11048,28 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.192</v>
+        <v>0.239</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.039</v>
+        <v>0.053</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0.001</v>
@@ -11081,31 +11081,31 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.112</v>
+        <v>0.048</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I36" s="24" t="n">
         <v>0</v>
@@ -11114,28 +11114,28 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.364</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.024</v>
+        <v>0.094</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>0</v>
@@ -11147,28 +11147,28 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.21</v>
+        <v>0.351</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.047</v>
+        <v>0.023</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -11192,16 +11192,16 @@
         <v>40</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H39" s="11" t="n">
         <v>0</v>
@@ -11228,13 +11228,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.133</v>
+        <v>0.125</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0</v>
@@ -11291,10 +11291,10 @@
         <v>83</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>0</v>
@@ -11324,7 +11324,7 @@
         <v>82</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="E43" s="11" t="n">
         <v>0.013</v>
@@ -11390,13 +11390,13 @@
         <v>61</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.312</v>
+        <v>0.313</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.034</v>
+        <v>0.027</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>0</v>
@@ -11423,7 +11423,7 @@
         <v>85</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0.116</v>
+        <v>0.115</v>
       </c>
       <c r="E46" s="11" t="n">
         <v>0.007</v>
@@ -11456,13 +11456,13 @@
         <v>57</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.058</v>
+        <v>0.026</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
@@ -11489,13 +11489,13 @@
         <v>73</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.098</v>
+        <v>0.091</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>0.007</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>0</v>
@@ -11555,13 +11555,13 @@
         <v>50</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G50" s="11" t="n">
         <v>0</v>
@@ -11673,13 +11673,13 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.135</v>
+        <v>0.137</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>0.191</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.174</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="5">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.191</v>
+        <v>0.192</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.135</v>
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.202</v>
+        <v>0.2</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.117</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="7">
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.125</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>0.113</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="8">
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>0.08</v>
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>0.063</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>0.055</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="10">
@@ -11769,13 +11769,13 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0.063</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="11">
@@ -11785,7 +11785,7 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0.049</v>
@@ -11801,13 +11801,13 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="C12" s="27" t="n">
         <v>0.024</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="13">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="C14" s="27" t="n">
         <v>0.028</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="15">

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -3557,7 +3557,7 @@
           <t>SoFi Stadium, Los Angeles</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Turquía</t>
         </is>
@@ -3565,7 +3565,7 @@
       <c r="F20" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Estados Unidos</t>
         </is>
@@ -3588,22 +3588,22 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 – 2</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Estados Unidos</t>
+          <t>Ganó Turquía</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+          <t>Turquía</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
@@ -3638,7 +3638,7 @@
           <t>Levi's Stadium, San Francisco Bay Area</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
@@ -3667,24 +3667,24 @@
       <c r="L21" s="11" t="n">
         <v>0.324</v>
       </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="inlineStr">
-        <is>
-          <t>Favorito: Paraguay</t>
-        </is>
-      </c>
-      <c r="O21" s="12" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>0 – 0</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
@@ -4529,7 +4529,7 @@
           <t>MetLife Stadium, New York New Jersey</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
@@ -4558,24 +4558,24 @@
       <c r="L32" s="11" t="n">
         <v>0.374</v>
       </c>
-      <c r="M32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N32" s="16" t="inlineStr">
-        <is>
-          <t>Parejo</t>
-        </is>
-      </c>
-      <c r="O32" s="15" t="inlineStr">
-        <is>
-          <t>Empate</t>
-        </is>
-      </c>
-      <c r="P32" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>2 – 1</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>Ganó Ecuador</t>
+        </is>
+      </c>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="P32" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q32" s="14" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 – 2</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Costa de Marfil</t>
+          <t>Ganó Costa de Marfil</t>
         </is>
       </c>
       <c r="O33" s="12" t="inlineStr">
@@ -4654,9 +4654,9 @@
           <t>Costa de Marfil</t>
         </is>
       </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P33" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q33" s="14" t="inlineStr">
@@ -5015,7 +5015,7 @@
           <t>AT&amp;T Stadium, Dallas</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Japón</t>
         </is>
@@ -5044,24 +5044,24 @@
       <c r="L38" s="11" t="n">
         <v>0.208</v>
       </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N38" s="10" t="inlineStr">
-        <is>
-          <t>Favorito: Japón</t>
-        </is>
-      </c>
-      <c r="O38" s="12" t="inlineStr">
-        <is>
-          <t>Japón</t>
-        </is>
-      </c>
-      <c r="P38" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M38" s="15" t="inlineStr">
+        <is>
+          <t>1 – 1</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="O38" s="15" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="P38" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q38" s="14" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="N39" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Países Bajos</t>
+          <t>Ganó Países Bajos</t>
         </is>
       </c>
       <c r="O39" s="12" t="inlineStr">
@@ -5140,9 +5140,9 @@
           <t>Países Bajos</t>
         </is>
       </c>
-      <c r="P39" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P39" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q39" s="14" t="inlineStr">
@@ -8218,10 +8218,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.907</v>
+        <v>0.638</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>0.907</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="7">
@@ -8367,14 +8367,14 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.993</v>
+        <v>0</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>1</v>
@@ -8394,23 +8394,23 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.006</v>
+        <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.608</v>
+        <v>1</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -8428,16 +8428,16 @@
         <v>41</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.392</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.762</v>
+        <v>0.999</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>0.762</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="15">
@@ -8461,10 +8461,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8527,7 +8527,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Escocia</t>
         </is>
@@ -8542,10 +8542,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="G18" s="20" t="n">
-        <v>0.305</v>
+        <v>0.107</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.107</v>
       </c>
     </row>
     <row r="19">
@@ -8590,7 +8590,7 @@
         <v>10</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
         <v>1</v>
@@ -8617,16 +8617,16 @@
         <v>33</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.777</v>
+        <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.917</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -8635,7 +8635,7 @@
           <t>E</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
@@ -8647,13 +8647,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="G22" s="20" t="n">
-        <v>0.344</v>
+        <v>1</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -8674,13 +8674,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -8698,10 +8698,10 @@
         <v>18</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.819</v>
+        <v>1</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>1</v>
@@ -8725,10 +8725,10 @@
         <v>8</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.5639999999999999</v>
+        <v>1</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>1</v>
@@ -8752,16 +8752,16 @@
         <v>38</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.908</v>
+        <v>1</v>
       </c>
       <c r="G26" s="17" t="n">
-        <v>0.908</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -8839,10 +8839,10 @@
         <v>0.599</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="G29" s="17" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="30">
@@ -8866,10 +8866,10 @@
         <v>0.213</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.397</v>
+        <v>0.384</v>
       </c>
       <c r="G30" s="20" t="n">
-        <v>0.397</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="31">
@@ -8893,10 +8893,10 @@
         <v>0.261</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.313</v>
+        <v>0.312</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>0.313</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="32">
@@ -8947,10 +8947,10 @@
         <v>0.757</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.884</v>
+        <v>0.878</v>
       </c>
       <c r="G33" s="17" t="n">
-        <v>0.884</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="34">
@@ -8974,10 +8974,10 @@
         <v>0.458</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.679</v>
+        <v>0.665</v>
       </c>
       <c r="G34" s="17" t="n">
-        <v>0.679</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="35">
@@ -9082,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.509</v>
+        <v>0.378</v>
       </c>
       <c r="G38" s="20" t="n">
-        <v>0.509</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="39">
@@ -9109,10 +9109,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="40">
@@ -9163,10 +9163,10 @@
         <v>0.224</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="42">
@@ -9190,10 +9190,10 @@
         <v>0.779</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.981</v>
+        <v>0.966</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.981</v>
+        <v>0.966</v>
       </c>
     </row>
     <row r="43">
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="44">
@@ -9298,10 +9298,10 @@
         <v>0.004</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="G46" s="20" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="47">
@@ -9325,10 +9325,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.032</v>
+        <v>0.008</v>
       </c>
       <c r="G47" s="19" t="n">
-        <v>0.032</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="48">
@@ -9379,10 +9379,10 @@
         <v>0.711</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.954</v>
+        <v>0.885</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.954</v>
+        <v>0.885</v>
       </c>
     </row>
     <row r="50">
@@ -9406,10 +9406,10 @@
         <v>0.289</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.715</v>
+        <v>0.618</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>0.715</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="51">
@@ -9433,10 +9433,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
     </row>
   </sheetData>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>Escocia (3º D)</t>
+          <t>Suecia (3º F)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>Suecia (3º F)</t>
+          <t>Paraguay (3º C)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>Paraguay (3º C)</t>
+          <t>Irán (3º H)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>Senegal (3º I)</t>
+          <t>Ecuador (3º E)</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr"/>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>Ecuador (3º E)</t>
+          <t>Senegal (3º I)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -10040,19 +10040,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.899</v>
+        <v>0.85</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.674</v>
+        <v>0.641</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.479</v>
+        <v>0.458</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.323</v>
+        <v>0.309</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.2</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="5">
@@ -10073,19 +10073,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.862</v>
+        <v>0.85</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.622</v>
+        <v>0.611</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.447</v>
+        <v>0.438</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.306</v>
+        <v>0.299</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.192</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="6">
@@ -10109,13 +10109,13 @@
         <v>0.836</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.585</v>
+        <v>0.581</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.414</v>
+        <v>0.407</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.237</v>
+        <v>0.235</v>
       </c>
       <c r="I6" s="20" t="n">
         <v>0.137</v>
@@ -10139,7 +10139,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0.505</v>
@@ -10148,14 +10148,14 @@
         <v>0.293</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.156</v>
+        <v>0.157</v>
       </c>
       <c r="I7" s="20" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
@@ -10172,19 +10172,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.764</v>
+        <v>0.725</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.478</v>
+        <v>0.455</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.233</v>
+        <v>0.222</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="I8" s="20" t="n">
-        <v>0.05</v>
+        <v>0.106</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>0.049</v>
       </c>
     </row>
     <row r="9">
@@ -10205,16 +10205,16 @@
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.742</v>
+        <v>0.72</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.458</v>
+        <v>0.446</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.211</v>
+        <v>0.206</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="I9" s="24" t="n">
         <v>0.044</v>
@@ -10244,13 +10244,13 @@
         <v>0.416</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.226</v>
+        <v>0.225</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.092</v>
+        <v>0.093</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="11">
@@ -10274,82 +10274,82 @@
         <v>0.873</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.183</v>
+        <v>0.185</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.728</v>
+        <v>0.713</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.318</v>
+        <v>0.476</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.186</v>
+        <v>0.215</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.073</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.6</v>
+        <v>0.772</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.375</v>
+        <v>0.341</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.159</v>
+        <v>0.196</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.068</v>
+        <v>0.078</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="14">
@@ -10370,19 +10370,19 @@
         <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.574</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.123</v>
+        <v>0.124</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>0.061</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="15">
@@ -10403,19 +10403,19 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.702</v>
+        <v>0.737</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.232</v>
+        <v>0.249</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.116</v>
+        <v>0.126</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.053</v>
+        <v>0.058</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.023</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="16">
@@ -10436,19 +10436,19 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.337</v>
+        <v>0.332</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>0.057</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="17">
@@ -10466,16 +10466,16 @@
         <v>11</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.981</v>
+        <v>0.966</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.648</v>
+        <v>0.645</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.308</v>
+        <v>0.304</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.125</v>
+        <v>0.123</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>0.053</v>
@@ -10487,67 +10487,67 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.537</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.303</v>
+        <v>0.317</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.122</v>
+        <v>0.131</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.046</v>
+        <v>0.049</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.671</v>
+        <v>0.442</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.311</v>
+        <v>0.233</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.128</v>
+        <v>0.079</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.047</v>
+        <v>0.034</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="20">
@@ -10571,13 +10571,13 @@
         <v>0.761</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.36</v>
+        <v>0.344</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.124</v>
+        <v>0.119</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="I20" s="24" t="n">
         <v>0.01</v>
@@ -10586,130 +10586,130 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>0.397</v>
+        <v>1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.199</v>
+        <v>0.332</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.083</v>
+        <v>0.167</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.032</v>
+        <v>0.074</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.011</v>
+        <v>0.027</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.884</v>
+        <v>0.384</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.304</v>
+        <v>0.194</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.113</v>
+        <v>0.08</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.344</v>
+        <v>0.878</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.137</v>
+        <v>0.303</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.059</v>
+        <v>0.113</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.024</v>
+        <v>0.039</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.509</v>
+        <v>0.885</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.165</v>
+        <v>0.249</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.057</v>
+        <v>0.104</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>0.002</v>
@@ -10718,31 +10718,31 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>0.907</v>
+        <v>0.378</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.27</v>
+        <v>0.127</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.078</v>
+        <v>0.037</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.033</v>
+        <v>0.014</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="I25" s="24" t="n">
         <v>0.002</v>
@@ -10751,31 +10751,31 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.954</v>
+        <v>0.638</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.269</v>
+        <v>0.189</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.112</v>
+        <v>0.056</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.002</v>
@@ -10784,7 +10784,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -10793,25 +10793,25 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="F27" s="11" t="n">
         <v>0.13</v>
       </c>
-      <c r="E27" s="11" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>0.019</v>
-      </c>
       <c r="G27" s="11" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="28">
@@ -10829,19 +10829,19 @@
         <v>41</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.762</v>
+        <v>0.999</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.222</v>
+        <v>0.21</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.09</v>
+        <v>0.076</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0.001</v>
@@ -10850,31 +10850,31 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Costa de Marfil</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>0.882</v>
+        <v>1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.252</v>
+        <v>0.26</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.103</v>
+        <v>0.068</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0.001</v>
@@ -10883,31 +10883,31 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Costa de Marfil</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>0.917</v>
+        <v>0.665</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.231</v>
+        <v>0.152</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.06</v>
+        <v>0.034</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>0</v>
@@ -10916,28 +10916,28 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>0.908</v>
+        <v>0.618</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.219</v>
+        <v>0.121</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>0.002</v>
@@ -10949,31 +10949,31 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.715</v>
+        <v>1</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.138</v>
+        <v>0.204</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.044</v>
+        <v>0.039</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I32" s="24" t="n">
         <v>0</v>
@@ -10982,31 +10982,31 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.679</v>
+        <v>1</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.148</v>
+        <v>0.249</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.034</v>
+        <v>0.045</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I33" s="24" t="n">
         <v>0</v>
@@ -11015,28 +11015,28 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.198</v>
+        <v>0.239</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.038</v>
+        <v>0.05</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="H34" s="11" t="n">
         <v>0.001</v>
@@ -11048,31 +11048,31 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1</v>
+        <v>0.679</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.239</v>
+        <v>0.092</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.053</v>
+        <v>0.013</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I35" s="24" t="n">
         <v>0</v>
@@ -11081,31 +11081,31 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0.305</v>
+        <v>0.349</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.048</v>
+        <v>0.023</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.011</v>
+        <v>0.006</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I36" s="24" t="n">
         <v>0</v>
@@ -11114,28 +11114,28 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0.6870000000000001</v>
+        <v>0</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H37" s="11" t="n">
         <v>0</v>
@@ -11147,28 +11147,28 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>0.351</v>
+        <v>1</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.023</v>
+        <v>0.128</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H38" s="11" t="n">
         <v>0</v>
@@ -11180,16 +11180,16 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>0</v>
@@ -11213,28 +11213,28 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="G40" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H40" s="11" t="n">
         <v>0</v>
@@ -11246,16 +11246,16 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Haití</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -11288,19 +11288,19 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0</v>
+        <v>0.107</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H42" s="11" t="n">
         <v>0</v>
@@ -11324,13 +11324,13 @@
         <v>82</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0</v>
@@ -11390,10 +11390,10 @@
         <v>61</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.313</v>
+        <v>0.312</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>0.002</v>
@@ -11426,7 +11426,7 @@
         <v>0.115</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>0.001</v>
@@ -11456,10 +11456,10 @@
         <v>57</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="F47" s="11" t="n">
         <v>0</v>
@@ -11489,13 +11489,13 @@
         <v>73</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.091</v>
+        <v>0.09</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="E49" s="11" t="n">
         <v>0.001</v>
@@ -11555,10 +11555,10 @@
         <v>50</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.032</v>
+        <v>0.008</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F50" s="11" t="n">
         <v>0</v>
@@ -11588,10 +11588,10 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F51" s="11" t="n">
         <v>0</v>
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.192</v>
+        <v>0.188</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.135</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="6">
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.2</v>
+        <v>0.191</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.117</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.142</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="7">
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.125</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>0.112</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="8">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>0.063</v>
@@ -11769,13 +11769,13 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0.063</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="11">
@@ -11785,13 +11785,13 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0.049</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.042</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="12">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="C12" s="27" t="n">
         <v>0.024</v>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="C13" s="27" t="n">
         <v>0.019</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.025</v>
+        <v>0.026</v>
       </c>
       <c r="C14" s="27" t="n">
         <v>0.028</v>
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>0.028</v>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -12397,7 +12397,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: Argentina  (20% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: Argentina  (19% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -233,9 +233,6 @@
     <xf numFmtId="9" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -250,6 +247,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 – 1</t>
         </is>
       </c>
       <c r="N62" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Croacia</t>
+          <t>Ganó Croacia</t>
         </is>
       </c>
       <c r="O62" s="12" t="inlineStr">
@@ -7003,9 +7003,9 @@
           <t>Croacia</t>
         </is>
       </c>
-      <c r="P62" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P62" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q62" s="14" t="inlineStr">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 – 2</t>
         </is>
       </c>
       <c r="N63" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Inglaterra</t>
+          <t>Ganó Inglaterra</t>
         </is>
       </c>
       <c r="O63" s="12" t="inlineStr">
@@ -7084,9 +7084,9 @@
           <t>Inglaterra</t>
         </is>
       </c>
-      <c r="P63" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P63" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q63" s="14" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0 – 0</t>
         </is>
       </c>
       <c r="N68" s="16" t="inlineStr">
         <is>
-          <t>Parejo</t>
+          <t>Empate</t>
         </is>
       </c>
       <c r="O68" s="15" t="inlineStr">
@@ -7489,9 +7489,9 @@
           <t>Empate</t>
         </is>
       </c>
-      <c r="P68" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P68" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q68" s="14" t="inlineStr">
@@ -7526,7 +7526,7 @@
           <t>Mercedes-Benz Stadium, Atlanta</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>RD Congo</t>
         </is>
@@ -7555,24 +7555,24 @@
       <c r="L69" s="11" t="n">
         <v>0.405</v>
       </c>
-      <c r="M69" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="16" t="inlineStr">
-        <is>
-          <t>Parejo</t>
-        </is>
-      </c>
-      <c r="O69" s="15" t="inlineStr">
-        <is>
-          <t>Empate</t>
-        </is>
-      </c>
-      <c r="P69" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>3 – 1</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>Ganó RD Congo</t>
+        </is>
+      </c>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>RD Congo</t>
+        </is>
+      </c>
+      <c r="P69" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q69" s="14" t="inlineStr">
@@ -7939,7 +7939,7 @@
       <c r="F74" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="G74" s="10" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
@@ -7960,24 +7960,24 @@
       <c r="L74" s="11" t="n">
         <v>0.45</v>
       </c>
-      <c r="M74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>Favorito: Austria</t>
-        </is>
-      </c>
-      <c r="O74" s="12" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="P74" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>3 – 3</t>
+        </is>
+      </c>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="O74" s="15" t="inlineStr">
+        <is>
+          <t>Empate</t>
+        </is>
+      </c>
+      <c r="P74" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q74" s="14" t="inlineStr">
@@ -8043,12 +8043,12 @@
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1 – 3</t>
         </is>
       </c>
       <c r="N75" s="10" t="inlineStr">
         <is>
-          <t>Favorito: Argentina</t>
+          <t>Ganó Argentina</t>
         </is>
       </c>
       <c r="O75" s="12" t="inlineStr">
@@ -8056,9 +8056,9 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="P75" s="8" t="inlineStr">
-        <is>
-          <t>Proyección</t>
+      <c r="P75" s="13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
         </is>
       </c>
       <c r="Q75" s="14" t="inlineStr">
@@ -8203,7 +8203,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Corea del Sur</t>
         </is>
@@ -8218,10 +8218,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0.396</v>
+        <v>0</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8230,7 +8230,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>República Checa</t>
         </is>
@@ -8247,7 +8247,7 @@
       <c r="F7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Catar</t>
         </is>
@@ -8355,7 +8355,7 @@
       <c r="F11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Turquía</t>
         </is>
@@ -8463,7 +8463,7 @@
       <c r="F15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Escocia</t>
         </is>
@@ -8544,7 +8544,7 @@
       <c r="F18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Haití</t>
         </is>
@@ -8571,7 +8571,7 @@
       <c r="F19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="20" t="n">
+      <c r="G19" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
           <t>E</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Curazao</t>
         </is>
@@ -8679,7 +8679,7 @@
       <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="20" t="n">
+      <c r="G23" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Túnez</t>
         </is>
@@ -8787,7 +8787,7 @@
       <c r="F27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="20" t="n">
+      <c r="G27" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>Arabia Saudita</t>
         </is>
@@ -8868,7 +8868,7 @@
       <c r="F30" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="20" t="n">
+      <c r="G30" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
           <t>G</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
@@ -8895,7 +8895,7 @@
       <c r="F31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="20" t="n">
+      <c r="G31" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
           <t>H</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>Irán</t>
         </is>
@@ -8974,10 +8974,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="G34" s="17" t="n">
-        <v>0.915</v>
+        <v>0</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -8986,7 +8986,7 @@
           <t>H</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>Nueva Zelanda</t>
         </is>
@@ -9003,7 +9003,7 @@
       <c r="F35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="20" t="n">
+      <c r="G35" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
           <t>I</t>
         </is>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
@@ -9111,7 +9111,7 @@
       <c r="F39" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="20" t="n">
+      <c r="G39" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9123,17 +9123,17 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.224</v>
+        <v>1</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>1</v>
@@ -9150,17 +9150,17 @@
       </c>
       <c r="B41" s="10" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0.707</v>
+        <v>0</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.998</v>
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>1</v>
@@ -9177,23 +9177,23 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0.254</v>
+        <v>1</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.956</v>
+        <v>1</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>0.956</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -9202,7 +9202,7 @@
           <t>J</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>Panamá</t>
         </is>
@@ -9217,10 +9217,10 @@
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G43" s="20" t="n">
-        <v>0.004</v>
+        <v>0</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -9238,7 +9238,7 @@
         <v>13</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>0.637</v>
+        <v>1</v>
       </c>
       <c r="E44" s="11" t="n">
         <v>1</v>
@@ -9265,10 +9265,10 @@
         <v>5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.363</v>
+        <v>0</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.996</v>
+        <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>1</v>
@@ -9283,7 +9283,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>RD Congo</t>
         </is>
@@ -9295,13 +9295,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="G46" s="18" t="n">
-        <v>0.349</v>
+        <v>1</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -9310,7 +9310,7 @@
           <t>K</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>Uzbekistán</t>
         </is>
@@ -9325,10 +9325,10 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G47" s="20" t="n">
-        <v>0.001</v>
+        <v>0</v>
+      </c>
+      <c r="G47" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -9339,17 +9339,17 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.999</v>
+        <v>0</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>1</v>
@@ -9366,23 +9366,23 @@
       </c>
       <c r="B49" s="10" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.711</v>
+        <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.828</v>
+        <v>1</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>0.828</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -9391,25 +9391,25 @@
           <t>L</t>
         </is>
       </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Argelia</t>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.289</v>
+        <v>1</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="G50" s="18" t="n">
-        <v>0.549</v>
+        <v>1</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -9418,7 +9418,7 @@
           <t>L</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>Jordania</t>
         </is>
@@ -9433,10 +9433,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G51" s="20" t="n">
-        <v>0.002</v>
+        <v>0</v>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9531,12 +9531,12 @@
           <t>28 jun</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Sudáfrica (2A)</t>
         </is>
       </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Canadá (2B)</t>
         </is>
@@ -9558,14 +9558,14 @@
           <t>29 jun</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Alemania (1E)</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>Paraguay (3º C)</t>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Corea del Sur (3º A)</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -9585,12 +9585,12 @@
           <t>29 jun</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Países Bajos (1F)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Australia (2C)</t>
         </is>
@@ -9612,12 +9612,12 @@
           <t>29 jun</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Estados Unidos (1C)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>Japón (2F)</t>
         </is>
@@ -9639,14 +9639,14 @@
           <t>30 jun</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Francia (1I)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>Suecia (3º F)</t>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>Paraguay (3º C)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -9666,12 +9666,12 @@
           <t>30 jun</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Costa de Marfil (2E)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Noruega (2I)</t>
         </is>
@@ -9693,14 +9693,14 @@
           <t>30 jun</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>México (1A)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>Irán (3º H)</t>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>Senegal (3º I)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -9720,12 +9720,12 @@
           <t>1 jul</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Argentina (1L)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>RD Congo (3º K)</t>
         </is>
@@ -9743,14 +9743,14 @@
           <t>1 jul</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Brasil (1D)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>Ecuador (3º E)</t>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Suiza (3º B)</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr"/>
@@ -9766,14 +9766,14 @@
           <t>1 jul</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>España (1G)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>Corea del Sur (3º A)</t>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Ecuador (3º E)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr"/>
@@ -9789,14 +9789,14 @@
           <t>2 jul</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Portugal (2K)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Austria (2L)</t>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Argelia (2L)</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -9816,12 +9816,12 @@
           <t>2 jul</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Bélgica (1H)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Ghana (2J)</t>
         </is>
@@ -9843,14 +9843,14 @@
           <t>2 jul</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Bosnia y Herzegovina (1B)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Senegal (3º I)</t>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Suecia (3º F)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -9870,12 +9870,12 @@
           <t>3 jul</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>Inglaterra (1J)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Croacia (1J)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Egipto (2H)</t>
         </is>
@@ -9897,14 +9897,14 @@
           <t>3 jul</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Colombia (1K)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Argelia (3º L)</t>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Escocia (3º D)</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -9924,12 +9924,12 @@
           <t>3 jul</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Marruecos (2D)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>Cabo Verde (2G)</t>
         </is>
@@ -10023,7 +10023,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
@@ -10040,23 +10040,23 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.879</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.66</v>
+        <v>0.712</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.488</v>
+        <v>0.527</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.334</v>
+        <v>0.352</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.202</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>España</t>
         </is>
@@ -10073,23 +10073,23 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.908</v>
+        <v>0.753</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.654</v>
+        <v>0.535</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.473</v>
+        <v>0.398</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.317</v>
+        <v>0.266</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.198</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Francia</t>
         </is>
@@ -10109,20 +10109,20 @@
         <v>0.828</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.584</v>
+        <v>0.58</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.434</v>
+        <v>0.432</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>0.142</v>
+        <v>0.251</v>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>0.144</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Inglaterra</t>
         </is>
@@ -10139,151 +10139,151 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.849</v>
+        <v>0.897</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.536</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.315</v>
+        <v>0.352</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.177</v>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>0.092</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Marruecos</t>
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.883</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.449</v>
+        <v>0.508</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.248</v>
+        <v>0.253</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>0.045</v>
+        <v>0.115</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>0.052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.697</v>
+        <v>0.883</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.443</v>
+        <v>0.402</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.21</v>
+        <v>0.221</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.1</v>
+        <v>0.091</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.045</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.705</v>
+        <v>0.945</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.038</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.875</v>
+        <v>0.716</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.298</v>
+        <v>0.441</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.157</v>
+        <v>0.183</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.074</v>
+        <v>0.093</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.034</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="12">
@@ -10310,13 +10310,13 @@
         <v>0.476</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.201</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.077</v>
+        <v>0.082</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="13">
@@ -10337,19 +10337,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.79</v>
+        <v>0.866</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.314</v>
+        <v>0.345</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.18</v>
+        <v>0.198</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.067</v>
+        <v>0.08</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="14">
@@ -10376,13 +10376,13 @@
         <v>0.34</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="15">
@@ -10403,76 +10403,76 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.628</v>
+        <v>0.772</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.208</v>
+        <v>0.247</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.111</v>
+        <v>0.132</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.706</v>
+        <v>0.597</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.33</v>
+        <v>0.291</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.114</v>
+        <v>0.106</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.052</v>
+        <v>0.047</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D17" s="11" t="n">
-        <v>0.956</v>
+        <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.58</v>
+        <v>0.706</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.271</v>
+        <v>0.33</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>0.108</v>
@@ -10481,7 +10481,7 @@
         <v>0.046</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="18">
@@ -10502,19 +10502,19 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.72</v>
+        <v>0.571</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.326</v>
+        <v>0.267</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.136</v>
+        <v>0.103</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="19">
@@ -10541,79 +10541,79 @@
         <v>0.253</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.039</v>
+        <v>0.035</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.352</v>
+        <v>0.761</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.192</v>
+        <v>0.344</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.109</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.011</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.761</v>
+        <v>0.247</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.344</v>
+        <v>0.114</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.11</v>
+        <v>0.056</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="22">
@@ -10634,19 +10634,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.391</v>
+        <v>0.429</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.098</v>
+        <v>0.17</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.038</v>
+        <v>0.054</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="23">
@@ -10667,16 +10667,16 @@
         <v>1</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.452</v>
+        <v>0.403</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.177</v>
+        <v>0.16</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>0.004</v>
@@ -10697,19 +10697,19 @@
         <v>24</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0.828</v>
+        <v>1</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.233</v>
+        <v>0.284</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.089</v>
+        <v>0.108</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.021</v>
+        <v>0.023</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>0.002</v>
@@ -10769,7 +10769,7 @@
         <v>0.172</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="G26" s="11" t="n">
         <v>0.026</v>
@@ -10805,7 +10805,7 @@
         <v>0.078</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>0.003</v>
@@ -10817,31 +10817,31 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>0.396</v>
+        <v>1</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.131</v>
+        <v>0.228</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.032</v>
+        <v>0.025</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0</v>
@@ -10850,31 +10850,31 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.264</v>
+        <v>0.103</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.058</v>
+        <v>0.021</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0</v>
@@ -10883,31 +10883,31 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.149</v>
+        <v>0.188</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.033</v>
+        <v>0.056</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>0</v>
@@ -10916,31 +10916,31 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.117</v>
+        <v>0.239</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.016</v>
+        <v>0.05</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0</v>
@@ -10949,28 +10949,28 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>0.349</v>
+        <v>1</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.023</v>
+        <v>0.117</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0</v>
@@ -10982,31 +10982,31 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.549</v>
+        <v>1</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.107</v>
+        <v>0.06</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.033</v>
+        <v>0.015</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I33" s="24" t="n">
         <v>0</v>
@@ -11015,7 +11015,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -11024,22 +11024,22 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.239</v>
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I34" s="24" t="n">
         <v>0</v>
@@ -11096,13 +11096,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.128</v>
+        <v>0.134</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>0</v>
@@ -11390,19 +11390,19 @@
         <v>20</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0.915</v>
+        <v>0</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I45" s="24" t="n">
         <v>0</v>
@@ -11492,10 +11492,10 @@
         <v>1</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.065</v>
+        <v>0.055</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
@@ -11522,10 +11522,10 @@
         <v>34</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>50</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
         <v>63</v>
       </c>
       <c r="D51" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="E51" s="11" t="n">
         <v>0</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.142</v>
+        <v>0.144</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>0.191</v>
@@ -11689,13 +11689,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.198</v>
+        <v>0.163</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.135</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.148</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="6">
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.202</v>
+        <v>0.218</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.117</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.134</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="7">
@@ -11721,13 +11721,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.092</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.125</v>
       </c>
-      <c r="D7" s="18" t="n">
-        <v>0.117</v>
+      <c r="D7" s="23" t="n">
+        <v>0.119</v>
       </c>
     </row>
     <row r="8">
@@ -11737,13 +11737,13 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>0.08</v>
       </c>
-      <c r="D8" s="18" t="n">
-        <v>0.07099999999999999</v>
+      <c r="D8" s="23" t="n">
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -11753,13 +11753,13 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.034</v>
+        <v>0.041</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>0.063</v>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>0.057</v>
+      <c r="D9" s="23" t="n">
+        <v>0.058</v>
       </c>
     </row>
     <row r="10">
@@ -11769,13 +11769,13 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.029</v>
+        <v>0.033</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0.063</v>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>0.056</v>
+      <c r="D10" s="23" t="n">
+        <v>0.057</v>
       </c>
     </row>
     <row r="11">
@@ -11785,42 +11785,42 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0.049</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.045</v>
+        <v>0.026</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>0.024</v>
+        <v>0.028</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.027</v>
+        <v>0.041</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>0.028</v>
+        <v>0.024</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>0.028</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="C14" s="27" t="n">
         <v>0.028</v>
@@ -11849,13 +11849,13 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.045</v>
+        <v>0.052</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>0.019</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0.024</v>
+        <v>0.026</v>
       </c>
     </row>
   </sheetData>
@@ -12064,12 +12064,12 @@
           <t>M95</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Croacia</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Marruecos</t>
         </is>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -12203,12 +12203,12 @@
           <t>M100</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Marruecos</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -12397,7 +12397,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: Argentina  (20% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: Argentina  (22% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -2641,7 +2641,7 @@
       </c>
       <c r="R8" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.47 – 1.79</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.10 – 1.00</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.57 – 1.02</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="R20" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.71 – 2.06</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.24 – 0.55</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.13 – 4.46</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.27 – 0.65</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.50 – 1.31</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.31 – 0.61</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.62 – 1.85</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.52 – 0.40</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.84 – 1.97</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.25 – 3.65</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="R54" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.38 – 0.60</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="R61" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.54 – 1.63</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="R67" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.98 – 0.37</t>
         </is>
       </c>
     </row>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="R72" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.62 – 0.50</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="R73" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.63 – 1.89</t>
         </is>
       </c>
     </row>
@@ -10040,19 +10040,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.712</v>
+        <v>0.715</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.527</v>
+        <v>0.542</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.352</v>
+        <v>0.374</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.218</v>
+        <v>0.237</v>
       </c>
     </row>
     <row r="5">
@@ -10073,19 +10073,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.753</v>
+        <v>0.741</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.535</v>
+        <v>0.51</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.398</v>
+        <v>0.373</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.266</v>
+        <v>0.249</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.163</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="6">
@@ -10106,19 +10106,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.828</v>
+        <v>0.831</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="I6" s="23" t="n">
-        <v>0.144</v>
+        <v>0.137</v>
       </c>
     </row>
     <row r="7">
@@ -10139,23 +10139,23 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.897</v>
+        <v>0.898</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.352</v>
+        <v>0.357</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.177</v>
+        <v>0.174</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
@@ -10172,25 +10172,25 @@
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.508</v>
+        <v>0.494</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.253</v>
+        <v>0.235</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>0.052</v>
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>0.047</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -10199,31 +10199,31 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.883</v>
+        <v>0.956</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.402</v>
+        <v>0.371</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.221</v>
+        <v>0.211</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.091</v>
+        <v>0.1</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.041</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -10232,22 +10232,22 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.945</v>
+        <v>0.881</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.35</v>
+        <v>0.408</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.192</v>
+        <v>0.23</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.091</v>
+        <v>0.093</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>0.041</v>
@@ -10271,16 +10271,16 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.716</v>
+        <v>0.719</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.441</v>
+        <v>0.427</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.183</v>
+        <v>0.177</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.093</v>
+        <v>0.09</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>0.039</v>
@@ -10304,19 +10304,19 @@
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.713</v>
+        <v>0.706</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.476</v>
+        <v>0.467</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.2</v>
+        <v>0.197</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="13">
@@ -10337,85 +10337,85 @@
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.866</v>
+        <v>0.852</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.198</v>
+        <v>0.192</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.34</v>
+        <v>0.246</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.128</v>
+        <v>0.139</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.062</v>
+        <v>0.068</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.026</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.772</v>
+        <v>0.529</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.247</v>
+        <v>0.31</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.132</v>
+        <v>0.105</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.06</v>
+        <v>0.048</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -10436,16 +10436,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.597</v>
+        <v>0.572</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.291</v>
+        <v>0.29</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>0.018</v>
@@ -10469,49 +10469,49 @@
         <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.706</v>
+        <v>0.702</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.33</v>
+        <v>0.342</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>0.046</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.571</v>
+        <v>0.471</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.103</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="I18" s="24" t="n">
         <v>0.014</v>
@@ -10520,31 +10520,31 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.442</v>
+        <v>0.576</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.253</v>
+        <v>0.272</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.082</v>
+        <v>0.105</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.035</v>
+        <v>0.037</v>
       </c>
       <c r="I19" s="24" t="n">
         <v>0.013</v>
@@ -10553,133 +10553,133 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.761</v>
+        <v>0.259</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.344</v>
+        <v>0.116</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.109</v>
+        <v>0.057</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.247</v>
+        <v>0.761</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.114</v>
+        <v>0.348</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.056</v>
+        <v>0.113</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.023</v>
+        <v>0.036</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.17</v>
+        <v>0.182</v>
       </c>
       <c r="G22" s="11" t="n">
         <v>0.054</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.403</v>
+        <v>0.424</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.16</v>
+        <v>0.168</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.014</v>
+        <v>0.016</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="24">
@@ -10700,16 +10700,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.284</v>
+        <v>0.281</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.108</v>
+        <v>0.101</v>
       </c>
       <c r="G24" s="11" t="n">
         <v>0.023</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="I24" s="24" t="n">
         <v>0.002</v>
@@ -10733,19 +10733,19 @@
         <v>1</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.287</v>
+        <v>0.294</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.13</v>
+        <v>0.136</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.006</v>
+        <v>0.008</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="26">
@@ -10766,16 +10766,16 @@
         <v>1</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.172</v>
+        <v>0.169</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>0.062</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.001</v>
@@ -10799,10 +10799,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.294</v>
+        <v>0.298</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.078</v>
+        <v>0.082</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>0.014</v>
@@ -10817,64 +10817,64 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.228</v>
+        <v>0.207</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.025</v>
+        <v>0.067</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="H28" s="11" t="n">
         <v>0.002</v>
       </c>
       <c r="I28" s="24" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.103</v>
+        <v>0.239</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.021</v>
+        <v>0.049</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0</v>
@@ -10883,31 +10883,31 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.188</v>
+        <v>0.148</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.056</v>
+        <v>0.016</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>0</v>
@@ -10916,25 +10916,25 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.239</v>
+        <v>0.216</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.05</v>
+        <v>0.024</v>
       </c>
       <c r="G31" s="11" t="n">
         <v>0.006</v>
@@ -10949,28 +10949,28 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0</v>
@@ -10982,28 +10982,28 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H33" s="11" t="n">
         <v>0</v>
@@ -11015,16 +11015,16 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>0</v>
@@ -11048,16 +11048,16 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>0</v>
@@ -11081,28 +11081,28 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>Haití</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H36" s="11" t="n">
         <v>0</v>
@@ -11114,16 +11114,16 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>0</v>
@@ -11147,16 +11147,16 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>0</v>
@@ -11180,16 +11180,16 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Túnez</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>0</v>
@@ -11213,16 +11213,16 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>0</v>
@@ -11246,16 +11246,16 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>0</v>
@@ -11279,28 +11279,28 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Túnez</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0</v>
+        <v>0.119</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H42" s="11" t="n">
         <v>0</v>
@@ -11312,28 +11312,28 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H43" s="11" t="n">
         <v>0</v>
@@ -11345,16 +11345,16 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>0</v>
@@ -11378,7 +11378,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -11387,7 +11387,7 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>0</v>
@@ -11411,16 +11411,16 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Nueva Zelanda</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>0</v>
@@ -11444,25 +11444,25 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
@@ -11477,7 +11477,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -11486,16 +11486,16 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
@@ -11510,28 +11510,28 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -11673,45 +11673,45 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.144</v>
+        <v>0.137</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.191</v>
+        <v>0.205</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.181</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.163</v>
+        <v>0.237</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>0.135</v>
+        <v>0.177</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.14</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.218</v>
+        <v>0.151</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.137</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="7">
@@ -11721,45 +11721,45 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>0.119</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.039</v>
+        <v>0.044</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>0.058</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="10">
@@ -11769,13 +11769,13 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>0.063</v>
+        <v>0.056</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="11">
@@ -11785,29 +11785,29 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.026</v>
+        <v>0.047</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="13">
@@ -11820,42 +11820,42 @@
         <v>0.041</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="C14" s="27" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.052</v>
+        <v>0.018</v>
       </c>
       <c r="C15" s="27" t="n">
-        <v>0.019</v>
+        <v>0.025</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0.026</v>
+        <v>0.024</v>
       </c>
     </row>
   </sheetData>
@@ -12397,7 +12397,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: Argentina  (22% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: Argentina  (24% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -10037,71 +10037,71 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.969</v>
+        <v>0.893</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.879</v>
+        <v>0.664</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.639</v>
+        <v>0.528</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.41</v>
+        <v>0.328</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.275</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.859</v>
+        <v>0.952</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.611</v>
+        <v>0.846</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.468</v>
+        <v>0.596</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.268</v>
+        <v>0.351</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.175</v>
+        <v>0.219</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Francia</t>
         </is>
@@ -10118,19 +10118,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.884</v>
+        <v>0.899</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.631</v>
+        <v>0.656</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.435</v>
+        <v>0.462</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>0.14</v>
+        <v>0.301</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="7">
@@ -10151,23 +10151,23 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.88</v>
+        <v>0.873</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.551</v>
+        <v>0.525</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.19</v>
+        <v>0.174</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
@@ -10184,19 +10184,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.958</v>
+        <v>0.962</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>0.627</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.233</v>
+        <v>0.257</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>0.049</v>
+        <v>0.115</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>0.056</v>
       </c>
     </row>
     <row r="9">
@@ -10217,19 +10217,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.58</v>
+        <v>0.612</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.368</v>
+        <v>0.396</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.18</v>
+        <v>0.198</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="10">
@@ -10250,184 +10250,184 @@
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.539</v>
+        <v>0.54</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.168</v>
+        <v>0.161</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.081</v>
+        <v>0.083</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.857</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.513</v>
+        <v>0.268</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.188</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.068</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.211</v>
+        <v>0.491</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.127</v>
+        <v>0.161</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.048</v>
+        <v>0.057</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.023</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.461</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.305</v>
+        <v>0.253</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.129</v>
+        <v>0.135</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.264</v>
+        <v>0.299</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.137</v>
+        <v>0.121</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.062</v>
+        <v>0.057</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.546</v>
+        <v>0.528</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.24</v>
+        <v>0.166</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.059</v>
+        <v>0.038</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="16">
@@ -10448,49 +10448,49 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.703</v>
+        <v>0.679</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.318</v>
+        <v>0.306</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.131</v>
+        <v>0.122</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.054</v>
+        <v>0.049</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.42</v>
+        <v>0.717</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.235</v>
+        <v>0.304</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.042</v>
+        <v>0.032</v>
       </c>
       <c r="I17" s="24" t="n">
         <v>0.014</v>
@@ -10499,97 +10499,97 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.454</v>
+        <v>0.472</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.184</v>
+        <v>0.138</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.092</v>
+        <v>0.077</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.038</v>
+        <v>0.03</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.716</v>
+        <v>0.436</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.304</v>
+        <v>0.183</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.761</v>
+        <v>0.388</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.286</v>
+        <v>0.21</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.094</v>
+        <v>0.08</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="I20" s="24" t="n">
         <v>0.008999999999999999</v>
@@ -10598,34 +10598,34 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.434</v>
+        <v>0.765</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.136</v>
+        <v>0.295</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.023</v>
+        <v>0.032</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -10646,19 +10646,19 @@
         <v>1</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.518</v>
+        <v>0.508</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.239</v>
+        <v>0.241</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H22" s="11" t="n">
         <v>0.018</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="23">
@@ -10679,19 +10679,19 @@
         <v>1</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.482</v>
+        <v>0.492</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.216</v>
+        <v>0.226</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="24">
@@ -10712,13 +10712,13 @@
         <v>1</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.659</v>
+        <v>0.646</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.089</v>
+        <v>0.107</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="H24" s="11" t="n">
         <v>0.007</v>
@@ -10748,7 +10748,7 @@
         <v>0.311</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>0.024</v>
@@ -10757,37 +10757,37 @@
         <v>0.007</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Costa de Marfil</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.141</v>
+        <v>0.321</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.042</v>
+        <v>0.089</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="I26" s="24" t="n">
         <v>0.001</v>
@@ -10796,31 +10796,31 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Costa de Marfil</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.297</v>
+        <v>0.107</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.079</v>
+        <v>0.032</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="I27" s="24" t="n">
         <v>0.001</v>
@@ -10829,25 +10829,25 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.116</v>
+        <v>0.283</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.035</v>
+        <v>0.064</v>
       </c>
       <c r="G28" s="11" t="n">
         <v>0.01</v>
@@ -10862,31 +10862,31 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.284</v>
+        <v>0.354</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.064</v>
+        <v>0.029</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0</v>
@@ -10895,28 +10895,28 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.341</v>
+        <v>0.101</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.003</v>
+        <v>0.006</v>
       </c>
       <c r="H30" s="11" t="n">
         <v>0.001</v>
@@ -10928,31 +10928,31 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.12</v>
+        <v>0.235</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H31" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I31" s="24" t="n">
         <v>0</v>
@@ -10961,28 +10961,28 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.239</v>
+        <v>0.048</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.036</v>
+        <v>0.018</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0</v>
@@ -11075,10 +11075,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.143</v>
+        <v>0.173</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.031</v>
+        <v>0.042</v>
       </c>
       <c r="G35" s="11" t="n">
         <v>0.003</v>
@@ -11357,28 +11357,28 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H44" s="11" t="n">
         <v>0</v>
@@ -11390,7 +11390,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>0</v>
@@ -11423,16 +11423,16 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Nueva Zelanda</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>0</v>
@@ -11456,25 +11456,25 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
@@ -11489,7 +11489,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -11498,16 +11498,16 @@
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="G48" s="11" t="n">
         <v>0</v>
@@ -11522,28 +11522,28 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -11681,33 +11681,33 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.275</v>
+        <v>0.16</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.177</v>
+        <v>0.205</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.14</v>
+        <v>0.219</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>0.205</v>
+        <v>0.177</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.192</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="6">
@@ -11717,13 +11717,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.175</v>
+        <v>0.222</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.12</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.131</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="7">
@@ -11733,13 +11733,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.12</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>0.114</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="8">
@@ -11749,23 +11749,23 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.033</v>
+        <v>0.037</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>0.065</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>0.056</v>
@@ -11777,17 +11777,17 @@
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.022</v>
+        <v>0.016</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0.056</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="11">
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0.05</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="12">
@@ -11813,13 +11813,13 @@
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.049</v>
+        <v>0.056</v>
       </c>
       <c r="C12" s="27" t="n">
         <v>0.025</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="13">
@@ -11829,13 +11829,13 @@
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.03</v>
+        <v>0.024</v>
       </c>
       <c r="C13" s="27" t="n">
         <v>0.025</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="14">
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
       <c r="C14" s="27" t="n">
         <v>0.022</v>
@@ -11861,13 +11861,13 @@
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="C15" s="27" t="n">
         <v>0.025</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
     </row>
   </sheetData>
@@ -12288,12 +12288,12 @@
           <t>M102</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>España</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>España</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -12409,7 +12409,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: Argentina  (28% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: España  (22% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Partidos A-L'!$A$3:$R$75</definedName>
@@ -343,13 +343,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -368,7 +368,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -420,13 +420,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -445,7 +445,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -497,13 +497,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -522,7 +522,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -574,13 +574,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -599,7 +599,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -651,13 +651,13 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -676,7 +676,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -726,13 +726,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -751,7 +751,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -803,13 +803,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -828,7 +828,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -880,13 +880,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -905,7 +905,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -957,13 +957,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -982,7 +982,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1034,13 +1034,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1059,7 +1059,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1111,13 +1111,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1136,7 +1136,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1188,13 +1188,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1213,7 +1213,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1265,13 +1265,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1290,7 +1290,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1342,7 +1342,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1357,9 +1357,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1379,9 +1379,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1401,9 +1401,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1423,9 +1423,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1445,9 +1445,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1467,9 +1467,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1489,9 +1489,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1511,9 +1511,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1533,9 +1533,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId9"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1555,9 +1555,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId10"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1577,9 +1577,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId11"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1599,9 +1599,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId12"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1611,7 +1611,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -1626,9 +1626,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10052,19 +10052,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>0.893</v>
+        <v>1</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.664</v>
+        <v>1</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.528</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.328</v>
+        <v>0.499</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.222</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="5">
@@ -10085,19 +10085,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>0.952</v>
+        <v>1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.846</v>
+        <v>1</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.596</v>
+        <v>0.733</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.351</v>
+        <v>0.371</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.219</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="6">
@@ -10118,19 +10118,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.899</v>
+        <v>1</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.656</v>
+        <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.462</v>
+        <v>0.647</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.301</v>
+        <v>0.408</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>0.16</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="7">
@@ -10151,322 +10151,322 @@
         <v>1</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.873</v>
+        <v>1</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.525</v>
+        <v>1</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.333</v>
+        <v>0.648</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.174</v>
+        <v>0.302</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>0.077</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.962</v>
+        <v>1</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>0.627</v>
+        <v>1</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.257</v>
+        <v>0.353</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.115</v>
+        <v>0.172</v>
       </c>
       <c r="I8" s="23" t="n">
-        <v>0.056</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.612</v>
+        <v>1</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.396</v>
+        <v>1</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.198</v>
+        <v>0.352</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.095</v>
+        <v>0.118</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.037</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>0.371</v>
+        <v>1</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.161</v>
+        <v>0.267</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.083</v>
+        <v>0.076</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.5639999999999999</v>
+        <v>1</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.268</v>
+        <v>1</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.15</v>
+        <v>0.184</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.026</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.827</v>
+        <v>1</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.491</v>
+        <v>0</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="I12" s="24" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0.6889999999999999</v>
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.253</v>
+        <v>0</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I13" s="24" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.299</v>
+        <v>0</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="I14" s="24" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.166</v>
+        <v>0</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="I15" s="24" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.679</v>
+        <v>1</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>0.306</v>
+        <v>0</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.122</v>
+        <v>0</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="I16" s="24" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -10475,295 +10475,295 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.717</v>
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="G17" s="11" t="n">
-        <v>0.096</v>
+        <v>0</v>
       </c>
       <c r="H17" s="11" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="I17" s="24" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Croacia</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>0.138</v>
+        <v>0</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.077</v>
+        <v>0</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.436</v>
+        <v>1</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.037</v>
+        <v>0</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.388</v>
+        <v>1</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.765</v>
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.295</v>
+        <v>0</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="I21" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.508</v>
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.241</v>
+        <v>0</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="H22" s="11" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.492</v>
+        <v>1</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.226</v>
+        <v>0</v>
       </c>
       <c r="G23" s="11" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="H23" s="11" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="I23" s="24" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Haití</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.646</v>
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="I24" s="24" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0.311</v>
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="I25" s="24" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Costa de Marfil</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -10772,88 +10772,88 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="I26" s="24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.107</v>
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H27" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I27" s="24" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Argelia</t>
+          <t>Costa de Marfil</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.283</v>
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>0</v>
@@ -10862,31 +10862,31 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.354</v>
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="H29" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>0</v>
@@ -10895,7 +10895,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -10904,22 +10904,22 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.101</v>
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="G30" s="11" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="H30" s="11" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>0</v>
@@ -10928,28 +10928,28 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>0</v>
@@ -10961,28 +10961,28 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H32" s="11" t="n">
         <v>0</v>
@@ -10994,16 +10994,16 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Túnez</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>0</v>
@@ -11027,16 +11027,16 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>0</v>
@@ -11060,28 +11060,28 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0.173</v>
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>0</v>
@@ -11093,19 +11093,19 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="11" t="n">
         <v>0</v>
@@ -11126,22 +11126,22 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>0</v>
@@ -11159,16 +11159,16 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>0</v>
@@ -11192,16 +11192,16 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>0</v>
@@ -11225,19 +11225,19 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>0</v>
@@ -11258,16 +11258,16 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Túnez</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>0</v>
@@ -11291,19 +11291,19 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Croacia</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="11" t="n">
         <v>0</v>
@@ -11324,19 +11324,19 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="D43" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="11" t="n">
         <v>0</v>
@@ -11357,16 +11357,16 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Panamá</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>0</v>
@@ -11390,22 +11390,22 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>Nueva Zelanda</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>0</v>
@@ -11423,19 +11423,19 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>RD Congo</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="11" t="n">
         <v>0</v>
@@ -11456,25 +11456,25 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Uzbekistán</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D47" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
@@ -11489,22 +11489,22 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>Panamá</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>0</v>
@@ -11522,28 +11522,28 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>RD Congo</t>
+          <t>Argelia</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0.127</v>
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G49" s="11" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="H49" s="11" t="n">
         <v>0</v>
@@ -11555,19 +11555,19 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>Uzbekistán</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="11" t="n">
         <v>0</v>
@@ -11685,45 +11685,45 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.16</v>
+        <v>0.199</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.205</v>
+        <v>0.327</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.196</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.219</v>
+        <v>0.323</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>0.177</v>
+        <v>0.191</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.185</v>
+        <v>0.217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.222</v>
+        <v>0.218</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.141</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="7">
@@ -11733,141 +11733,141 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.077</v>
+        <v>0.123</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>0.112</v>
+        <v>0.158</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>0.151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.037</v>
+        <v>0.031</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>0.065</v>
+        <v>0.056</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.022</v>
+        <v>0.061</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>0.056</v>
+        <v>0.031</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>0.056</v>
+        <v>0.029</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>0.048</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>0.05</v>
+        <v>0.029</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.044</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B12" s="27" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="C12" s="27" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B13" s="27" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="C13" s="27" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="C14" s="27" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B15" s="27" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="C15" s="27" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -11988,12 +11988,12 @@
           <t>M91</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Noruega</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
@@ -12032,12 +12032,12 @@
           <t>M93</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Bélgica</t>
         </is>
@@ -12076,12 +12076,12 @@
           <t>M95</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Suiza</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -12409,7 +12409,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: España  (22% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: España  (32% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Partidos A-L'!$A$3:$R$75</definedName>
@@ -343,13 +343,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -368,7 +368,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -420,13 +420,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -445,7 +445,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -497,13 +497,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -522,7 +522,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -574,13 +574,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -599,7 +599,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -651,13 +651,13 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -676,7 +676,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -726,13 +726,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -751,7 +751,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -803,13 +803,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -828,7 +828,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -880,13 +880,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -905,7 +905,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -957,13 +957,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -982,7 +982,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1034,13 +1034,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1059,7 +1059,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1111,13 +1111,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1136,7 +1136,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1188,13 +1188,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1213,7 +1213,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1265,13 +1265,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1290,7 +1290,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1342,7 +1342,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1357,9 +1357,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1379,9 +1379,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1401,9 +1401,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1423,9 +1423,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1445,9 +1445,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1467,9 +1467,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1489,9 +1489,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1511,9 +1511,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <c:chart r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1533,9 +1533,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <c:chart r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1555,9 +1555,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <c:chart r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1577,9 +1577,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <c:chart r:id="rId11"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1599,9 +1599,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <c:chart r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1611,7 +1611,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -1626,9 +1626,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -12161,7 +12161,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>9 jul · Gillette Stadium, Boston</t>
+          <t>9 jul 14:00h · Gillette Stadium, Boston</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>10 jul · SoFi Stadium, Los Ángeles</t>
+          <t>10 jul 13:00h · SoFi Stadium, Los Ángeles</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>11 jul · Hard Rock Stadium, Miami</t>
+          <t>11 jul 15:00h · Hard Rock Stadium, Miami</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>11 jul · Arrowhead Stadium, Kansas City</t>
+          <t>11 jul 19:00h · Arrowhead Stadium, Kansas City</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>14 jul · AT&amp;T Stadium, Dallas</t>
+          <t>14 jul 13:00h · AT&amp;T Stadium, Dallas</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>15 jul · Mercedes-Benz, Atlanta</t>
+          <t>15 jul 13:00h · Mercedes-Benz, Atlanta</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>19 jul · MetLife, Nueva York/NJ</t>
+          <t>19 jul 13:00h · MetLife, Nueva York/NJ</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>18 jul · Hard Rock Stadium, Miami</t>
+          <t>18 jul 15:00h · Hard Rock Stadium, Miami</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -10058,13 +10058,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.499</v>
+        <v>0.515</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="5">
@@ -10091,13 +10091,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.733</v>
+        <v>0.749</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.371</v>
+        <v>0.498</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.218</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="6">
@@ -10124,13 +10124,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.647</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.408</v>
+        <v>0.342</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>0.199</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="7">
@@ -10157,17 +10157,17 @@
         <v>1</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.648</v>
+        <v>0.64</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.302</v>
+        <v>0.284</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>0.123</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Marruecos</t>
         </is>
@@ -10190,13 +10190,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.353</v>
+        <v>0.31</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>0.061</v>
+        <v>0.098</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>0.039</v>
       </c>
     </row>
     <row r="9">
@@ -10223,13 +10223,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.352</v>
+        <v>0.36</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.118</v>
+        <v>0.114</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -10256,13 +10256,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.267</v>
+        <v>0.251</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.076</v>
+        <v>0.104</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="11">
@@ -10289,10 +10289,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.184</v>
+        <v>0.17</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.054</v>
+        <v>0.046</v>
       </c>
       <c r="I11" s="24" t="n">
         <v>0.015</v>
@@ -11685,13 +11685,13 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.199</v>
+        <v>0.197</v>
       </c>
       <c r="C4" s="27" t="n">
-        <v>0.327</v>
+        <v>0.433</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.301</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="5">
@@ -11701,13 +11701,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>0.191</v>
+        <v>0.199</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.217</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="6">
@@ -11717,13 +11717,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.218</v>
+        <v>0.252</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>0.18</v>
+        <v>0.196</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.187</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="7">
@@ -11733,45 +11733,45 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.123</v>
+        <v>0.112</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>0.158</v>
+        <v>0.172</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>0.151</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.031</v>
+        <v>0.039</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <v>0.051</v>
+        <v>0</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.061</v>
+        <v>0.03</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>0.037</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="10">
@@ -11781,13 +11781,13 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="11">
@@ -11800,10 +11800,10 @@
         <v>0.015</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.026</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="12">
@@ -12266,14 +12266,14 @@
           <t>M101</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Francia</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>España</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -12288,12 +12288,12 @@
           <t>M102</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
@@ -12339,14 +12339,14 @@
           <t>M104</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>España</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
@@ -12409,7 +12409,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: España  (32% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: España  (33% en la simulación)</t>
         </is>
       </c>
     </row>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Partidos A-L'!$A$3:$R$75</definedName>
@@ -343,13 +343,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -368,7 +368,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -420,13 +420,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -445,7 +445,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -497,13 +497,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -522,7 +522,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -574,13 +574,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -599,7 +599,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -651,13 +651,13 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -676,7 +676,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -726,13 +726,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -751,7 +751,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -803,13 +803,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -828,7 +828,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -880,13 +880,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -905,7 +905,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -957,13 +957,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -982,7 +982,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1034,13 +1034,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1059,7 +1059,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1111,13 +1111,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1136,7 +1136,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1188,13 +1188,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1213,7 +1213,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1265,13 +1265,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1290,7 +1290,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1342,7 +1342,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1357,9 +1357,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1379,9 +1379,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1401,9 +1401,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1423,9 +1423,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1445,9 +1445,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1467,9 +1467,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1489,9 +1489,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1511,9 +1511,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1533,9 +1533,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId9"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1555,9 +1555,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId10"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1577,9 +1577,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId11"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1599,9 +1599,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId12"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1611,7 +1611,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -1626,9 +1626,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Proyeccion-Mundial-2026-MAESTRO.xlsx
+++ b/Proyeccion-Mundial-2026-MAESTRO.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partidos A-L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avance Montecarlo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gráficos avance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro R32" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camino a la final" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Favoritos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuadro octavos-final" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Partidos A-L'!$A$3:$R$75</definedName>
@@ -343,13 +343,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -368,7 +368,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -420,13 +420,13 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -445,7 +445,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -497,13 +497,13 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -522,7 +522,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -574,13 +574,13 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -599,7 +599,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -651,13 +651,13 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -676,7 +676,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -726,13 +726,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -751,7 +751,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -803,13 +803,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -828,7 +828,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -880,13 +880,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -905,7 +905,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -957,13 +957,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -982,7 +982,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1034,13 +1034,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1059,7 +1059,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1111,13 +1111,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1136,7 +1136,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1188,13 +1188,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1213,7 +1213,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1265,13 +1265,13 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1290,7 +1290,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1342,7 +1342,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1357,9 +1357,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1379,9 +1379,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1401,9 +1401,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1423,9 +1423,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1445,9 +1445,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1467,9 +1467,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1489,9 +1489,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1511,9 +1511,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1533,9 +1533,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId9"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1555,9 +1555,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId10"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1577,9 +1577,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId11"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1599,9 +1599,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId12"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1611,7 +1611,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -1626,9 +1626,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2282,13 +2282,13 @@
         <v/>
       </c>
       <c r="J4" s="11" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.203</v>
+        <v>0.212</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>0.115</v>
+        <v>0.101</v>
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         <v/>
       </c>
       <c r="J5" s="11" t="n">
-        <v>0.454</v>
+        <v>0.483</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>0.259</v>
+        <v>0.294</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>0.287</v>
+        <v>0.223</v>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
@@ -2444,13 +2444,13 @@
         <v/>
       </c>
       <c r="J6" s="11" t="n">
-        <v>0.437</v>
+        <v>0.364</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.261</v>
+        <v>0.31</v>
       </c>
       <c r="L6" s="11" t="n">
-        <v>0.303</v>
+        <v>0.326</v>
       </c>
       <c r="M6" s="15" t="inlineStr">
         <is>
@@ -2525,13 +2525,13 @@
         <v/>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.526</v>
+        <v>0.523</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.248</v>
+        <v>0.281</v>
       </c>
       <c r="L7" s="11" t="n">
-        <v>0.227</v>
+        <v>0.196</v>
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
@@ -2606,13 +2606,13 @@
         <v/>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.16</v>
+        <v>0.109</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.226</v>
+        <v>0.213</v>
       </c>
       <c r="L8" s="11" t="n">
-        <v>0.614</v>
+        <v>0.678</v>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
@@ -2687,13 +2687,13 @@
         <v/>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.227</v>
+        <v>0.208</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.248</v>
+        <v>0.296</v>
       </c>
       <c r="L9" s="11" t="n">
-        <v>0.525</v>
+        <v>0.496</v>
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
@@ -2768,13 +2768,13 @@
         <v/>
       </c>
       <c r="J10" s="11" t="n">
-        <v>0.572</v>
+        <v>0.62</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>0.237</v>
+        <v>0.231</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>0.191</v>
+        <v>0.15</v>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
@@ -2849,13 +2849,13 @@
         <v/>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.167</v>
+        <v>0.067</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.228</v>
+        <v>0.156</v>
       </c>
       <c r="L11" s="11" t="n">
-        <v>0.605</v>
+        <v>0.777</v>
       </c>
       <c r="M11" s="15" t="inlineStr">
         <is>
@@ -2930,13 +2930,13 @@
         <v/>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.63</v>
+        <v>0.583</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.221</v>
+        <v>0.269</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
@@ -3011,13 +3011,13 @@
         <v/>
       </c>
       <c r="J13" s="11" t="n">
-        <v>0.546</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.243</v>
+        <v>0.122</v>
       </c>
       <c r="L13" s="11" t="n">
-        <v>0.211</v>
+        <v>0.061</v>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
@@ -3092,13 +3092,13 @@
         <v/>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.426</v>
+        <v>0.367</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.262</v>
+        <v>0.285</v>
       </c>
       <c r="L14" s="11" t="n">
-        <v>0.313</v>
+        <v>0.348</v>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
@@ -3173,13 +3173,13 @@
         <v/>
       </c>
       <c r="J15" s="11" t="n">
-        <v>0.343</v>
+        <v>0.519</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="L15" s="11" t="n">
-        <v>0.393</v>
+        <v>0.213</v>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
@@ -3254,13 +3254,13 @@
         <v/>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0.483</v>
+        <v>0.43</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.255</v>
+        <v>0.292</v>
       </c>
       <c r="L16" s="11" t="n">
-        <v>0.262</v>
+        <v>0.277</v>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
@@ -3335,13 +3335,13 @@
         <v/>
       </c>
       <c r="J17" s="11" t="n">
-        <v>0.29</v>
+        <v>0.209</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.259</v>
+        <v>0.276</v>
       </c>
       <c r="L17" s="11" t="n">
-        <v>0.451</v>
+        <v>0.515</v>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
@@ -3416,13 +3416,13 @@
         <v/>
       </c>
       <c r="J18" s="11" t="n">
-        <v>0.53</v>
+        <v>0.425</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.247</v>
+        <v>0.295</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>0.223</v>
+        <v>0.279</v>
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
@@ -3497,13 +3497,13 @@
         <v/>
       </c>
       <c r="J19" s="11" t="n">
-        <v>0.405</v>
+        <v>0.521</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0.263</v>
+        <v>0.272</v>
       </c>
       <c r="L19" s="11" t="n">
-        <v>0.332</v>
+        <v>0.207</v>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
@@ -3578,13 +3578,13 @@
         <v/>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.295</v>
+        <v>0.457</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.26</v>
+        <v>0.266</v>
       </c>
       <c r="L20" s="11" t="n">
-        <v>0.445</v>
+        <v>0.277</v>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
@@ -3659,13 +3659,13 @@
         <v/>
       </c>
       <c r="J21" s="11" t="n">
-        <v>0.413</v>
+        <v>0.334</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0.262</v>
+        <v>0.327</v>
       </c>
       <c r="L21" s="11" t="n">
-        <v>0.324</v>
+        <v>0.339</v>
       </c>
       <c r="M21" s="15" t="inlineStr">
         <is>
@@ -3740,13 +3740,13 @@
         <v/>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.364</v>
+        <v>0.484</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.264</v>
+        <v>0.255</v>
       </c>
       <c r="L22" s="11" t="n">
-        <v>0.372</v>
+        <v>0.261</v>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
@@ -3821,13 +3821,13 @@
         <v/>
       </c>
       <c r="J23" s="11" t="n">
-        <v>0.245</v>
+        <v>0.297</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0.252</v>
+        <v>0.272</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>0.503</v>
+        <v>0.43</v>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
@@ -3902,13 +3902,13 @@
         <v/>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.141</v>
+        <v>0.127</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.217</v>
+        <v>0.204</v>
       </c>
       <c r="L24" s="11" t="n">
-        <v>0.642</v>
+        <v>0.669</v>
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
@@ -3983,13 +3983,13 @@
         <v/>
       </c>
       <c r="J25" s="11" t="n">
-        <v>0.763</v>
+        <v>0.834</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.169</v>
+        <v>0.116</v>
       </c>
       <c r="L25" s="11" t="n">
-        <v>0.068</v>
+        <v>0.05</v>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
@@ -4064,13 +4064,13 @@
         <v/>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.767</v>
+        <v>0.736</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.167</v>
+        <v>0.172</v>
       </c>
       <c r="L26" s="11" t="n">
-        <v>0.066</v>
+        <v>0.092</v>
       </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         <v/>
       </c>
       <c r="J27" s="11" t="n">
-        <v>0.144</v>
+        <v>0.073</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.218</v>
+        <v>0.148</v>
       </c>
       <c r="L27" s="11" t="n">
-        <v>0.638</v>
+        <v>0.778</v>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
@@ -4226,13 +4226,13 @@
         <v/>
       </c>
       <c r="J28" s="11" t="n">
-        <v>0.725</v>
+        <v>0.839</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>0.186</v>
+        <v>0.115</v>
       </c>
       <c r="L28" s="11" t="n">
-        <v>0.089</v>
+        <v>0.046</v>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
@@ -4307,13 +4307,13 @@
         <v/>
       </c>
       <c r="J29" s="11" t="n">
-        <v>0.207</v>
+        <v>0.251</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.242</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="11" t="n">
-        <v>0.55</v>
+        <v>0.449</v>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
@@ -4388,10 +4388,10 @@
         <v/>
       </c>
       <c r="J30" s="11" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.543</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>0.241</v>
+        <v>0.256</v>
       </c>
       <c r="L30" s="11" t="n">
         <v>0.202</v>
@@ -4469,13 +4469,13 @@
         <v/>
       </c>
       <c r="J31" s="11" t="n">
-        <v>0.72</v>
+        <v>0.752</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.188</v>
+        <v>0.174</v>
       </c>
       <c r="L31" s="11" t="n">
-        <v>0.092</v>
+        <v>0.074</v>
       </c>
       <c r="M31" s="15" t="inlineStr">
         <is>
@@ -4550,13 +4550,13 @@
         <v/>
       </c>
       <c r="J32" s="11" t="n">
-        <v>0.362</v>
+        <v>0.293</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.264</v>
+        <v>0.281</v>
       </c>
       <c r="L32" s="11" t="n">
-        <v>0.374</v>
+        <v>0.426</v>
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
@@ -4631,13 +4631,13 @@
         <v/>
       </c>
       <c r="J33" s="11" t="n">
-        <v>0.214</v>
+        <v>0.123</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.244</v>
+        <v>0.224</v>
       </c>
       <c r="L33" s="11" t="n">
-        <v>0.542</v>
+        <v>0.653</v>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
@@ -4712,13 +4712,13 @@
         <v/>
       </c>
       <c r="J34" s="11" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>0.263</v>
+        <v>0.301</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>0.335</v>
+        <v>0.298</v>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
@@ -4793,13 +4793,13 @@
         <v/>
       </c>
       <c r="J35" s="11" t="n">
-        <v>0.398</v>
+        <v>0.404</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.263</v>
+        <v>0.294</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>0.338</v>
+        <v>0.302</v>
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
@@ -4874,13 +4874,13 @@
         <v/>
       </c>
       <c r="J36" s="11" t="n">
-        <v>0.584</v>
+        <v>0.618</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.234</v>
+        <v>0.23</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>0.182</v>
+        <v>0.152</v>
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
         <v/>
       </c>
       <c r="J37" s="11" t="n">
-        <v>0.184</v>
+        <v>0.155</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.235</v>
+        <v>0.265</v>
       </c>
       <c r="L37" s="11" t="n">
         <v>0.58</v>
@@ -5036,13 +5036,13 @@
         <v/>
       </c>
       <c r="J38" s="11" t="n">
-        <v>0.549</v>
+        <v>0.551</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.243</v>
+        <v>0.26</v>
       </c>
       <c r="L38" s="11" t="n">
-        <v>0.208</v>
+        <v>0.189</v>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
@@ -5117,13 +5117,13 @@
         <v/>
       </c>
       <c r="J39" s="11" t="n">
-        <v>0.16</v>
+        <v>0.124</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.225</v>
+        <v>0.232</v>
       </c>
       <c r="L39" s="11" t="n">
-        <v>0.615</v>
+        <v>0.644</v>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
@@ -5198,13 +5198,13 @@
         <v/>
       </c>
       <c r="J40" s="11" t="n">
-        <v>0.111</v>
+        <v>0.133</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="L40" s="11" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
@@ -5279,13 +5279,13 @@
         <v/>
       </c>
       <c r="J41" s="11" t="n">
-        <v>0.845</v>
+        <v>0.847</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.126</v>
+        <v>0.117</v>
       </c>
       <c r="L41" s="11" t="n">
-        <v>0.029</v>
+        <v>0.036</v>
       </c>
       <c r="M41" s="15" t="inlineStr">
         <is>
@@ -5360,13 +5360,13 @@
         <v/>
       </c>
       <c r="J42" s="11" t="n">
-        <v>0.876</v>
+        <v>0.87</v>
       </c>
       <c r="K42" s="11" t="n">
         <v>0.106</v>
       </c>
       <c r="L42" s="11" t="n">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
@@ -5441,13 +5441,13 @@
         <v/>
       </c>
       <c r="J43" s="11" t="n">
-        <v>0.633</v>
+        <v>0.549</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0.22</v>
+        <v>0.264</v>
       </c>
       <c r="L43" s="11" t="n">
-        <v>0.147</v>
+        <v>0.186</v>
       </c>
       <c r="M43" s="15" t="inlineStr">
         <is>
@@ -5522,13 +5522,13 @@
         <v/>
       </c>
       <c r="J44" s="11" t="n">
-        <v>0.426</v>
+        <v>0.437</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>0.262</v>
+        <v>0.294</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>0.313</v>
+        <v>0.269</v>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
@@ -5603,13 +5603,13 @@
         <v/>
       </c>
       <c r="J45" s="11" t="n">
-        <v>0.163</v>
+        <v>0.107</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.227</v>
+        <v>0.239</v>
       </c>
       <c r="L45" s="11" t="n">
-        <v>0.611</v>
+        <v>0.655</v>
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
@@ -5684,13 +5684,13 @@
         <v/>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0.539</v>
+        <v>0.609</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>0.245</v>
+        <v>0.231</v>
       </c>
       <c r="L46" s="11" t="n">
-        <v>0.216</v>
+        <v>0.16</v>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
@@ -5765,13 +5765,13 @@
         <v/>
       </c>
       <c r="J47" s="11" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0.241</v>
+        <v>0.225</v>
       </c>
       <c r="L47" s="11" t="n">
-        <v>0.202</v>
+        <v>0.17</v>
       </c>
       <c r="M47" s="15" t="inlineStr">
         <is>
@@ -5846,13 +5846,13 @@
         <v/>
       </c>
       <c r="J48" s="11" t="n">
-        <v>0.479</v>
+        <v>0.577</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>0.256</v>
+        <v>0.242</v>
       </c>
       <c r="L48" s="11" t="n">
-        <v>0.266</v>
+        <v>0.181</v>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
@@ -5927,13 +5927,13 @@
         <v/>
       </c>
       <c r="J49" s="11" t="n">
-        <v>0.25</v>
+        <v>0.193</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="L49" s="11" t="n">
-        <v>0.497</v>
+        <v>0.571</v>
       </c>
       <c r="M49" s="8" t="inlineStr">
         <is>
@@ -6008,13 +6008,13 @@
         <v/>
       </c>
       <c r="J50" s="11" t="n">
-        <v>0.312</v>
+        <v>0.33</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>0.262</v>
+        <v>0.279</v>
       </c>
       <c r="L50" s="11" t="n">
-        <v>0.427</v>
+        <v>0.391</v>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
@@ -6089,13 +6089,13 @@
         <v/>
       </c>
       <c r="J51" s="11" t="n">
-        <v>0.124</v>
+        <v>0.062</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.208</v>
+        <v>0.136</v>
       </c>
       <c r="L51" s="11" t="n">
-        <v>0.668</v>
+        <v>0.802</v>
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v/>
       </c>
       <c r="J52" s="11" t="n">
-        <v>0.586</v>
+        <v>0.711</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>0.234</v>
+        <v>0.168</v>
       </c>
       <c r="L52" s="11" t="n">
-        <v>0.18</v>
+        <v>0.121</v>
       </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
@@ -6251,13 +6251,13 @@
         <v/>
       </c>
       <c r="J53" s="11" t="n">
-        <v>0.143</v>
+        <v>0.078</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.218</v>
+        <v>0.137</v>
       </c>
       <c r="L53" s="11" t="n">
-        <v>0.64</v>
+        <v>0.785</v>
       </c>
       <c r="M53" s="8" t="inlineStr">
         <is>
@@ -6332,13 +6332,13 @@
         <v/>
       </c>
       <c r="J54" s="11" t="n">
-        <v>0.784</v>
+        <v>0.963</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>0.159</v>
+        <v>0.03</v>
       </c>
       <c r="L54" s="11" t="n">
-        <v>0.057</v>
+        <v>0.008</v>
       </c>
       <c r="M54" s="8" t="inlineStr">
         <is>
@@ -6413,13 +6413,13 @@
         <v/>
       </c>
       <c r="J55" s="11" t="n">
-        <v>0.428</v>
+        <v>0.336</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0.261</v>
+        <v>0.234</v>
       </c>
       <c r="L55" s="11" t="n">
-        <v>0.311</v>
+        <v>0.43</v>
       </c>
       <c r="M55" s="8" t="inlineStr">
         <is>
@@ -6494,13 +6494,13 @@
         <v/>
       </c>
       <c r="J56" s="11" t="n">
-        <v>0.227</v>
+        <v>0.1</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>0.248</v>
+        <v>0.158</v>
       </c>
       <c r="L56" s="11" t="n">
-        <v>0.525</v>
+        <v>0.742</v>
       </c>
       <c r="M56" s="8" t="inlineStr">
         <is>
@@ -6575,13 +6575,13 @@
         <v/>
       </c>
       <c r="J57" s="11" t="n">
-        <v>0.579</v>
+        <v>0.828</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0.235</v>
+        <v>0.112</v>
       </c>
       <c r="L57" s="11" t="n">
-        <v>0.185</v>
+        <v>0.06</v>
       </c>
       <c r="M57" s="8" t="inlineStr">
         <is>
@@ -6656,13 +6656,13 @@
         <v/>
       </c>
       <c r="J58" s="11" t="n">
-        <v>0.491</v>
+        <v>0.522</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>0.254</v>
+        <v>0.238</v>
       </c>
       <c r="L58" s="11" t="n">
-        <v>0.255</v>
+        <v>0.24</v>
       </c>
       <c r="M58" s="8" t="inlineStr">
         <is>
@@ -6737,13 +6737,13 @@
         <v/>
       </c>
       <c r="J59" s="11" t="n">
-        <v>0.161</v>
+        <v>0.244</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.226</v>
+        <v>0.331</v>
       </c>
       <c r="L59" s="11" t="n">
-        <v>0.614</v>
+        <v>0.426</v>
       </c>
       <c r="M59" s="8" t="inlineStr">
         <is>
@@ -6818,13 +6818,13 @@
         <v/>
       </c>
       <c r="J60" s="11" t="n">
-        <v>0.874</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>0.108</v>
+        <v>0.137</v>
       </c>
       <c r="L60" s="11" t="n">
-        <v>0.018</v>
+        <v>0.048</v>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
@@ -6899,13 +6899,13 @@
         <v/>
       </c>
       <c r="J61" s="11" t="n">
-        <v>0.203</v>
+        <v>0.151</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.241</v>
+        <v>0.237</v>
       </c>
       <c r="L61" s="11" t="n">
-        <v>0.556</v>
+        <v>0.612</v>
       </c>
       <c r="M61" s="8" t="inlineStr">
         <is>
@@ -6980,13 +6980,13 @@
         <v/>
       </c>
       <c r="J62" s="11" t="n">
-        <v>0.787</v>
+        <v>0.726</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>0.157</v>
+        <v>0.183</v>
       </c>
       <c r="L62" s="11" t="n">
-        <v>0.056</v>
+        <v>0.091</v>
       </c>
       <c r="M62" s="8" t="inlineStr">
         <is>
@@ -7061,13 +7061,13 @@
         <v/>
       </c>
       <c r="J63" s="11" t="n">
-        <v>0.118</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.204</v>
+        <v>0.195</v>
       </c>
       <c r="L63" s="11" t="n">
-        <v>0.678</v>
+        <v>0.719</v>
       </c>
       <c r="M63" s="8" t="inlineStr">
         <is>
@@ -7142,13 +7142,13 @@
         <v/>
       </c>
       <c r="J64" s="11" t="n">
-        <v>0.644</v>
+        <v>0.511</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>0.216</v>
+        <v>0.285</v>
       </c>
       <c r="L64" s="11" t="n">
-        <v>0.14</v>
+        <v>0.205</v>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
@@ -7223,13 +7223,13 @@
         <v/>
       </c>
       <c r="J65" s="11" t="n">
-        <v>0.144</v>
+        <v>0.079</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.218</v>
+        <v>0.182</v>
       </c>
       <c r="L65" s="11" t="n">
-        <v>0.638</v>
+        <v>0.739</v>
       </c>
       <c r="M65" s="8" t="inlineStr">
         <is>
@@ -7304,13 +7304,13 @@
         <v/>
       </c>
       <c r="J66" s="11" t="n">
-        <v>0.607</v>
+        <v>0.668</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>0.228</v>
+        <v>0.212</v>
       </c>
       <c r="L66" s="11" t="n">
-        <v>0.166</v>
+        <v>0.12</v>
       </c>
       <c r="M66" s="8" t="inlineStr">
         <is>
@@ -7385,13 +7385,13 @@
         <v/>
       </c>
       <c r="J67" s="11" t="n">
-        <v>0.674</v>
+        <v>0.588</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.206</v>
+        <v>0.265</v>
       </c>
       <c r="L67" s="11" t="n">
-        <v>0.12</v>
+        <v>0.146</v>
       </c>
       <c r="M67" s="8" t="inlineStr">
         <is>
@@ -7466,13 +7466,13 @@
         <v/>
       </c>
       <c r="J68" s="11" t="n">
-        <v>0.399</v>
+        <v>0.413</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>0.263</v>
+        <v>0.329</v>
       </c>
       <c r="L68" s="11" t="n">
-        <v>0.338</v>
+        <v>0.258</v>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
@@ -7547,13 +7547,13 @@
         <v/>
       </c>
       <c r="J69" s="11" t="n">
-        <v>0.332</v>
+        <v>0.503</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.263</v>
+        <v>0.261</v>
       </c>
       <c r="L69" s="11" t="n">
-        <v>0.405</v>
+        <v>0.236</v>
       </c>
       <c r="M69" s="8" t="inlineStr">
         <is>
@@ -7628,13 +7628,13 @@
         <v/>
       </c>
       <c r="J70" s="11" t="n">
-        <v>0.754</v>
+        <v>0.799</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>0.173</v>
+        <v>0.135</v>
       </c>
       <c r="L70" s="11" t="n">
-        <v>0.073</v>
+        <v>0.065</v>
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
@@ -7709,13 +7709,13 @@
         <v/>
       </c>
       <c r="J71" s="11" t="n">
-        <v>0.55</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.242</v>
+        <v>0.227</v>
       </c>
       <c r="L71" s="11" t="n">
-        <v>0.207</v>
+        <v>0.216</v>
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
@@ -7790,13 +7790,13 @@
         <v/>
       </c>
       <c r="J72" s="11" t="n">
-        <v>0.678</v>
+        <v>0.805</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>0.204</v>
+        <v>0.126</v>
       </c>
       <c r="L72" s="11" t="n">
-        <v>0.118</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
@@ -7871,13 +7871,13 @@
         <v/>
       </c>
       <c r="J73" s="11" t="n">
-        <v>0.276</v>
+        <v>0.236</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.257</v>
+        <v>0.255</v>
       </c>
       <c r="L73" s="11" t="n">
-        <v>0.466</v>
+        <v>0.51</v>
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
@@ -7952,13 +7952,13 @@
         <v/>
       </c>
       <c r="J74" s="11" t="n">
-        <v>0.291</v>
+        <v>0.351</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>0.259</v>
+        <v>0.243</v>
       </c>
       <c r="L74" s="11" t="n">
-        <v>0.45</v>
+        <v>0.406</v>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
@@ -8033,13 +8033,13 @@
         <v/>
       </c>
       <c r="J75" s="11" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.132</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L75" s="11" t="n">
-        <v>0.835</v>
+        <v>0.884</v>
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>1</v>
@@ -8431,7 +8431,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>1</v>
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>1</v>
@@ -8755,7 +8755,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>1</v>
@@ -9079,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>1</v>
@@ -9160,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>1</v>
@@ -9295,7 +9295,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="11" t="n">
         <v>1</v>
@@ -9349,7 +9349,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="11" t="n">
         <v>1</v>
@@ -10037,16 +10037,16 @@
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1</v>
@@ -10058,28 +10058,28 @@
         <v>1</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.515</v>
+        <v>0.516</v>
       </c>
       <c r="I4" s="17" t="n">
-        <v>0.328</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>España</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>1</v>
@@ -10091,28 +10091,28 @@
         <v>1</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.749</v>
+        <v>1</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.498</v>
+        <v>0.484</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.252</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>Francia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>1</v>
@@ -10124,13 +10124,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.342</v>
+        <v>0.611</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>0.197</v>
+        <v>0.263</v>
       </c>
     </row>
     <row r="7">
@@ -10157,28 +10157,28 @@
         <v>1</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>0.284</v>
+        <v>0.389</v>
       </c>
       <c r="I7" s="23" t="n">
-        <v>0.112</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1</v>
@@ -10187,130 +10187,130 @@
         <v>1</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="H9" s="11" t="n">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>0.104</v>
+        <v>0</v>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
@@ -10334,16 +10334,16 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1</v>
@@ -10367,16 +10367,16 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>0</v>
@@ -10400,25 +10400,25 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>0</v>
@@ -10433,16 +10433,16 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>1</v>
@@ -10466,22 +10466,22 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Bosnia y Herzegovina</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>0</v>
@@ -10499,19 +10499,19 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Catar</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
         <v>0</v>
@@ -10532,7 +10532,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>Turquía</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -10541,13 +10541,13 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>0</v>
@@ -10565,16 +10565,16 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>1</v>
@@ -10598,25 +10598,25 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Marruecos</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>0</v>
@@ -10631,16 +10631,16 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Turquía</t>
+          <t>Haití</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Escocia</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -10673,13 +10673,13 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -10697,19 +10697,19 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>Haití</t>
+          <t>Alemania</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>0</v>
@@ -10730,16 +10730,16 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Escocia</t>
+          <t>Curazao</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>0</v>
@@ -10763,7 +10763,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Alemania</t>
+          <t>Costa de Marfil</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>1</v>
@@ -10796,7 +10796,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Curazao</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -10805,10 +10805,10 @@
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>0</v>
@@ -10829,16 +10829,16 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Costa de Marfil</t>
+          <t>Países Bajos</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>1</v>
@@ -10862,16 +10862,16 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Japón</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>1</v>
@@ -10895,7 +10895,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Países Bajos</t>
+          <t>Suecia</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>1</v>
@@ -10928,7 +10928,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>Japón</t>
+          <t>Túnez</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>0</v>
@@ -10961,19 +10961,19 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Suecia</t>
+          <t>Arabia Saudita</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="11" t="n">
         <v>0</v>
@@ -10994,16 +10994,16 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Túnez</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>0</v>
@@ -11027,7 +11027,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Arabia Saudita</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -11036,10 +11036,10 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>0</v>
@@ -11060,25 +11060,25 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="11" t="n">
         <v>0</v>
@@ -11093,22 +11093,22 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Egipto</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>0</v>
@@ -11126,7 +11126,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Egipto</t>
+          <t>Irán</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -11135,13 +11135,13 @@
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>0</v>
@@ -11159,7 +11159,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Irán</t>
+          <t>Nueva Zelanda</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -11168,7 +11168,7 @@
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>0</v>
@@ -11192,19 +11192,19 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Nueva Zelanda</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>0</v>
@@ -11225,7 +11225,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="11" t="n">
         <v>0</v>
@@ -11258,7 +11258,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -11267,16 +11267,16 @@
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="D41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="11" t="n">
         <v>0</v>
@@ -11685,13 +11685,13 @@
         </is>
       </c>
       <c r="B4" s="27" t="n">
-        <v>0.197</v>
+        <v>0.323</v>
       </c>
       <c r="C4" s="27" t="n">
         <v>0.433</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0.386</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="5">
@@ -11701,13 +11701,13 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>0.328</v>
+        <v>0.293</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>0.199</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>0.225</v>
+        <v>0.218</v>
       </c>
     </row>
     <row r="6">
@@ -11717,13 +11717,13 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>0.252</v>
+        <v>0.263</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>0.196</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.207</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="7">
@@ -11733,83 +11733,83 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.112</v>
+        <v>0.121</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.172</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>0.16</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Marruecos</t>
+          <t>México</t>
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Sudáfrica</t>
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Suiza</t>
+          <t>Corea del Sur</t>
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>República Checa</t>
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="C11" s="27" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Canadá</t>
         </is>
       </c>
       <c r="B12" s="27" t="n">
@@ -11825,7 +11825,7 @@
     <row r="13">
       <c r="A13" s="26" t="inlineStr">
         <is>
-          <t>Sudáfrica</t>
+          <t>Bosnia y Herzegovina</t>
         </is>
       </c>
       <c r="B13" s="27" t="n">
@@ -11841,7 +11841,7 @@
     <row r="14">
       <c r="A14" s="26" t="inlineStr">
         <is>
-          <t>Corea del Sur</t>
+          <t>Catar</t>
         </is>
       </c>
       <c r="B14" s="27" t="n">
@@ -11857,7 +11857,7 @@
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>República Checa</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="B15" s="27" t="n">
@@ -12266,12 +12266,12 @@
           <t>M101</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Francia</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>España</t>
         </is>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
-          <t>España</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -12390,14 +12390,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Argentina</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -12409,7 +12409,7 @@
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>CAMPEÓN PROYECTADO: España  (33% en la simulación)</t>
+          <t>CAMPEÓN PROYECTADO: Francia  (32% en la simulación)</t>
         </is>
       </c>
     </row>
